--- a/diagnostic/Business-Diagnostic-Spec.xlsx
+++ b/diagnostic/Business-Diagnostic-Spec.xlsx
@@ -13282,7 +13282,7 @@
       </c>
       <c r="F233" s="7" t="inlineStr">
         <is>
-          <t>most of it</t>
+          <t>Most</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr"/>
@@ -13315,7 +13315,7 @@
       </c>
       <c r="F234" s="7" t="inlineStr">
         <is>
-          <t>some of it</t>
+          <t>Some</t>
         </is>
       </c>
       <c r="G234" s="5" t="inlineStr"/>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F235" s="7" t="inlineStr">
         <is>
-          <t>almost none of it</t>
+          <t>Almost none</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr"/>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="F240" s="7" t="inlineStr">
         <is>
-          <t>not at all</t>
+          <t>next to never</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr"/>
@@ -13751,7 +13751,7 @@
       </c>
       <c r="F246" s="7" t="inlineStr">
         <is>
-          <t>almost none of it</t>
+          <t>almost none</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr"/>
@@ -13784,7 +13784,7 @@
       </c>
       <c r="F247" s="7" t="inlineStr">
         <is>
-          <t>some of it</t>
+          <t>some</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr"/>
@@ -13821,7 +13821,7 @@
       </c>
       <c r="F248" s="7" t="inlineStr">
         <is>
-          <t>most of it</t>
+          <t>most</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr"/>
@@ -13858,7 +13858,7 @@
       </c>
       <c r="F249" s="7" t="inlineStr">
         <is>
-          <t>all of it</t>
+          <t>all</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr"/>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="F251" s="7" t="inlineStr">
         <is>
-          <t>written down</t>
+          <t>a written plan</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr"/>
@@ -14076,7 +14076,7 @@
       </c>
       <c r="F255" s="7" t="inlineStr">
         <is>
-          <t>nothing</t>
+          <t>none</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr"/>
@@ -14253,7 +14253,7 @@
       </c>
       <c r="F260" s="7" t="inlineStr">
         <is>
-          <t>partly</t>
+          <t>only partly a match for what you wanted</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr"/>
@@ -16959,7 +16959,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>You've got {q46.band} of how the work gets done written down. Every new hire takes longer than it should, quality moves depending on who's on the job, and nothing can be handed over cleanly.</t>
+          <t>{q46.band} of how the work gets done is written down. Every new hire takes longer than it should, quality moves depending on who's on the job, and nothing can be handed over cleanly.</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr"/>

--- a/diagnostic/Business-Diagnostic-Spec.xlsx
+++ b/diagnostic/Business-Diagnostic-Spec.xlsx
@@ -26,16 +26,16 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Questions'!$A$2:$I$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Answer options'!$A$2:$I$262</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Constraints and order'!$A$2:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Report, constraint'!$A$2:$D$96</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Report, minor'!$A$2:$C$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Report, risk flags'!$A$2:$G$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Report, constraint'!$A$2:$E$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Report, minor'!$A$2:$D$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Report, risk flags'!$A$2:$H$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Report, risk framing'!$A$2:$E$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Report, compound'!$A$2:$D$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Report, compound'!$A$2:$E$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Report, don''t do yet'!$A$2:$C$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Report, open and close'!$A$2:$D$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Report, open and close'!$A$2:$E$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Thresholds'!$A$2:$C$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Logic'!$A$1:$B$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Data slots'!$A$2:$G$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Data slots'!$A$2:$F$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -129,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -154,6 +154,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -520,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -575,227 +578,239 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Ids the engine matches on. Changing one breaks the link between a question, its answer and the report line that quotes it.</t>
+          <t>Ids the engine matches on, and columns it works out for you. Changing one breaks the link between a question, its answer and the report line that quotes it.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>Variables</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Anything in {curly braces} is filled in from the answers. Write band phrases lower case, because sentence case is applied after a variable is filled in, so one landing at the start of a sentence gets capitalised for you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>White cells</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Numbers and settings. Safe to change, and the Thresholds tab explains what each one does.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="3" t="inlineStr"/>
-    </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>The one rule</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>The report names one constraint. Not a list. If an edit starts adding a second finding, it is working against the tool.</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>The second rule</t>
+          <t>The one rule</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>No scores, no grades, no dollar figures, no timeframes. None of those can be defended from banded answers.</t>
+          <t>The report names one constraint. Not a list. If an edit starts adding a second finding, it is working against the tool.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>The second rule</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>No scores, no grades, no dollar figures, no timeframes. None of those can be defended from banded answers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>Voice</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>No dashes of any kind. No colons except before a list. Australian spelling. Contractions throughout.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="3" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Tabs, in order</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Questions</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>All 52 questions. Wording, help text, which block each one feeds, how heavily it counts.</t>
-        </is>
-      </c>
+          <t>Tabs, in order</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Answer options</t>
+          <t>Questions</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Every option under every question. This is where the bands live, and the band phrase is what gets quoted in the report.</t>
+          <t>All 52 questions. Wording, help text, which block each one feeds, how heavily it counts.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Constraints and order</t>
+          <t>Answer options</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>The seven constraints, the fixed order they are checked in, and what suppresses what.</t>
+          <t>Every option under every question. This is where the bands live, and the band phrase is what gets quoted in the report.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Report, constraint</t>
+          <t>Constraints and order</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>The constraint blocks. Opening line, evidence clauses, closing line, and the fix actions.</t>
+          <t>The seven constraints, the fixed order they are checked in, and what suppresses what.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Report, minor</t>
+          <t>Report, constraint</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>The one line that prints when a second constraint is loud but downstream.</t>
+          <t>The constraint blocks. Opening line, evidence clauses, closing line, and the fix actions.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Report, risk flags</t>
+          <t>Report, minor</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>All 16 risk flags. Definition, the version used when the answer was Not sure, and the fix.</t>
+          <t>The one line that prints when a second constraint is loud but downstream.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Report, risk framing</t>
+          <t>Report, risk flags</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>The three family blocks and the minor risk lines.</t>
+          <t>All 16 risk flags. Definition, the version used when the answer was Not sure, and the fix.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Report, compound</t>
+          <t>Report, risk framing</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>The blocks that fire when a risk and the constraint are the same problem seen twice.</t>
+          <t>The three family blocks and the minor risk lines.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Report, don't do yet</t>
+          <t>Report, compound</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>The closing section. What not to touch until the constraint is fixed.</t>
+          <t>The blocks that fire when a risk and the constraint are the same problem seen twice.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Report, open and close</t>
+          <t>Report, don't do yet</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>The opening and closing of the report, including the three opening variants.</t>
+          <t>The closing section. What not to touch until the constraint is fixed.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Thresholds</t>
+          <t>Report, open and close</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Every tunable number, and what moving it does.</t>
+          <t>The opening and closing of the report, including the three opening variants.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Logic</t>
+          <t>Thresholds</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>How the engine picks the primary, the minor, and the risks. Read this before changing a threshold.</t>
+          <t>Every tunable number, and what moving it does.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>Logic</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>How the engine picks the primary, the minor, and the risks. Read this before changing a threshold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>Data slots</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Which questions can be quoted in the report, and how.</t>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Every variable, every phrase it can print, and which report blocks quote it. Check here before changing a band phrase, because it shows you the sentences that band lands in.</t>
         </is>
       </c>
     </row>
@@ -1571,13 +1586,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="108" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="98" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1608,6 +1624,11 @@
           <t>Wording</t>
         </is>
       </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Variables in this row</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -1631,6 +1652,7 @@
 It names one constraint. There'll be other things wrong, there always are. They're not in here because the order you fix them in matters more than the list.</t>
         </is>
       </c>
+      <c r="E3" s="9" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -1654,6 +1676,7 @@
 What follows is the tightest thing in the business rather than a problem. Treat it as where the next bit of growth will come from, not something to fix.</t>
         </is>
       </c>
+      <c r="E4" s="9" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -1677,6 +1700,7 @@
 What follows is the tightest thing in the business right now rather than something that's failing outright. Treat it as the next thing to work on, not an emergency.</t>
         </is>
       </c>
+      <c r="E5" s="9" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1700,6 +1724,7 @@
 The finding below is the best available reading of what you did tell us. The bigger issue is that the business isn't visible to you, and that's covered in the risk section. Come back and run this again once you can answer the numbers.</t>
         </is>
       </c>
+      <c r="E6" s="9" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1722,6 +1747,11 @@
           <t>Nothing in here is failing, so there's no evidence to walk you through. What you've got is {d.primaryShort} sitting as the tightest of the seven right now, which makes it the likeliest place the next bit of growth comes from. The actions below are worth doing and none of them are urgent.</t>
         </is>
       </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>{d.primaryShort}</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1745,6 +1775,11 @@
 The risk section is the part of this report to take seriously. Not being able to answer the questions is the finding, and it's the one worth acting on first.</t>
         </is>
       </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>{d.primaryShort}</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1768,6 +1803,7 @@
 Work the constraint and check back in ninety days. That's long enough for it to move and short enough that you'll still remember what you changed.</t>
         </is>
       </c>
+      <c r="E9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1791,6 +1827,7 @@
 Run this again in ninety days, or whenever something material changes. The constraint moves as the business grows, and the answer you get next time probably won't be this one.</t>
         </is>
       </c>
+      <c r="E10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1814,6 +1851,7 @@
 Get the numbers visible, then run this again. The second time through it will be worth something.</t>
         </is>
       </c>
+      <c r="E11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1832,11 +1870,12 @@
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D12"/>
+  <autoFilter ref="A2:E12"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2186,1156 +2225,1406 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="66" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>An exact figure is only offered on questions whose answer actually reaches the report prose, not on all fifty two. Asking for a number the report never uses is friction for nothing.</t>
+          <t>An exact figure is only offered on questions whose answer actually reaches the report prose, not on all fifty two. Asking for a number the report never uses is friction for nothing. Sentence case is applied after a variable is filled in, so write band phrases lower case and let the engine capitalise the ones that land at the start of a sentence.</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
           <t>Q#</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>q id</t>
-        </is>
-      </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Question</t>
+          <t>Question it comes from</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Band quoted in the report</t>
+          <t>Every phrase it can print</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>Offers an exact figure</t>
+          <t>When it does not resolve</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>Exact figure quoted</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>Unit</t>
+          <t>Report blocks that quote it</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>{q6.band}</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>q6</t>
-        </is>
-      </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">In the last 6 months, how often have you delayed paying a supplier, a </t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr"/>
+          <t>In the last 6 months, how often have you delayed paying a supplier, a bill or yourself because the money hadn't landed yet?</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>never | once or twice | most months | every month</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / cashflow / evidence [2] / banded</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>{q7.band}</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>q7</t>
-        </is>
-      </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">From finishing a job to the money hitting your account, how long does </t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>days</t>
+          <t>From finishing a job to the money hitting your account, how long does it usually take?</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>upfront or on the day | inside a fortnight | in the 15 to 30 day range | in the 31 to 60 day range | beyond 60 days</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / cashflow / evidence [1] / banded</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>{q7.exact}</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>From finishing a job to the money hitting your account, how long does it usually take?</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>the number they typed, in days</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>optional, so the precise wording only prints when it was filled in</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / cashflow / evidence [1] / precise</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>{q8.band}</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>q8</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">If revenue stopped tomorrow, how long could you cover wages and fixed </t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>If revenue stopped tomorrow, how long could you cover wages and fixed costs from the cash you have?</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>more than three months of cover | one to three months of cover | two to four weeks of cover | under a fortnight of cover</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / cashflow / evidence [3] / banded  riskDef / no_buffer / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>{q9.band}</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>q9</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>In the last 12 months, have you turned down or delayed work because yo</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>In the last 12 months, have you turned down or delayed work because you couldn't fund the upfront cost of it?</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>never | once | a few times | regularly</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / cashflow / evidence [4] / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>{q12.band}</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>q12</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>If you were uncontactable for a month, what happens to the business?</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>runs fine without you | runs, but the decisions wait for you | degrades quickly without you | stops without you</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / talent / evidence [2] / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>{q13.band}</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>q13</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>How much of your week goes to work someone a level below you could do?</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>almost none of your week | about a quarter of your week | about half your week | most of your week</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / talent / evidence [1] / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>{q14.band}</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>q14</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>In the last 12 months, has something you wanted to grow stalled becaus</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>In the last 12 months, has something you wanted to grow stalled because there was nobody to hand it to?</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>never | once | a few times | as a matter of routine</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / talent / evidence [3] / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>{q16.band}</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>q16</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>How booked is your delivery capacity for the next 30 days?</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>under half full | around two thirds full | at or near full | full, with people waiting | over capacity and behind</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / fulfilment / evidence [1] / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>{q16.exact}</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>How booked is your delivery capacity for the next 30 days?</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>the number they typed, in %</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>optional, so the precise wording only prints when it was filled in</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / fulfilment / evidence [1] / precise</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>{q17.band}</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>q17</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">In the last 6 months, have you turned work away or pushed out a start </t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>In the last 6 months, have you turned work away or pushed out a start date because you couldn't fit it in?</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>never | once or twice | most months | constantly</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / fulfilment / evidence [2] / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>{q18.band}</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>q18</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>What's happened to your lead time in the last 12 months?</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>come down | held steady | stretched out | blown out</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / fulfilment / evidence [3] / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>{q19.band}</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>q19</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>How often does delivery slip past what you promised the customer?</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>rarely | occasionally | regularly | on most jobs</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / fulfilment / evidence [4] / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>{q21.band}</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>q21</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Of the customers who bought from you a year ago, roughly how many stil</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Of the customers who bought from you a year ago, roughly how many still buy from you?</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>above 70% | around half | under a third | close to none | one off by design</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / value / evidence [1] / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>{q21.exact}</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Of the customers who bought from you a year ago, roughly how many still buy from you?</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>the number they typed, in %</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>optional, so the precise wording only prints when it was filled in</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / value / evidence [1] / precise</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>{q22.band}</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>q22</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>How often do customers come back and buy again without you chasing the</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>How often do customers come back and buy again without you chasing them?</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>usually | sometimes | rarely | never</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / value / evidence [2] / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>{q23.band}</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>q23</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>How many of your new customers arrive through a referral from an exist</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>How many of your new customers arrive through a referral from an existing one?</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>most of them | about half | a few | almost none</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / value / evidence [3] / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>{q26.band}</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>q26</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Of the people who enquire and get a quote or a proposal, how many go a</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Of the people who enquire and get a quote or a proposal, how many go ahead?</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>above 50% | in the 25 to 50% range | in the 10 to 25% range | under 10%</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / offer / evidence [1] / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>{q26.exact}</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Of the people who enquire and get a quote or a proposal, how many go ahead?</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>the number they typed, in %</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>optional, so the precise wording only prints when it was filled in</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / offer / evidence [1] / precise</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>{q27.band}</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>q27</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>When you lose a deal, what's the most common reason?</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>price | timing | a competitor | inaction | unknown</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / offer / evidence [2] / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>{q28.band}</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>q28</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">How often do you have to explain what you do twice, or get asked what </t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>How often do you have to explain what you do twice, or get asked what exactly you sell?</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>rarely | sometimes | often | in most conversations</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / offer / evidence [3] / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>{q31.band}</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>q31</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>How many new enquiries does the business get in a typical month?</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>a month</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>a handful at most | in the 3 to 10 range | in the 11 to 30 range | in the 31 to 100 range | above 100</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / demand / evidence [1] / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>{q31.exact}</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>How many new enquiries does the business get in a typical month?</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>the number they typed, in a month</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>optional, so the precise wording only prints when it was filled in</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / demand / evidence [1] / precise</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>{q33.band}</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>q33</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Has enquiry volume changed in the last 12 months?</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>grown | stayed flat | fallen | fallen sharply</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / demand / evidence [2] / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>{q35.band}</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>q35</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Are you doing anything right now to generate new enquiries?</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>consistently | on and off | nothing, it all comes to you</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / demand / evidence [3] / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>{q36.band}</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>q36</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>On a typical job or sale, what's left after the direct cost of deliver</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>On a typical job or sale, what's left after the direct cost of delivering it?</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>above 50% | in the 30 to 50% range | in the 15 to 30% range | under 15%</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / margin / evidence [1] / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>{q36.exact}</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>On a typical job or sale, what's left after the direct cost of delivering it?</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>the number they typed, in %</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>optional, so the precise wording only prints when it was filled in</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / margin / evidence [1] / precise</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>{q37.band}</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>q37</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>After everything, including paying yourself properly, what's left at t</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>After everything, including paying yourself properly, what's left at the end of a year?</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>above 20% | in the 10 to 20% range | in the 1 to 10% range | nothing, or a loss</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / margin / evidence [2] / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>{q37.exact}</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>After everything, including paying yourself properly, what's left at the end of a year?</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>the number they typed, in %</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>optional, so the precise wording only prints when it was filled in</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / margin / evidence [2] / precise</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>{q38.band}</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>q38</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>When did you last raise your prices?</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>inside the last six months | in the last year | one to two years ago | more than two years ago | never</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / margin / evidence [3] / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>{q39.band}</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>q39</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>How often does a job end up costing more to deliver than you quoted?</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>rarely | sometimes | often | on most jobs</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / margin / evidence [4] / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>{q41.band}</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>q41</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>What share of your revenue comes from your single biggest customer?</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>under 10% | between 10 and 20% | between 20 and 30% | between 30 and 50% | more than half</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>compound [15] / text  compound [17] / text  compound [4] / text  compound [5] / text  riskDef / key_client / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>{q41.exact}</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>What share of your revenue comes from your single biggest customer?</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>the number they typed, in %</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>optional, so the precise wording only prints when it was filled in</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>riskDef / key_client / precise</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>{q42.band}</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>q42</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>What share of revenue comes from your single biggest product or servic</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>What share of revenue comes from your single biggest product or service line?</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>under a quarter | a quarter to a half | half to three quarters | more than three quarters</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>riskDef / key_product / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>{q42.exact}</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>What share of revenue comes from your single biggest product or service line?</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>the number they typed, in %</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>optional, so the precise wording only prints when it was filled in</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>riskDef / key_product / precise</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>{q43.band}</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>q43</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>How spread out are the places your new customers come from?</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>spread across several channels | carried by two channels | almost entirely one channel</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>riskDef / key_channel / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>{q45.band}</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>q45</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>How is your work actually committed by the customer?</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>term contracts | job by job agreements | month to month | a handshake and an email</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>riskDef / no_contracts / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>{q46.band}</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>q46</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>How much of how the work gets done is written down well enough for som</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>How much of how the work gets done is written down well enough for someone new to follow?</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Most | Some | Almost none</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>riskDef / no_process / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>{q47.band}</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>q47</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>How often do you look at numbers that tell you how the business is tra</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>How often do you look at numbers that tell you how the business is travelling?</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>weekly | monthly | once a year at tax time | next to never</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>riskDef / no_data / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>{q49.band}</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>q49</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>If you sold the business tomorrow, how much of what the buyer is payin</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>If you sold the business tomorrow, how much of what the buyer is paying for is you personally?</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>almost none | some | most | all</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>riskDef / owner_trapped / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>{q50.band}</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>q50</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Is there a plan for what happens to the business if you stop, sell or </t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Is there a plan for what happens to the business if you stop, sell or step back?</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>a written plan | a rough idea | nothing</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>riskDef / no_succession / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>{q51.band}</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>q51</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Have you personally guaranteed any of the business's debt, leases or f</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Have you personally guaranteed any of the business's debt, leases or facilities?</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>none | a small amount | a significant amount</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>riskDef / personal_guarantee / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>{q52.band}</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>q52</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>How well does the way you spend your week match what you wanted out of</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr"/>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>How well does the way you spend your week match what you wanted out of this business?</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>close to what you signed up for | only partly a match for what you wanted | the opposite of what you wanted</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>clause is dropped on: Not sure</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>riskDef / model_misfit / banded</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>{d.primaryShort}</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr"/>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>derived, not a question</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>the primary constraint's short name, lower case</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>always resolves</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>looseBody  minorConstraint / cashflow  minorConstraint / demand  minorConstraint / fulfilment  minorConstraint / margin  minorConstraint / offer  minorConstraint / talent  minorConstraint / value  unsureBody</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>{d.unownedLayers}</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr"/>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>derived, not a question</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>a sentence naming which layers sit with the owner</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>always resolves</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>constraintDef / talent / open</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G36"/>
+  <autoFilter ref="A2:F47"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14669,13 +14958,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="92" customWidth="1" min="3" max="3"/>
-    <col width="78" customWidth="1" min="4" max="4"/>
+    <col width="82" customWidth="1" min="3" max="3"/>
+    <col width="68" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -14706,6 +14996,11 @@
           <t>Precise version, used only when they typed the figure</t>
         </is>
       </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Variables in this row</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -14724,6 +15019,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr"/>
+      <c r="E3" s="9" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -14742,6 +15038,7 @@
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="9" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -14760,6 +15057,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="9" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -14782,6 +15080,11 @@
           <t>money takes {q7.exact} days to arrive after the work is done</t>
         </is>
       </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>{q7.band}, {q7.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -14800,6 +15103,11 @@
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>{q6.band}</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -14818,6 +15126,11 @@
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>{q8.band}</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -14836,6 +15149,11 @@
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>{q9.band}</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -14854,6 +15172,7 @@
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -14872,6 +15191,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -14890,6 +15210,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -14908,6 +15229,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -14926,6 +15248,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -14944,6 +15267,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -14962,6 +15286,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -14980,6 +15305,7 @@
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr"/>
+      <c r="E17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -14998,6 +15324,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr"/>
+      <c r="E18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -15016,6 +15343,11 @@
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr"/>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>{d.unownedLayers}</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -15034,6 +15366,11 @@
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr"/>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>{q13.band}</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -15052,6 +15389,11 @@
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr"/>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>{q12.band}</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -15070,6 +15412,11 @@
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>{q14.band}</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -15088,6 +15435,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr"/>
+      <c r="E23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -15106,6 +15454,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr"/>
+      <c r="E24" s="9" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -15124,6 +15473,7 @@
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr"/>
+      <c r="E25" s="9" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -15142,6 +15492,7 @@
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr"/>
+      <c r="E26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -15160,6 +15511,7 @@
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr"/>
+      <c r="E27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -15178,6 +15530,7 @@
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr"/>
+      <c r="E28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -15196,6 +15549,7 @@
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr"/>
+      <c r="E29" s="9" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -15214,6 +15568,7 @@
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr"/>
+      <c r="E30" s="9" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -15232,6 +15587,7 @@
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr"/>
+      <c r="E31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -15250,6 +15606,7 @@
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr"/>
+      <c r="E32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -15272,6 +15629,11 @@
           <t>you're running at {q16.exact}% booked</t>
         </is>
       </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>{q16.band}, {q16.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -15290,6 +15652,11 @@
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr"/>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>{q17.band}</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -15308,6 +15675,11 @@
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr"/>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>{q18.band}</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -15326,6 +15698,11 @@
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr"/>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>{q19.band}</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -15344,6 +15721,7 @@
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr"/>
+      <c r="E37" s="9" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -15362,6 +15740,7 @@
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr"/>
+      <c r="E38" s="9" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -15380,6 +15759,7 @@
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr"/>
+      <c r="E39" s="9" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -15398,6 +15778,7 @@
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr"/>
+      <c r="E40" s="9" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -15416,6 +15797,7 @@
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr"/>
+      <c r="E41" s="9" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -15434,6 +15816,7 @@
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr"/>
+      <c r="E42" s="9" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -15452,6 +15835,7 @@
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr"/>
+      <c r="E43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -15470,6 +15854,7 @@
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr"/>
+      <c r="E44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -15488,6 +15873,7 @@
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr"/>
+      <c r="E45" s="9" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -15506,6 +15892,7 @@
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr"/>
+      <c r="E46" s="9" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -15528,6 +15915,11 @@
           <t>of the customers you had a year ago, {q21.exact}% still buy from you</t>
         </is>
       </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>{q21.band}, {q21.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -15546,6 +15938,11 @@
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr"/>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>{q22.band}</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -15564,6 +15961,11 @@
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr"/>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>{q23.band}</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -15582,6 +15984,7 @@
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr"/>
+      <c r="E50" s="9" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -15600,6 +16003,7 @@
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr"/>
+      <c r="E51" s="9" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -15618,6 +16022,7 @@
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr"/>
+      <c r="E52" s="9" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -15636,6 +16041,7 @@
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr"/>
+      <c r="E53" s="9" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -15654,6 +16060,7 @@
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr"/>
+      <c r="E54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -15672,6 +16079,7 @@
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr"/>
+      <c r="E55" s="9" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -15690,6 +16098,7 @@
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr"/>
+      <c r="E56" s="9" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -15708,6 +16117,7 @@
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr"/>
+      <c r="E57" s="9" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -15726,6 +16136,7 @@
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr"/>
+      <c r="E58" s="9" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -15744,6 +16155,7 @@
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr"/>
+      <c r="E59" s="9" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -15766,6 +16178,11 @@
           <t>your close rate sits at {q26.exact}%</t>
         </is>
       </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>{q26.band}, {q26.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
@@ -15784,6 +16201,11 @@
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr"/>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>{q27.band}</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -15802,6 +16224,11 @@
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr"/>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>{q28.band}</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -15820,6 +16247,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr"/>
+      <c r="E63" s="9" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
@@ -15838,6 +16266,7 @@
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr"/>
+      <c r="E64" s="9" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -15856,6 +16285,7 @@
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr"/>
+      <c r="E65" s="9" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -15874,6 +16304,7 @@
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr"/>
+      <c r="E66" s="9" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
@@ -15892,6 +16323,7 @@
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr"/>
+      <c r="E67" s="9" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -15910,6 +16342,7 @@
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr"/>
+      <c r="E68" s="9" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -15928,6 +16361,7 @@
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr"/>
+      <c r="E69" s="9" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -15946,6 +16380,7 @@
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr"/>
+      <c r="E70" s="9" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -15964,6 +16399,7 @@
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr"/>
+      <c r="E71" s="9" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -15982,6 +16418,7 @@
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr"/>
+      <c r="E72" s="9" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
@@ -16004,6 +16441,11 @@
           <t>enquiries run at about {q31.exact} a month</t>
         </is>
       </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>{q31.band}, {q31.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
@@ -16022,6 +16464,11 @@
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr"/>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>{q33.band}</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -16040,6 +16487,11 @@
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr"/>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>{q35.band}</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
@@ -16058,6 +16510,7 @@
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr"/>
+      <c r="E76" s="9" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -16076,6 +16529,7 @@
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr"/>
+      <c r="E77" s="9" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
@@ -16094,6 +16548,7 @@
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr"/>
+      <c r="E78" s="9" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
@@ -16112,6 +16567,7 @@
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr"/>
+      <c r="E79" s="9" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
@@ -16130,6 +16586,7 @@
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr"/>
+      <c r="E80" s="9" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
@@ -16148,6 +16605,7 @@
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr"/>
+      <c r="E81" s="9" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
@@ -16166,6 +16624,7 @@
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr"/>
+      <c r="E82" s="9" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
@@ -16184,6 +16643,7 @@
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr"/>
+      <c r="E83" s="9" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
@@ -16202,6 +16662,7 @@
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr"/>
+      <c r="E84" s="9" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
@@ -16220,6 +16681,7 @@
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr"/>
+      <c r="E85" s="9" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
@@ -16242,6 +16704,11 @@
           <t>what's left after direct costs sits at {q36.exact}%</t>
         </is>
       </c>
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t>{q36.band}, {q36.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
@@ -16264,6 +16731,11 @@
           <t>after everything it's {q37.exact}%</t>
         </is>
       </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>{q37.band}, {q37.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
@@ -16282,6 +16754,11 @@
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr"/>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>{q38.band}</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
@@ -16300,6 +16777,11 @@
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr"/>
+      <c r="E89" s="9" t="inlineStr">
+        <is>
+          <t>{q39.band}</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
@@ -16318,6 +16800,7 @@
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr"/>
+      <c r="E90" s="9" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
@@ -16336,6 +16819,7 @@
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr"/>
+      <c r="E91" s="9" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
@@ -16354,6 +16838,7 @@
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr"/>
+      <c r="E92" s="9" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
@@ -16372,6 +16857,7 @@
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr"/>
+      <c r="E93" s="9" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
@@ -16390,6 +16876,7 @@
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr"/>
+      <c r="E94" s="9" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
@@ -16408,6 +16895,7 @@
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr"/>
+      <c r="E95" s="9" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
@@ -16426,11 +16914,12 @@
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr"/>
+      <c r="E96" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D96"/>
+  <autoFilter ref="A2:E96"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16442,12 +16931,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="110" customWidth="1" min="3" max="3"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -16473,6 +16963,11 @@
           <t>The one line printed when this is a loud but downstream second finding</t>
         </is>
       </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Variables in this row</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -16490,6 +16985,11 @@
           <t>There's cash flow strain in your answers too. It sits downstream of the {d.primaryShort} problem and it should ease as that one moves.</t>
         </is>
       </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>{d.primaryShort}</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -16507,6 +17007,11 @@
           <t>A talent gap shows up in your answers as well. It's downstream of the {d.primaryShort} problem, so it isn't the thing to work on first.</t>
         </is>
       </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>{d.primaryShort}</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -16524,6 +17029,11 @@
           <t>You'll see fulfilment strain in here as well. That's downstream of the {d.primaryShort} problem, and it should settle once the layer above it is in place.</t>
         </is>
       </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>{d.primaryShort}</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -16541,6 +17051,11 @@
           <t>Retention looks soft too. That's downstream of the {d.primaryShort} problem rather than a separate finding.</t>
         </is>
       </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>{d.primaryShort}</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -16558,6 +17073,11 @@
           <t>The offer looks weak in places as well. Downstream of the {d.primaryShort} problem, and not worth touching yet.</t>
         </is>
       </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>{d.primaryShort}</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -16575,6 +17095,11 @@
           <t>Demand reads thin too. It's downstream of the {d.primaryShort} problem, so leave it where it is.</t>
         </is>
       </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>{d.primaryShort}</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -16592,11 +17117,16 @@
           <t>Margin looks tight as well. That's downstream of the {d.primaryShort} problem and it'll move when that does.</t>
         </is>
       </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>{d.primaryShort}</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C9"/>
+  <autoFilter ref="A2:D9"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16608,16 +17138,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="78" customWidth="1" min="4" max="4"/>
-    <col width="62" customWidth="1" min="5" max="5"/>
-    <col width="78" customWidth="1" min="6" max="6"/>
-    <col width="72" customWidth="1" min="7" max="7"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="5" max="5"/>
+    <col width="72" customWidth="1" min="6" max="6"/>
+    <col width="66" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -16663,6 +17194,11 @@
           <t>What to do</t>
         </is>
       </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>Variables in this row</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -16696,6 +17232,11 @@
           <t>Set a ceiling, say twenty percent of revenue from any one customer, and treat crossing it as the trigger to go and win two more. Get them onto a term agreement in the meantime.</t>
         </is>
       </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>{q41.band}, {q41.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -16727,6 +17268,11 @@
       <c r="G4" s="7" t="inlineStr">
         <is>
           <t>Build a second line and sell it to the customers you already have. It's cheaper than finding new customers for the line you've got.</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>{q42.band}, {q42.exact}</t>
         </is>
       </c>
     </row>
@@ -16758,6 +17304,11 @@
           <t>Stand up a second channel before you need it, and give it ninety days before you judge it. One channel is a decision somebody else gets to make on your behalf.</t>
         </is>
       </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>{q43.band}</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -16787,6 +17338,7 @@
           <t>Qualify a second supplier and give them ten percent of your volume. A backup you've never actually bought from isn't a backup.</t>
         </is>
       </c>
+      <c r="H6" s="9" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -16816,6 +17368,7 @@
           <t>Write down what they hold, then move one piece of it to somebody else this month. Repeat until nothing sits in one head.</t>
         </is>
       </c>
+      <c r="H7" s="9" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -16845,6 +17398,7 @@
           <t>Have them document the work while they're still here, and pay them properly to do it. It's the cheapest insurance available to you.</t>
         </is>
       </c>
+      <c r="H8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -16874,6 +17428,7 @@
           <t>Take one thing you do well and sell it somewhere else, even at a small scale. Proving it travels is the whole exercise.</t>
         </is>
       </c>
+      <c r="H9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -16907,6 +17462,11 @@
           <t>Build to one month of fixed costs in a separate account, then three. Move a fixed percentage of every payment that comes in, automatically, so it isn't a decision you make each time.</t>
         </is>
       </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>{q8.band}</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -16940,6 +17500,11 @@
           <t>Put a written agreement behind every piece of work, with terms, scope and a notice period. Start with your largest customers.</t>
         </is>
       </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>{q45.band}</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -16973,6 +17538,11 @@
           <t>Record yourself doing the five things that go wrong most often, then turn each one into a one page checklist. Checklists beat manuals, because people actually use them.</t>
         </is>
       </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>{q46.band}</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -17004,6 +17574,11 @@
       <c r="G13" s="7" t="inlineStr">
         <is>
           <t>Pick five numbers and look at them weekly. Cash in the bank, enquiries, close rate, jobs delivered, and margin on the last ten jobs. One page, same day every week.</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>{q47.band}</t>
         </is>
       </c>
     </row>
@@ -17035,6 +17610,7 @@
           <t>Name the person, tell them, and start handing over one area at a time with the decisions attached. A deputy who can't decide anything is a job title.</t>
         </is>
       </c>
+      <c r="H14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -17068,6 +17644,11 @@
           <t>Work out what only you can do and start moving everything else. The test is whether the business survives you taking a month off, so book the month and find out.</t>
         </is>
       </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>{q49.band}</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -17101,6 +17682,11 @@
           <t>Write the one page version. Who runs it, what happens to the customers, what it's worth and who'd buy it. It doesn't need to be right, it needs to exist.</t>
         </is>
       </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>{q50.band}</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -17134,6 +17720,11 @@
           <t>List every guarantee you've signed and put a date against each one to renegotiate or release it. Most get renewed on autopilot because nobody asks.</t>
         </is>
       </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>{q51.band}</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -17167,11 +17758,16 @@
           <t>Write down what you actually wanted out of this, then hold your week up against it. The gap is the brief for the next twelve months.</t>
         </is>
       </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>{q52.band}</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G18"/>
+  <autoFilter ref="A2:H18"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17342,13 +17938,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="122" customWidth="1" min="4" max="4"/>
+    <col width="112" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -17379,6 +17976,11 @@
           <t>Block. Prints when both are present</t>
         </is>
       </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Variables in this row</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -17399,6 +18001,11 @@
           <t>Cash flow is your constraint and one customer carries {q41.band} of your revenue. That customer is also setting your payment terms, which means they're setting your cash position. Fixing terms with them is worth more than everything else on the list.</t>
         </is>
       </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>{q41.band}</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -17419,6 +18026,7 @@
           <t>You're cash constrained and personally guaranteeing the business's obligations. That's the combination that follows people home. Get the buffer built before you take on another dollar of guaranteed debt.</t>
         </is>
       </c>
+      <c r="E4" s="9" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -17439,6 +18047,7 @@
           <t>Cash flow is your constraint and your work isn't contracted. You're funding jobs upfront for customers who can walk without penalty. Deposits and written terms deal with both at once.</t>
         </is>
       </c>
+      <c r="E5" s="9" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -17459,6 +18068,7 @@
           <t>You're cash constrained and you're not looking at the numbers often enough to see it coming. A thirteen week cash forecast, updated weekly, is the highest value hour in your month right now.</t>
         </is>
       </c>
+      <c r="E6" s="9" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -17479,6 +18089,7 @@
           <t>You're demand constrained and the one channel you have isn't producing. A second channel is the fix and it's also the risk mitigation. Same move, two problems.</t>
         </is>
       </c>
+      <c r="E7" s="9" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -17499,6 +18110,11 @@
           <t>You're quiet and one customer carries {q41.band} of your revenue. Together those mean the business is one phone call from a crisis. New demand is urgent here for reasons that have nothing to do with growth.</t>
         </is>
       </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>{q41.band}</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -17519,6 +18135,7 @@
           <t>You're fulfilment constrained and almost nothing is written down. Those aren't two findings. Undocumented work is slow work, and it's why adding people hasn't given you the output you expected.</t>
         </is>
       </c>
+      <c r="E9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -17539,6 +18156,7 @@
           <t>You're at capacity and one person holds how the work actually gets done. Every hire you make is rate limited by the one person who has to train them. Getting that knowledge out of one head is what unlocks the capacity.</t>
         </is>
       </c>
+      <c r="E10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -17559,6 +18177,7 @@
           <t>You're at capacity and the business depends on one person to function. Adding work to that arrangement adds it to them. The capacity you're missing is currently locked in one diary.</t>
         </is>
       </c>
+      <c r="E11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -17579,6 +18198,7 @@
           <t>Margin is your constraint and you don't know which work makes money. You're almost certainly subsidising some customers with others, and until you can see which, every pricing decision you make is a guess.</t>
         </is>
       </c>
+      <c r="E12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -17599,6 +18219,11 @@
           <t>Margin is tight and one customer carries {q41.band} of your revenue. Big customers get big customer pricing, and yours is probably the one holding the margin down. Repricing them is the fastest lever you have, and it's the scariest, which is why it hasn't happened.</t>
         </is>
       </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>{q41.band}</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -17619,6 +18244,7 @@
           <t>The offer is your constraint and nearly all your enquiries come through one channel. That's why this feels like a demand problem. The channel is working. The thing it's delivering people to isn't.</t>
         </is>
       </c>
+      <c r="E14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -17639,6 +18265,7 @@
           <t>Your constraint is talent and your key person risk is the same thing seen from the other side. The layer that doesn't exist is the reason everything routes through one person, so hiring the role deals with both. Treat it as one job rather than two.</t>
         </is>
       </c>
+      <c r="E15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -17659,6 +18286,7 @@
           <t>You're talent constrained and the business is close to unsellable, and both of those come from the same fact. The business runs on you. The role you haven't hired is also the thing standing between you and owning something a buyer would want.</t>
         </is>
       </c>
+      <c r="E16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -17679,6 +18307,7 @@
           <t>The missing layer and the missing second in command are one problem with two names. You don't need a succession plan and a hire. You need the hire, and the succession plan writes itself afterwards.</t>
         </is>
       </c>
+      <c r="E17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -17699,6 +18328,11 @@
           <t>You're carrying a talent gap and a single customer worth {q41.band} of revenue. Building the layer while one customer can end your year is the sequencing error we'd flag hardest. Get that customer onto a term agreement before you take on the salary.</t>
         </is>
       </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>{q41.band}</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -17719,11 +18353,12 @@
           <t>Retention is your constraint and you don't know why customers leave. Those are the same sentence. Ten phone calls this week would find the leak, and nothing you do before those calls is anything but a guess.</t>
         </is>
       </c>
+      <c r="E19" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D19"/>
+  <autoFilter ref="A2:E19"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/diagnostic/Business-Diagnostic-Spec.xlsx
+++ b/diagnostic/Business-Diagnostic-Spec.xlsx
@@ -25,7 +25,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Questions'!$A$2:$J$60</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Answer options'!$A$2:$I$306</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Answer options'!$A$2:$I$305</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Constraints and order'!$A$2:$G$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Report, constraint'!$A$2:$E$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Report, minor'!$A$2:$D$9</definedName>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>never | once or twice | most months | every month</t>
+          <t>you haven't had to delay paying anyone | you've delayed paying someone once or twice | you've been delaying payments most months | you've been delaying payments every month</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>upfront or on the day | inside a fortnight | in the 15 to 30 day range | in the 31 to 60 day range | beyond 60 days</t>
+          <t>straight away | inside a fortnight | in the 15 to 30 day range | in the 31 to 60 day range | beyond 60 days</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>never | once | a few times | as a matter of routine</t>
+          <t>nothing you wanted to grow has stalled for want of someone to hand it to | something you wanted to grow has stalled once for want of anyone to hand it to | a few things have stalled for want of anyone to hand them to | things stall for want of anyone to hand them to as a matter of routine</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>never | once or twice | most months | constantly</t>
+          <t>you haven't had to turn work away | you've turned work away or pushed a start date once or twice | you're turning work away or pushing start dates most months | you're turning work away constantly</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>above 70% | around half | under a third | close to none | one off by design</t>
+          <t>above 70% | around half | under a third | close to none</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>most of them | about half | a few | almost none</t>
+          <t>most | about half | a few | almost none</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>price | timing | a competitor | inaction | unknown</t>
+          <t>price | timing | a competitor | inaction | something you can't put your finger on</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>consistently | on and off | nothing, it all comes to you</t>
+          <t>you're generating enquiries consistently | you're generating enquiries on and off | you're doing nothing to generate enquiries, it all comes to you</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>inside the last six months | in the last year | one to two years ago | more than two years ago | never</t>
+          <t>you last raised prices inside the last six months | you last raised prices in the last year | you last raised prices one to two years ago | you last raised prices more than two years ago | you've never raised your prices</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>spread across several channels | carried by two channels | almost entirely one channel</t>
+          <t>spread across several channels | through two channels | almost entirely through one channel</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>term contracts | job by job agreements | month to month | a handshake and an email</t>
+          <t>term contracts | job by job agreements | a month to month arrangement | a handshake and an email</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>not at all | a few weeks | the best part of a year | years</t>
+          <t>a buyer wouldn't need you at all | a buyer would need you for a few weeks of handover | a buyer would need you for the best part of a year | a buyer would need you for years, if it works without you at all</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -6287,7 +6287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I306"/>
+  <dimension ref="A1:I305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>you haven't had to delay paying anyone</t>
         </is>
       </c>
       <c r="G41" s="5" t="n">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>once or twice</t>
+          <t>you've delayed paying someone once or twice</t>
         </is>
       </c>
       <c r="G42" s="5" t="n">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>most months</t>
+          <t>you've been delaying payments most months</t>
         </is>
       </c>
       <c r="G43" s="5" t="n">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>every month</t>
+          <t>you've been delaying payments every month</t>
         </is>
       </c>
       <c r="G44" s="5" t="n">
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>Paid upfront or on the day</t>
+          <t>Straight away, we're paid before we'd invoice</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>upfront or on the day</t>
+          <t>straight away</t>
         </is>
       </c>
       <c r="G46" s="5" t="n">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>nothing you wanted to grow has stalled for want of someone to hand it to</t>
         </is>
       </c>
       <c r="G96" s="5" t="n">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>once</t>
+          <t>something you wanted to grow has stalled once for want of anyone to hand it to</t>
         </is>
       </c>
       <c r="G97" s="5" t="n">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>a few times</t>
+          <t>a few things have stalled for want of anyone to hand them to</t>
         </is>
       </c>
       <c r="G98" s="5" t="n">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>as a matter of routine</t>
+          <t>things stall for want of anyone to hand them to as a matter of routine</t>
         </is>
       </c>
       <c r="G99" s="5" t="n">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>you haven't had to turn work away</t>
         </is>
       </c>
       <c r="G113" s="5" t="n">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>once or twice</t>
+          <t>you've turned work away or pushed a start date once or twice</t>
         </is>
       </c>
       <c r="G114" s="5" t="n">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>most months</t>
+          <t>you're turning work away or pushing start dates most months</t>
         </is>
       </c>
       <c r="G115" s="5" t="n">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>constantly</t>
+          <t>you're turning work away constantly</t>
         </is>
       </c>
       <c r="G116" s="5" t="n">
@@ -10937,63 +10937,59 @@
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E137" s="7" t="inlineStr">
         <is>
-          <t>We're one off by nature, they don't come back</t>
-        </is>
-      </c>
-      <c r="F137" s="7" t="inlineStr">
-        <is>
-          <t>one off by design</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F137" s="7" t="inlineStr"/>
       <c r="G137" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H137" s="3" t="inlineStr"/>
       <c r="I137" s="3" t="inlineStr">
         <is>
-          <t>Shifts the value block onto referral</t>
+          <t>Not sure, scores nothing and feeds data blindness</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>q21</t>
+          <t>q57</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Of the customers who bought from you a year ago, roughly h...</t>
+          <t>Of the work your existing customers put out, how much of i...</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E138" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F138" s="7" t="inlineStr"/>
+          <t>Nearly all of it</t>
+        </is>
+      </c>
+      <c r="F138" s="7" t="inlineStr">
+        <is>
+          <t>nearly all</t>
+        </is>
+      </c>
       <c r="G138" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H138" s="3" t="inlineStr"/>
-      <c r="I138" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="I138" s="3" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
@@ -11011,21 +11007,21 @@
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
-          <t>Nearly all of it</t>
+          <t>More than half</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>nearly all</t>
+          <t>more than half</t>
         </is>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H139" s="3" t="inlineStr"/>
       <c r="I139" s="3" t="inlineStr"/>
@@ -11046,21 +11042,21 @@
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E140" s="7" t="inlineStr">
         <is>
-          <t>More than half</t>
+          <t>About half</t>
         </is>
       </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>more than half</t>
+          <t>about half</t>
         </is>
       </c>
       <c r="G140" s="5" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="H140" s="3" t="inlineStr"/>
       <c r="I140" s="3" t="inlineStr"/>
@@ -11081,21 +11077,21 @@
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>About half</t>
+          <t>Less than half</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>about half</t>
+          <t>less than half</t>
         </is>
       </c>
       <c r="G141" s="5" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="H141" s="3" t="inlineStr"/>
       <c r="I141" s="3" t="inlineStr"/>
@@ -11116,21 +11112,21 @@
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E142" s="7" t="inlineStr">
         <is>
-          <t>Less than half</t>
+          <t>A small slice, they spread it around</t>
         </is>
       </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>less than half</t>
+          <t>only a small slice</t>
         </is>
       </c>
       <c r="G142" s="5" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="H142" s="3" t="inlineStr"/>
       <c r="I142" s="3" t="inlineStr"/>
@@ -11151,63 +11147,63 @@
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E143" s="7" t="inlineStr">
         <is>
-          <t>A small slice, they spread it around</t>
-        </is>
-      </c>
-      <c r="F143" s="7" t="inlineStr">
-        <is>
-          <t>only a small slice</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F143" s="7" t="inlineStr"/>
       <c r="G143" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H143" s="3" t="inlineStr"/>
-      <c r="I143" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>no_data (70)</t>
+        </is>
+      </c>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>q57</t>
+          <t>q22</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Of the work your existing customers put out, how much of i...</t>
+          <t>How often do customers come back and buy again without you...</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E144" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F144" s="7" t="inlineStr"/>
+          <t>Usually</t>
+        </is>
+      </c>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
+          <t>usually</t>
+        </is>
+      </c>
       <c r="G144" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H144" s="3" t="inlineStr">
-        <is>
-          <t>no_data (70)</t>
-        </is>
-      </c>
-      <c r="I144" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="H144" s="3" t="inlineStr"/>
+      <c r="I144" s="3" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n">
@@ -11225,21 +11221,21 @@
       </c>
       <c r="D145" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E145" s="7" t="inlineStr">
         <is>
-          <t>Usually</t>
+          <t>Sometimes</t>
         </is>
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>usually</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H145" s="3" t="inlineStr"/>
       <c r="I145" s="3" t="inlineStr"/>
@@ -11260,21 +11256,21 @@
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E146" s="7" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Rarely</t>
         </is>
       </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="G146" s="5" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="H146" s="3" t="inlineStr"/>
       <c r="I146" s="3" t="inlineStr"/>
@@ -11295,21 +11291,21 @@
       </c>
       <c r="D147" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E147" s="7" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Never</t>
         </is>
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>never</t>
         </is>
       </c>
       <c r="G147" s="5" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="H147" s="3" t="inlineStr"/>
       <c r="I147" s="3" t="inlineStr"/>
@@ -11330,59 +11326,59 @@
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E148" s="7" t="inlineStr">
         <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="F148" s="7" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F148" s="7" t="inlineStr"/>
       <c r="G148" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H148" s="3" t="inlineStr"/>
-      <c r="I148" s="3" t="inlineStr"/>
+      <c r="I148" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>q22</t>
+          <t>q23</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>How often do customers come back and buy again without you...</t>
+          <t>How many of your new customers arrive through a referral f...</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E149" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F149" s="7" t="inlineStr"/>
+          <t>Most of them</t>
+        </is>
+      </c>
+      <c r="F149" s="7" t="inlineStr">
+        <is>
+          <t>most</t>
+        </is>
+      </c>
       <c r="G149" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H149" s="3" t="inlineStr"/>
-      <c r="I149" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="I149" s="3" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="5" t="n">
@@ -11400,21 +11396,21 @@
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E150" s="7" t="inlineStr">
         <is>
-          <t>Most of them</t>
+          <t>About half</t>
         </is>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>most of them</t>
+          <t>about half</t>
         </is>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H150" s="3" t="inlineStr"/>
       <c r="I150" s="3" t="inlineStr"/>
@@ -11435,21 +11431,21 @@
       </c>
       <c r="D151" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E151" s="7" t="inlineStr">
         <is>
-          <t>About half</t>
+          <t>A few</t>
         </is>
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
-          <t>about half</t>
+          <t>a few</t>
         </is>
       </c>
       <c r="G151" s="5" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="H151" s="3" t="inlineStr"/>
       <c r="I151" s="3" t="inlineStr"/>
@@ -11470,21 +11466,21 @@
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr">
         <is>
-          <t>A few</t>
+          <t>Almost none</t>
         </is>
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>a few</t>
+          <t>almost none</t>
         </is>
       </c>
       <c r="G152" s="5" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H152" s="3" t="inlineStr"/>
       <c r="I152" s="3" t="inlineStr"/>
@@ -11505,59 +11501,59 @@
       </c>
       <c r="D153" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr">
         <is>
-          <t>Almost none</t>
-        </is>
-      </c>
-      <c r="F153" s="7" t="inlineStr">
-        <is>
-          <t>almost none</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F153" s="7" t="inlineStr"/>
       <c r="G153" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H153" s="3" t="inlineStr"/>
-      <c r="I153" s="3" t="inlineStr"/>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>q23</t>
+          <t>q24</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>How many of your new customers arrive through a referral f...</t>
+          <t>In the last 12 months, how many customers have moved some ...</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F154" s="7" t="inlineStr"/>
+          <t>Almost none</t>
+        </is>
+      </c>
+      <c r="F154" s="7" t="inlineStr">
+        <is>
+          <t>almost none</t>
+        </is>
+      </c>
       <c r="G154" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H154" s="3" t="inlineStr"/>
-      <c r="I154" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="I154" s="3" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
@@ -11575,21 +11571,21 @@
       </c>
       <c r="D155" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E155" s="7" t="inlineStr">
         <is>
-          <t>Almost none</t>
+          <t>A handful</t>
         </is>
       </c>
       <c r="F155" s="7" t="inlineStr">
         <is>
-          <t>almost none</t>
+          <t>a handful</t>
         </is>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H155" s="3" t="inlineStr"/>
       <c r="I155" s="3" t="inlineStr"/>
@@ -11610,21 +11606,21 @@
       </c>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr">
         <is>
-          <t>A handful</t>
+          <t>A steady stream</t>
         </is>
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>a handful</t>
+          <t>a steady stream</t>
         </is>
       </c>
       <c r="G156" s="5" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="H156" s="3" t="inlineStr"/>
       <c r="I156" s="3" t="inlineStr"/>
@@ -11645,21 +11641,21 @@
       </c>
       <c r="D157" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E157" s="7" t="inlineStr">
         <is>
-          <t>A steady stream</t>
+          <t>Most of them</t>
         </is>
       </c>
       <c r="F157" s="7" t="inlineStr">
         <is>
-          <t>a steady stream</t>
+          <t>most of them</t>
         </is>
       </c>
       <c r="G157" s="5" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="H157" s="3" t="inlineStr"/>
       <c r="I157" s="3" t="inlineStr"/>
@@ -11680,59 +11676,59 @@
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E158" s="7" t="inlineStr">
         <is>
-          <t>Most of them</t>
-        </is>
-      </c>
-      <c r="F158" s="7" t="inlineStr">
-        <is>
-          <t>most of them</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F158" s="7" t="inlineStr"/>
       <c r="G158" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H158" s="3" t="inlineStr"/>
-      <c r="I158" s="3" t="inlineStr"/>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>q24</t>
+          <t>q25</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>In the last 12 months, how many customers have moved some ...</t>
+          <t>Do you know why customers stop buying, or go to a competit...</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E159" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F159" s="7" t="inlineStr"/>
+          <t>Yes, we ask them and we know</t>
+        </is>
+      </c>
+      <c r="F159" s="7" t="inlineStr">
+        <is>
+          <t>you ask them and you know</t>
+        </is>
+      </c>
       <c r="G159" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H159" s="3" t="inlineStr"/>
-      <c r="I159" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="I159" s="3" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="5" t="n">
@@ -11750,21 +11746,21 @@
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E160" s="7" t="inlineStr">
         <is>
-          <t>Yes, we ask them and we know</t>
+          <t>We have a theory</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr">
         <is>
-          <t>you ask them and you know</t>
+          <t>you have a theory</t>
         </is>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H160" s="3" t="inlineStr"/>
       <c r="I160" s="3" t="inlineStr"/>
@@ -11785,23 +11781,27 @@
       </c>
       <c r="D161" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E161" s="7" t="inlineStr">
         <is>
-          <t>We have a theory</t>
+          <t>No idea</t>
         </is>
       </c>
       <c r="F161" s="7" t="inlineStr">
         <is>
-          <t>you have a theory</t>
+          <t>no idea</t>
         </is>
       </c>
       <c r="G161" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="H161" s="3" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>no_data</t>
+        </is>
+      </c>
       <c r="I161" s="3" t="inlineStr"/>
     </row>
     <row r="162">
@@ -11820,67 +11820,63 @@
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E162" s="7" t="inlineStr">
         <is>
-          <t>No idea</t>
-        </is>
-      </c>
-      <c r="F162" s="7" t="inlineStr">
-        <is>
-          <t>no idea</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F162" s="7" t="inlineStr"/>
       <c r="G162" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
           <t>no_data</t>
         </is>
       </c>
-      <c r="I162" s="3" t="inlineStr"/>
+      <c r="I162" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>q25</t>
+          <t>q26</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>Do you know why customers stop buying, or go to a competit...</t>
+          <t>Of the people who enquire and get a quote or a proposal, h...</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E163" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F163" s="7" t="inlineStr"/>
+          <t>More than half</t>
+        </is>
+      </c>
+      <c r="F163" s="7" t="inlineStr">
+        <is>
+          <t>above 50%</t>
+        </is>
+      </c>
       <c r="G163" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H163" s="3" t="inlineStr">
-        <is>
-          <t>no_data</t>
-        </is>
-      </c>
-      <c r="I163" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="H163" s="3" t="inlineStr"/>
+      <c r="I163" s="3" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="5" t="n">
@@ -11898,21 +11894,21 @@
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E164" s="7" t="inlineStr">
         <is>
-          <t>More than half</t>
+          <t>25% to 50%</t>
         </is>
       </c>
       <c r="F164" s="7" t="inlineStr">
         <is>
-          <t>above 50%</t>
+          <t>in the 25 to 50% range</t>
         </is>
       </c>
       <c r="G164" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H164" s="3" t="inlineStr"/>
       <c r="I164" s="3" t="inlineStr"/>
@@ -11933,21 +11929,21 @@
       </c>
       <c r="D165" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E165" s="7" t="inlineStr">
         <is>
-          <t>25% to 50%</t>
+          <t>10% to 25%</t>
         </is>
       </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
-          <t>in the 25 to 50% range</t>
+          <t>in the 10 to 25% range</t>
         </is>
       </c>
       <c r="G165" s="5" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="H165" s="3" t="inlineStr"/>
       <c r="I165" s="3" t="inlineStr"/>
@@ -11968,21 +11964,21 @@
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E166" s="7" t="inlineStr">
         <is>
-          <t>10% to 25%</t>
+          <t>Under 10%</t>
         </is>
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>in the 10 to 25% range</t>
+          <t>under 10%</t>
         </is>
       </c>
       <c r="G166" s="5" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H166" s="3" t="inlineStr"/>
       <c r="I166" s="3" t="inlineStr"/>
@@ -12003,63 +11999,63 @@
       </c>
       <c r="D167" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E167" s="7" t="inlineStr">
         <is>
-          <t>Under 10%</t>
-        </is>
-      </c>
-      <c r="F167" s="7" t="inlineStr">
-        <is>
-          <t>under 10%</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F167" s="7" t="inlineStr"/>
       <c r="G167" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H167" s="3" t="inlineStr"/>
-      <c r="I167" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>no_data</t>
+        </is>
+      </c>
+      <c r="I167" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>q26</t>
+          <t>q27</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Of the people who enquire and get a quote or a proposal, h...</t>
+          <t>When you lose a deal, what's the most common reason?</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E168" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F168" s="7" t="inlineStr"/>
+          <t>Price, we were too expensive</t>
+        </is>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
       <c r="G168" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H168" s="3" t="inlineStr">
-        <is>
-          <t>no_data</t>
-        </is>
-      </c>
-      <c r="I168" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="H168" s="3" t="inlineStr"/>
+      <c r="I168" s="3" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
@@ -12077,21 +12073,21 @@
       </c>
       <c r="D169" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E169" s="7" t="inlineStr">
         <is>
-          <t>Price, we were too expensive</t>
+          <t>Timing, they weren't ready</t>
         </is>
       </c>
       <c r="F169" s="7" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="G169" s="5" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H169" s="3" t="inlineStr"/>
       <c r="I169" s="3" t="inlineStr"/>
@@ -12112,21 +12108,21 @@
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E170" s="7" t="inlineStr">
         <is>
-          <t>Timing, they weren't ready</t>
+          <t>They went with someone else</t>
         </is>
       </c>
       <c r="F170" s="7" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>a competitor</t>
         </is>
       </c>
       <c r="G170" s="5" t="n">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="H170" s="3" t="inlineStr"/>
       <c r="I170" s="3" t="inlineStr"/>
@@ -12147,21 +12143,21 @@
       </c>
       <c r="D171" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E171" s="7" t="inlineStr">
         <is>
-          <t>They went with someone else</t>
+          <t>They did nothing at all</t>
         </is>
       </c>
       <c r="F171" s="7" t="inlineStr">
         <is>
-          <t>a competitor</t>
+          <t>inaction</t>
         </is>
       </c>
       <c r="G171" s="5" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="H171" s="3" t="inlineStr"/>
       <c r="I171" s="3" t="inlineStr"/>
@@ -12182,23 +12178,27 @@
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E172" s="7" t="inlineStr">
         <is>
-          <t>They did nothing at all</t>
+          <t>We don't know</t>
         </is>
       </c>
       <c r="F172" s="7" t="inlineStr">
         <is>
-          <t>inaction</t>
+          <t>something you can't put your finger on</t>
         </is>
       </c>
       <c r="G172" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H172" s="3" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>no_data</t>
+        </is>
+      </c>
       <c r="I172" s="3" t="inlineStr"/>
     </row>
     <row r="173">
@@ -12217,67 +12217,63 @@
       </c>
       <c r="D173" s="6" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E173" s="7" t="inlineStr">
         <is>
-          <t>We don't know</t>
-        </is>
-      </c>
-      <c r="F173" s="7" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F173" s="7" t="inlineStr"/>
       <c r="G173" s="5" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
           <t>no_data</t>
         </is>
       </c>
-      <c r="I173" s="3" t="inlineStr"/>
+      <c r="I173" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>q27</t>
+          <t>q28</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>When you lose a deal, what's the most common reason?</t>
+          <t>When a prospect gets your quote, how often do they come ba...</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E174" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F174" s="7" t="inlineStr"/>
+          <t>Rarely, they just decide</t>
+        </is>
+      </c>
+      <c r="F174" s="7" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
       <c r="G174" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H174" s="3" t="inlineStr">
-        <is>
-          <t>no_data</t>
-        </is>
-      </c>
-      <c r="I174" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="H174" s="3" t="inlineStr"/>
+      <c r="I174" s="3" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="5" t="n">
@@ -12295,21 +12291,21 @@
       </c>
       <c r="D175" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E175" s="7" t="inlineStr">
         <is>
-          <t>Rarely, they just decide</t>
+          <t>Sometimes</t>
         </is>
       </c>
       <c r="F175" s="7" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="G175" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H175" s="3" t="inlineStr"/>
       <c r="I175" s="3" t="inlineStr"/>
@@ -12330,21 +12326,21 @@
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E176" s="7" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Often</t>
         </is>
       </c>
       <c r="F176" s="7" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>often</t>
         </is>
       </c>
       <c r="G176" s="5" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="H176" s="3" t="inlineStr"/>
       <c r="I176" s="3" t="inlineStr"/>
@@ -12365,21 +12361,21 @@
       </c>
       <c r="D177" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E177" s="7" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>On most quotes</t>
         </is>
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>often</t>
+          <t>on most quotes</t>
         </is>
       </c>
       <c r="G177" s="5" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="H177" s="3" t="inlineStr"/>
       <c r="I177" s="3" t="inlineStr"/>
@@ -12400,59 +12396,59 @@
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E178" s="7" t="inlineStr">
         <is>
-          <t>On most quotes</t>
-        </is>
-      </c>
-      <c r="F178" s="7" t="inlineStr">
-        <is>
-          <t>on most quotes</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F178" s="7" t="inlineStr"/>
       <c r="G178" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H178" s="3" t="inlineStr"/>
-      <c r="I178" s="3" t="inlineStr"/>
+      <c r="I178" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>q28</t>
+          <t>q29</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>When a prospect gets your quote, how often do they come ba...</t>
+          <t>Has the proportion of quotes that turn into work changed i...</t>
         </is>
       </c>
       <c r="D179" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E179" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F179" s="7" t="inlineStr"/>
+          <t>Improved</t>
+        </is>
+      </c>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
+          <t>improved</t>
+        </is>
+      </c>
       <c r="G179" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H179" s="3" t="inlineStr"/>
-      <c r="I179" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="I179" s="3" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="5" t="n">
@@ -12470,21 +12466,21 @@
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E180" s="7" t="inlineStr">
         <is>
-          <t>Improved</t>
+          <t>About the same</t>
         </is>
       </c>
       <c r="F180" s="7" t="inlineStr">
         <is>
-          <t>improved</t>
+          <t>held steady</t>
         </is>
       </c>
       <c r="G180" s="5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H180" s="3" t="inlineStr"/>
       <c r="I180" s="3" t="inlineStr"/>
@@ -12505,21 +12501,21 @@
       </c>
       <c r="D181" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E181" s="7" t="inlineStr">
         <is>
-          <t>About the same</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="F181" s="7" t="inlineStr">
         <is>
-          <t>held steady</t>
+          <t>dropped</t>
         </is>
       </c>
       <c r="G181" s="5" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="H181" s="3" t="inlineStr"/>
       <c r="I181" s="3" t="inlineStr"/>
@@ -12540,21 +12536,21 @@
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E182" s="7" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Dropped sharply</t>
         </is>
       </c>
       <c r="F182" s="7" t="inlineStr">
         <is>
-          <t>dropped</t>
+          <t>fallen off a cliff</t>
         </is>
       </c>
       <c r="G182" s="5" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H182" s="3" t="inlineStr"/>
       <c r="I182" s="3" t="inlineStr"/>
@@ -12575,63 +12571,63 @@
       </c>
       <c r="D183" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E183" s="7" t="inlineStr">
         <is>
-          <t>Dropped sharply</t>
-        </is>
-      </c>
-      <c r="F183" s="7" t="inlineStr">
-        <is>
-          <t>fallen off a cliff</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F183" s="7" t="inlineStr"/>
       <c r="G183" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H183" s="3" t="inlineStr"/>
-      <c r="I183" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H183" s="3" t="inlineStr">
+        <is>
+          <t>no_data</t>
+        </is>
+      </c>
+      <c r="I183" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>q29</t>
+          <t>q30</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>Has the proportion of quotes that turn into work changed i...</t>
+          <t>How does a prospect find out what you charge?</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E184" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F184" s="7" t="inlineStr"/>
+          <t>There's a price list or packages they can see themselves</t>
+        </is>
+      </c>
+      <c r="F184" s="7" t="inlineStr">
+        <is>
+          <t>from a price list they can see themselves</t>
+        </is>
+      </c>
       <c r="G184" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H184" s="3" t="inlineStr">
-        <is>
-          <t>no_data</t>
-        </is>
-      </c>
-      <c r="I184" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="H184" s="3" t="inlineStr"/>
+      <c r="I184" s="3" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="5" t="n">
@@ -12649,21 +12645,21 @@
       </c>
       <c r="D185" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E185" s="7" t="inlineStr">
         <is>
-          <t>There's a price list or packages they can see themselves</t>
+          <t>Standard pricing, but we walk them through it</t>
         </is>
       </c>
       <c r="F185" s="7" t="inlineStr">
         <is>
-          <t>from a price list they can see themselves</t>
+          <t>from standard pricing you walk them through</t>
         </is>
       </c>
       <c r="G185" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H185" s="3" t="inlineStr"/>
       <c r="I185" s="3" t="inlineStr"/>
@@ -12684,21 +12680,21 @@
       </c>
       <c r="D186" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E186" s="7" t="inlineStr">
         <is>
-          <t>Standard pricing, but we walk them through it</t>
+          <t>Every job gets quoted from scratch</t>
         </is>
       </c>
       <c r="F186" s="7" t="inlineStr">
         <is>
-          <t>from standard pricing you walk them through</t>
+          <t>from a quote built from scratch every time</t>
         </is>
       </c>
       <c r="G186" s="5" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="H186" s="3" t="inlineStr"/>
       <c r="I186" s="3" t="inlineStr"/>
@@ -12719,21 +12715,21 @@
       </c>
       <c r="D187" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E187" s="7" t="inlineStr">
         <is>
-          <t>Every job gets quoted from scratch</t>
+          <t>It depends who's asking</t>
         </is>
       </c>
       <c r="F187" s="7" t="inlineStr">
         <is>
-          <t>from a quote built from scratch every time</t>
+          <t>from a number that depends who's asking</t>
         </is>
       </c>
       <c r="G187" s="5" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H187" s="3" t="inlineStr"/>
       <c r="I187" s="3" t="inlineStr"/>
@@ -12754,59 +12750,59 @@
       </c>
       <c r="D188" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E188" s="7" t="inlineStr">
         <is>
-          <t>It depends who's asking</t>
-        </is>
-      </c>
-      <c r="F188" s="7" t="inlineStr">
-        <is>
-          <t>from a number that depends who's asking</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F188" s="7" t="inlineStr"/>
       <c r="G188" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H188" s="3" t="inlineStr"/>
-      <c r="I188" s="3" t="inlineStr"/>
+      <c r="I188" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>q30</t>
+          <t>q31</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>How does a prospect find out what you charge?</t>
+          <t>How many new enquiries does the business get in a typical ...</t>
         </is>
       </c>
       <c r="D189" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E189" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F189" s="7" t="inlineStr"/>
+          <t>0 to 2</t>
+        </is>
+      </c>
+      <c r="F189" s="7" t="inlineStr">
+        <is>
+          <t>a handful at most</t>
+        </is>
+      </c>
       <c r="G189" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H189" s="3" t="inlineStr"/>
-      <c r="I189" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="I189" s="3" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="5" t="n">
@@ -12824,21 +12820,21 @@
       </c>
       <c r="D190" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E190" s="7" t="inlineStr">
         <is>
-          <t>0 to 2</t>
+          <t>3 to 10</t>
         </is>
       </c>
       <c r="F190" s="7" t="inlineStr">
         <is>
-          <t>a handful at most</t>
+          <t>in the 3 to 10 range</t>
         </is>
       </c>
       <c r="G190" s="5" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H190" s="3" t="inlineStr"/>
       <c r="I190" s="3" t="inlineStr"/>
@@ -12859,21 +12855,21 @@
       </c>
       <c r="D191" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E191" s="7" t="inlineStr">
         <is>
-          <t>3 to 10</t>
+          <t>11 to 30</t>
         </is>
       </c>
       <c r="F191" s="7" t="inlineStr">
         <is>
-          <t>in the 3 to 10 range</t>
+          <t>in the 11 to 30 range</t>
         </is>
       </c>
       <c r="G191" s="5" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="H191" s="3" t="inlineStr"/>
       <c r="I191" s="3" t="inlineStr"/>
@@ -12894,21 +12890,21 @@
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E192" s="7" t="inlineStr">
         <is>
-          <t>11 to 30</t>
+          <t>31 to 100</t>
         </is>
       </c>
       <c r="F192" s="7" t="inlineStr">
         <is>
-          <t>in the 11 to 30 range</t>
+          <t>in the 31 to 100 range</t>
         </is>
       </c>
       <c r="G192" s="5" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="H192" s="3" t="inlineStr"/>
       <c r="I192" s="3" t="inlineStr"/>
@@ -12929,21 +12925,21 @@
       </c>
       <c r="D193" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E193" s="7" t="inlineStr">
         <is>
-          <t>31 to 100</t>
+          <t>More than 100</t>
         </is>
       </c>
       <c r="F193" s="7" t="inlineStr">
         <is>
-          <t>in the 31 to 100 range</t>
+          <t>above 100</t>
         </is>
       </c>
       <c r="G193" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H193" s="3" t="inlineStr"/>
       <c r="I193" s="3" t="inlineStr"/>
@@ -12964,63 +12960,59 @@
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E194" s="7" t="inlineStr">
         <is>
-          <t>More than 100</t>
-        </is>
-      </c>
-      <c r="F194" s="7" t="inlineStr">
-        <is>
-          <t>above 100</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F194" s="7" t="inlineStr"/>
       <c r="G194" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H194" s="3" t="inlineStr"/>
-      <c r="I194" s="3" t="inlineStr"/>
+      <c r="H194" s="3" t="inlineStr">
+        <is>
+          <t>no_data</t>
+        </is>
+      </c>
+      <c r="I194" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>q31</t>
+          <t>q32</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>How many new enquiries does the business get in a typical ...</t>
+          <t>Where do your enquiries actually come from?</t>
         </is>
       </c>
       <c r="D195" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E195" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>Word of mouth and referral</t>
         </is>
       </c>
       <c r="F195" s="7" t="inlineStr"/>
       <c r="G195" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H195" s="3" t="inlineStr">
-        <is>
-          <t>no_data</t>
-        </is>
-      </c>
-      <c r="I195" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="H195" s="3" t="inlineStr"/>
+      <c r="I195" s="3" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="5" t="n">
@@ -13038,12 +13030,12 @@
       </c>
       <c r="D196" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E196" s="7" t="inlineStr">
         <is>
-          <t>Word of mouth and referral</t>
+          <t>Repeat customers</t>
         </is>
       </c>
       <c r="F196" s="7" t="inlineStr"/>
@@ -13069,12 +13061,12 @@
       </c>
       <c r="D197" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E197" s="7" t="inlineStr">
         <is>
-          <t>Repeat customers</t>
+          <t>Paid advertising</t>
         </is>
       </c>
       <c r="F197" s="7" t="inlineStr"/>
@@ -13100,12 +13092,12 @@
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E198" s="7" t="inlineStr">
         <is>
-          <t>Paid advertising</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F198" s="7" t="inlineStr"/>
@@ -13131,12 +13123,12 @@
       </c>
       <c r="D199" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E199" s="7" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="F199" s="7" t="inlineStr"/>
@@ -13162,12 +13154,12 @@
       </c>
       <c r="D200" s="6" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>f</t>
         </is>
       </c>
       <c r="E200" s="7" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>Outbound, we go and get it</t>
         </is>
       </c>
       <c r="F200" s="7" t="inlineStr"/>
@@ -13193,12 +13185,12 @@
       </c>
       <c r="D201" s="6" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E201" s="7" t="inlineStr">
         <is>
-          <t>Outbound, we go and get it</t>
+          <t>A partner or a channel</t>
         </is>
       </c>
       <c r="F201" s="7" t="inlineStr"/>
@@ -13224,59 +13216,63 @@
       </c>
       <c r="D202" s="6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>n</t>
         </is>
       </c>
       <c r="E202" s="7" t="inlineStr">
         <is>
-          <t>A partner or a channel</t>
+          <t>We don't really know</t>
         </is>
       </c>
       <c r="F202" s="7" t="inlineStr"/>
       <c r="G202" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H202" s="3" t="inlineStr"/>
-      <c r="I202" s="3" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="H202" s="3" t="inlineStr">
+        <is>
+          <t>no_data</t>
+        </is>
+      </c>
+      <c r="I202" s="3" t="inlineStr">
+        <is>
+          <t>Clears every other tick</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>q32</t>
+          <t>q33</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>Where do your enquiries actually come from?</t>
+          <t>Has enquiry volume changed in the last 12 months?</t>
         </is>
       </c>
       <c r="D203" s="6" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E203" s="7" t="inlineStr">
         <is>
-          <t>We don't really know</t>
-        </is>
-      </c>
-      <c r="F203" s="7" t="inlineStr"/>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="F203" s="7" t="inlineStr">
+        <is>
+          <t>grown</t>
+        </is>
+      </c>
       <c r="G203" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H203" s="3" t="inlineStr">
-        <is>
-          <t>no_data</t>
-        </is>
-      </c>
-      <c r="I203" s="3" t="inlineStr">
-        <is>
-          <t>Clears every other tick</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H203" s="3" t="inlineStr"/>
+      <c r="I203" s="3" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="5" t="n">
@@ -13294,21 +13290,21 @@
       </c>
       <c r="D204" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E204" s="7" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Flat</t>
         </is>
       </c>
       <c r="F204" s="7" t="inlineStr">
         <is>
-          <t>grown</t>
+          <t>stayed flat</t>
         </is>
       </c>
       <c r="G204" s="5" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H204" s="3" t="inlineStr"/>
       <c r="I204" s="3" t="inlineStr"/>
@@ -13329,21 +13325,21 @@
       </c>
       <c r="D205" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E205" s="7" t="inlineStr">
         <is>
-          <t>Flat</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="F205" s="7" t="inlineStr">
         <is>
-          <t>stayed flat</t>
+          <t>fallen</t>
         </is>
       </c>
       <c r="G205" s="5" t="n">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="H205" s="3" t="inlineStr"/>
       <c r="I205" s="3" t="inlineStr"/>
@@ -13364,21 +13360,21 @@
       </c>
       <c r="D206" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E206" s="7" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Down sharply</t>
         </is>
       </c>
       <c r="F206" s="7" t="inlineStr">
         <is>
-          <t>fallen</t>
+          <t>fallen sharply</t>
         </is>
       </c>
       <c r="G206" s="5" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="H206" s="3" t="inlineStr"/>
       <c r="I206" s="3" t="inlineStr"/>
@@ -13399,63 +13395,63 @@
       </c>
       <c r="D207" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E207" s="7" t="inlineStr">
         <is>
-          <t>Down sharply</t>
-        </is>
-      </c>
-      <c r="F207" s="7" t="inlineStr">
-        <is>
-          <t>fallen sharply</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F207" s="7" t="inlineStr"/>
       <c r="G207" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H207" s="3" t="inlineStr"/>
-      <c r="I207" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H207" s="3" t="inlineStr">
+        <is>
+          <t>no_data</t>
+        </is>
+      </c>
+      <c r="I207" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>q33</t>
+          <t>q34</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>Has enquiry volume changed in the last 12 months?</t>
+          <t>If twice as many enquiries landed next month, could you de...</t>
         </is>
       </c>
       <c r="D208" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E208" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F208" s="7" t="inlineStr"/>
+          <t>Yes, easily</t>
+        </is>
+      </c>
+      <c r="F208" s="7" t="inlineStr">
+        <is>
+          <t>comfortably</t>
+        </is>
+      </c>
       <c r="G208" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H208" s="3" t="inlineStr">
-        <is>
-          <t>no_data</t>
-        </is>
-      </c>
-      <c r="I208" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="H208" s="3" t="inlineStr"/>
+      <c r="I208" s="3" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="5" t="n">
@@ -13473,21 +13469,21 @@
       </c>
       <c r="D209" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E209" s="7" t="inlineStr">
         <is>
-          <t>Yes, easily</t>
+          <t>Yes, with a stretch</t>
         </is>
       </c>
       <c r="F209" s="7" t="inlineStr">
         <is>
-          <t>comfortably</t>
+          <t>with a stretch</t>
         </is>
       </c>
       <c r="G209" s="5" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="H209" s="3" t="inlineStr"/>
       <c r="I209" s="3" t="inlineStr"/>
@@ -13508,24 +13504,28 @@
       </c>
       <c r="D210" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E210" s="7" t="inlineStr">
         <is>
-          <t>Yes, with a stretch</t>
+          <t>No, we'd be well over capacity</t>
         </is>
       </c>
       <c r="F210" s="7" t="inlineStr">
         <is>
-          <t>with a stretch</t>
+          <t>not a chance</t>
         </is>
       </c>
       <c r="G210" s="5" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H210" s="3" t="inlineStr"/>
-      <c r="I210" s="3" t="inlineStr"/>
+      <c r="I210" s="3" t="inlineStr">
+        <is>
+          <t>Rules out demand entirely</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="5" t="n">
@@ -13543,63 +13543,59 @@
       </c>
       <c r="D211" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E211" s="7" t="inlineStr">
         <is>
-          <t>No, we'd be well over capacity</t>
-        </is>
-      </c>
-      <c r="F211" s="7" t="inlineStr">
-        <is>
-          <t>not a chance</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F211" s="7" t="inlineStr"/>
       <c r="G211" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H211" s="3" t="inlineStr"/>
       <c r="I211" s="3" t="inlineStr">
         <is>
-          <t>Rules out demand entirely</t>
+          <t>Not sure, scores nothing and feeds data blindness</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>q34</t>
+          <t>q35</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>If twice as many enquiries landed next month, could you de...</t>
+          <t>Are you doing anything right now to generate new enquiries...</t>
         </is>
       </c>
       <c r="D212" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E212" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F212" s="7" t="inlineStr"/>
+          <t>Yes, consistently</t>
+        </is>
+      </c>
+      <c r="F212" s="7" t="inlineStr">
+        <is>
+          <t>you're generating enquiries consistently</t>
+        </is>
+      </c>
       <c r="G212" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H212" s="3" t="inlineStr"/>
-      <c r="I212" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="I212" s="3" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="5" t="n">
@@ -13617,21 +13613,21 @@
       </c>
       <c r="D213" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E213" s="7" t="inlineStr">
         <is>
-          <t>Yes, consistently</t>
+          <t>On and off</t>
         </is>
       </c>
       <c r="F213" s="7" t="inlineStr">
         <is>
-          <t>consistently</t>
+          <t>you're generating enquiries on and off</t>
         </is>
       </c>
       <c r="G213" s="5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H213" s="3" t="inlineStr"/>
       <c r="I213" s="3" t="inlineStr"/>
@@ -13652,21 +13648,21 @@
       </c>
       <c r="D214" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E214" s="7" t="inlineStr">
         <is>
-          <t>On and off</t>
+          <t>No, it all comes to us</t>
         </is>
       </c>
       <c r="F214" s="7" t="inlineStr">
         <is>
-          <t>on and off</t>
+          <t>you're doing nothing to generate enquiries, it all comes to you</t>
         </is>
       </c>
       <c r="G214" s="5" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="H214" s="3" t="inlineStr"/>
       <c r="I214" s="3" t="inlineStr"/>
@@ -13687,59 +13683,59 @@
       </c>
       <c r="D215" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E215" s="7" t="inlineStr">
         <is>
-          <t>No, it all comes to us</t>
-        </is>
-      </c>
-      <c r="F215" s="7" t="inlineStr">
-        <is>
-          <t>nothing, it all comes to you</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F215" s="7" t="inlineStr"/>
       <c r="G215" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H215" s="3" t="inlineStr"/>
-      <c r="I215" s="3" t="inlineStr"/>
+      <c r="I215" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>q35</t>
+          <t>q36</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>Are you doing anything right now to generate new enquiries...</t>
+          <t>On a typical job or sale, what's left after the direct cos...</t>
         </is>
       </c>
       <c r="D216" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E216" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F216" s="7" t="inlineStr"/>
+          <t>More than 50%</t>
+        </is>
+      </c>
+      <c r="F216" s="7" t="inlineStr">
+        <is>
+          <t>above 50%</t>
+        </is>
+      </c>
       <c r="G216" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H216" s="3" t="inlineStr"/>
-      <c r="I216" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="I216" s="3" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="5" t="n">
@@ -13757,21 +13753,21 @@
       </c>
       <c r="D217" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E217" s="7" t="inlineStr">
         <is>
-          <t>More than 50%</t>
+          <t>30% to 50%</t>
         </is>
       </c>
       <c r="F217" s="7" t="inlineStr">
         <is>
-          <t>above 50%</t>
+          <t>in the 30 to 50% range</t>
         </is>
       </c>
       <c r="G217" s="5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H217" s="3" t="inlineStr"/>
       <c r="I217" s="3" t="inlineStr"/>
@@ -13792,21 +13788,21 @@
       </c>
       <c r="D218" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E218" s="7" t="inlineStr">
         <is>
-          <t>30% to 50%</t>
+          <t>15% to 30%</t>
         </is>
       </c>
       <c r="F218" s="7" t="inlineStr">
         <is>
-          <t>in the 30 to 50% range</t>
+          <t>in the 15 to 30% range</t>
         </is>
       </c>
       <c r="G218" s="5" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="H218" s="3" t="inlineStr"/>
       <c r="I218" s="3" t="inlineStr"/>
@@ -13827,21 +13823,21 @@
       </c>
       <c r="D219" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E219" s="7" t="inlineStr">
         <is>
-          <t>15% to 30%</t>
+          <t>Under 15%</t>
         </is>
       </c>
       <c r="F219" s="7" t="inlineStr">
         <is>
-          <t>in the 15 to 30% range</t>
+          <t>under 15%</t>
         </is>
       </c>
       <c r="G219" s="5" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H219" s="3" t="inlineStr"/>
       <c r="I219" s="3" t="inlineStr"/>
@@ -13862,63 +13858,63 @@
       </c>
       <c r="D220" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E220" s="7" t="inlineStr">
         <is>
-          <t>Under 15%</t>
-        </is>
-      </c>
-      <c r="F220" s="7" t="inlineStr">
-        <is>
-          <t>under 15%</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F220" s="7" t="inlineStr"/>
       <c r="G220" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H220" s="3" t="inlineStr"/>
-      <c r="I220" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H220" s="3" t="inlineStr">
+        <is>
+          <t>no_data</t>
+        </is>
+      </c>
+      <c r="I220" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B221" s="6" t="inlineStr">
         <is>
-          <t>q36</t>
+          <t>q37</t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>On a typical job or sale, what's left after the direct cos...</t>
+          <t>After everything, including paying yourself properly, what...</t>
         </is>
       </c>
       <c r="D221" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E221" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F221" s="7" t="inlineStr"/>
+          <t>More than 20%</t>
+        </is>
+      </c>
+      <c r="F221" s="7" t="inlineStr">
+        <is>
+          <t>above 20%</t>
+        </is>
+      </c>
       <c r="G221" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H221" s="3" t="inlineStr">
-        <is>
-          <t>no_data</t>
-        </is>
-      </c>
-      <c r="I221" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="H221" s="3" t="inlineStr"/>
+      <c r="I221" s="3" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="5" t="n">
@@ -13936,21 +13932,21 @@
       </c>
       <c r="D222" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E222" s="7" t="inlineStr">
         <is>
-          <t>More than 20%</t>
+          <t>10% to 20%</t>
         </is>
       </c>
       <c r="F222" s="7" t="inlineStr">
         <is>
-          <t>above 20%</t>
+          <t>in the 10 to 20% range</t>
         </is>
       </c>
       <c r="G222" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H222" s="3" t="inlineStr"/>
       <c r="I222" s="3" t="inlineStr"/>
@@ -13971,21 +13967,21 @@
       </c>
       <c r="D223" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E223" s="7" t="inlineStr">
         <is>
-          <t>10% to 20%</t>
+          <t>1% to 10%</t>
         </is>
       </c>
       <c r="F223" s="7" t="inlineStr">
         <is>
-          <t>in the 10 to 20% range</t>
+          <t>in the 1 to 10% range</t>
         </is>
       </c>
       <c r="G223" s="5" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="H223" s="3" t="inlineStr"/>
       <c r="I223" s="3" t="inlineStr"/>
@@ -14006,21 +14002,21 @@
       </c>
       <c r="D224" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E224" s="7" t="inlineStr">
         <is>
-          <t>1% to 10%</t>
+          <t>Nothing, or a loss</t>
         </is>
       </c>
       <c r="F224" s="7" t="inlineStr">
         <is>
-          <t>in the 1 to 10% range</t>
+          <t>nothing, or a loss</t>
         </is>
       </c>
       <c r="G224" s="5" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H224" s="3" t="inlineStr"/>
       <c r="I224" s="3" t="inlineStr"/>
@@ -14041,63 +14037,63 @@
       </c>
       <c r="D225" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E225" s="7" t="inlineStr">
         <is>
-          <t>Nothing, or a loss</t>
-        </is>
-      </c>
-      <c r="F225" s="7" t="inlineStr">
-        <is>
-          <t>nothing, or a loss</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F225" s="7" t="inlineStr"/>
       <c r="G225" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H225" s="3" t="inlineStr"/>
-      <c r="I225" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H225" s="3" t="inlineStr">
+        <is>
+          <t>no_data</t>
+        </is>
+      </c>
+      <c r="I225" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>q37</t>
+          <t>q38</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>After everything, including paying yourself properly, what...</t>
+          <t>When did you last raise your prices?</t>
         </is>
       </c>
       <c r="D226" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E226" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F226" s="7" t="inlineStr"/>
+          <t>In the last 6 months</t>
+        </is>
+      </c>
+      <c r="F226" s="7" t="inlineStr">
+        <is>
+          <t>you last raised prices inside the last six months</t>
+        </is>
+      </c>
       <c r="G226" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H226" s="3" t="inlineStr">
-        <is>
-          <t>no_data</t>
-        </is>
-      </c>
-      <c r="I226" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="H226" s="3" t="inlineStr"/>
+      <c r="I226" s="3" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="5" t="n">
@@ -14115,21 +14111,21 @@
       </c>
       <c r="D227" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E227" s="7" t="inlineStr">
         <is>
-          <t>In the last 6 months</t>
+          <t>6 to 12 months ago</t>
         </is>
       </c>
       <c r="F227" s="7" t="inlineStr">
         <is>
-          <t>inside the last six months</t>
+          <t>you last raised prices in the last year</t>
         </is>
       </c>
       <c r="G227" s="5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H227" s="3" t="inlineStr"/>
       <c r="I227" s="3" t="inlineStr"/>
@@ -14150,21 +14146,21 @@
       </c>
       <c r="D228" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E228" s="7" t="inlineStr">
         <is>
-          <t>6 to 12 months ago</t>
+          <t>1 to 2 years ago</t>
         </is>
       </c>
       <c r="F228" s="7" t="inlineStr">
         <is>
-          <t>in the last year</t>
+          <t>you last raised prices one to two years ago</t>
         </is>
       </c>
       <c r="G228" s="5" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="H228" s="3" t="inlineStr"/>
       <c r="I228" s="3" t="inlineStr"/>
@@ -14185,21 +14181,21 @@
       </c>
       <c r="D229" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E229" s="7" t="inlineStr">
         <is>
-          <t>1 to 2 years ago</t>
+          <t>More than 2 years ago</t>
         </is>
       </c>
       <c r="F229" s="7" t="inlineStr">
         <is>
-          <t>one to two years ago</t>
+          <t>you last raised prices more than two years ago</t>
         </is>
       </c>
       <c r="G229" s="5" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="H229" s="3" t="inlineStr"/>
       <c r="I229" s="3" t="inlineStr"/>
@@ -14220,21 +14216,21 @@
       </c>
       <c r="D230" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E230" s="7" t="inlineStr">
         <is>
-          <t>More than 2 years ago</t>
+          <t>Never</t>
         </is>
       </c>
       <c r="F230" s="7" t="inlineStr">
         <is>
-          <t>more than two years ago</t>
+          <t>you've never raised your prices</t>
         </is>
       </c>
       <c r="G230" s="5" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H230" s="3" t="inlineStr"/>
       <c r="I230" s="3" t="inlineStr"/>
@@ -14255,59 +14251,59 @@
       </c>
       <c r="D231" s="6" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E231" s="7" t="inlineStr">
         <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="F231" s="7" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F231" s="7" t="inlineStr"/>
       <c r="G231" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H231" s="3" t="inlineStr"/>
-      <c r="I231" s="3" t="inlineStr"/>
+      <c r="I231" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t>q38</t>
+          <t>q39</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>When did you last raise your prices?</t>
+          <t>How often does a job end up costing more to deliver than y...</t>
         </is>
       </c>
       <c r="D232" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E232" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F232" s="7" t="inlineStr"/>
+          <t>Rarely</t>
+        </is>
+      </c>
+      <c r="F232" s="7" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
       <c r="G232" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H232" s="3" t="inlineStr"/>
-      <c r="I232" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="I232" s="3" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="5" t="n">
@@ -14325,21 +14321,21 @@
       </c>
       <c r="D233" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E233" s="7" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Sometimes</t>
         </is>
       </c>
       <c r="F233" s="7" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="G233" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H233" s="3" t="inlineStr"/>
       <c r="I233" s="3" t="inlineStr"/>
@@ -14360,21 +14356,21 @@
       </c>
       <c r="D234" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E234" s="7" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Often</t>
         </is>
       </c>
       <c r="F234" s="7" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>often</t>
         </is>
       </c>
       <c r="G234" s="5" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="H234" s="3" t="inlineStr"/>
       <c r="I234" s="3" t="inlineStr"/>
@@ -14395,21 +14391,21 @@
       </c>
       <c r="D235" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E235" s="7" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>On most jobs</t>
         </is>
       </c>
       <c r="F235" s="7" t="inlineStr">
         <is>
-          <t>often</t>
+          <t>on most jobs</t>
         </is>
       </c>
       <c r="G235" s="5" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="H235" s="3" t="inlineStr"/>
       <c r="I235" s="3" t="inlineStr"/>
@@ -14430,59 +14426,59 @@
       </c>
       <c r="D236" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E236" s="7" t="inlineStr">
         <is>
-          <t>On most jobs</t>
-        </is>
-      </c>
-      <c r="F236" s="7" t="inlineStr">
-        <is>
-          <t>on most jobs</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F236" s="7" t="inlineStr"/>
       <c r="G236" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H236" s="3" t="inlineStr"/>
-      <c r="I236" s="3" t="inlineStr"/>
+      <c r="I236" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B237" s="6" t="inlineStr">
         <is>
-          <t>q39</t>
+          <t>q40</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>How often does a job end up costing more to deliver than y...</t>
+          <t>Do you know which customers, jobs or product lines actuall...</t>
         </is>
       </c>
       <c r="D237" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E237" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F237" s="7" t="inlineStr"/>
+          <t>Yes, job by job or line by line</t>
+        </is>
+      </c>
+      <c r="F237" s="7" t="inlineStr">
+        <is>
+          <t>job by job</t>
+        </is>
+      </c>
       <c r="G237" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H237" s="3" t="inlineStr"/>
-      <c r="I237" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="I237" s="3" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="5" t="n">
@@ -14500,21 +14496,21 @@
       </c>
       <c r="D238" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E238" s="7" t="inlineStr">
         <is>
-          <t>Yes, job by job or line by line</t>
+          <t>Roughly</t>
         </is>
       </c>
       <c r="F238" s="7" t="inlineStr">
         <is>
-          <t>job by job</t>
+          <t>roughly</t>
         </is>
       </c>
       <c r="G238" s="5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H238" s="3" t="inlineStr"/>
       <c r="I238" s="3" t="inlineStr"/>
@@ -14535,23 +14531,27 @@
       </c>
       <c r="D239" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E239" s="7" t="inlineStr">
         <is>
-          <t>Roughly</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F239" s="7" t="inlineStr">
         <is>
-          <t>roughly</t>
+          <t>not at all</t>
         </is>
       </c>
       <c r="G239" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="H239" s="3" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="H239" s="3" t="inlineStr">
+        <is>
+          <t>no_data</t>
+        </is>
+      </c>
       <c r="I239" s="3" t="inlineStr"/>
     </row>
     <row r="240">
@@ -14570,67 +14570,61 @@
       </c>
       <c r="D240" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E240" s="7" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F240" s="7" t="inlineStr">
-        <is>
-          <t>not at all</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F240" s="7" t="inlineStr"/>
       <c r="G240" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H240" s="3" t="inlineStr">
         <is>
           <t>no_data</t>
         </is>
       </c>
-      <c r="I240" s="3" t="inlineStr"/>
+      <c r="I240" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B241" s="6" t="inlineStr">
         <is>
-          <t>q40</t>
+          <t>q41</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>Do you know which customers, jobs or product lines actuall...</t>
+          <t>What share of your revenue comes from your single biggest ...</t>
         </is>
       </c>
       <c r="D241" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E241" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F241" s="7" t="inlineStr"/>
-      <c r="G241" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H241" s="3" t="inlineStr">
-        <is>
-          <t>no_data</t>
-        </is>
-      </c>
-      <c r="I241" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+          <t>Under 10%</t>
+        </is>
+      </c>
+      <c r="F241" s="7" t="inlineStr">
+        <is>
+          <t>under 10%</t>
+        </is>
+      </c>
+      <c r="G241" s="5" t="inlineStr"/>
+      <c r="H241" s="3" t="inlineStr"/>
+      <c r="I241" s="3" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="5" t="n">
@@ -14648,21 +14642,25 @@
       </c>
       <c r="D242" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E242" s="7" t="inlineStr">
         <is>
-          <t>Under 10%</t>
+          <t>10% to 20%</t>
         </is>
       </c>
       <c r="F242" s="7" t="inlineStr">
         <is>
-          <t>under 10%</t>
+          <t>between 10 and 20%</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr"/>
-      <c r="H242" s="3" t="inlineStr"/>
+      <c r="H242" s="3" t="inlineStr">
+        <is>
+          <t>key_client (35)</t>
+        </is>
+      </c>
       <c r="I242" s="3" t="inlineStr"/>
     </row>
     <row r="243">
@@ -14681,23 +14679,23 @@
       </c>
       <c r="D243" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E243" s="7" t="inlineStr">
         <is>
-          <t>10% to 20%</t>
+          <t>20% to 30%</t>
         </is>
       </c>
       <c r="F243" s="7" t="inlineStr">
         <is>
-          <t>between 10 and 20%</t>
+          <t>between 20 and 30%</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr"/>
       <c r="H243" s="3" t="inlineStr">
         <is>
-          <t>key_client (35)</t>
+          <t>key_client (65)</t>
         </is>
       </c>
       <c r="I243" s="3" t="inlineStr"/>
@@ -14718,23 +14716,23 @@
       </c>
       <c r="D244" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E244" s="7" t="inlineStr">
         <is>
-          <t>20% to 30%</t>
+          <t>30% to 50%</t>
         </is>
       </c>
       <c r="F244" s="7" t="inlineStr">
         <is>
-          <t>between 20 and 30%</t>
+          <t>between 30 and 50%</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr"/>
       <c r="H244" s="3" t="inlineStr">
         <is>
-          <t>key_client (65)</t>
+          <t>key_client (90)</t>
         </is>
       </c>
       <c r="I244" s="3" t="inlineStr"/>
@@ -14755,23 +14753,23 @@
       </c>
       <c r="D245" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E245" s="7" t="inlineStr">
         <is>
-          <t>30% to 50%</t>
+          <t>More than 50%</t>
         </is>
       </c>
       <c r="F245" s="7" t="inlineStr">
         <is>
-          <t>between 30 and 50%</t>
+          <t>more than half</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr"/>
       <c r="H245" s="3" t="inlineStr">
         <is>
-          <t>key_client (90)</t>
+          <t>key_client (100)</t>
         </is>
       </c>
       <c r="I245" s="3" t="inlineStr"/>
@@ -14792,63 +14790,59 @@
       </c>
       <c r="D246" s="6" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E246" s="7" t="inlineStr">
         <is>
-          <t>More than 50%</t>
-        </is>
-      </c>
-      <c r="F246" s="7" t="inlineStr">
-        <is>
-          <t>more than half</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F246" s="7" t="inlineStr"/>
       <c r="G246" s="5" t="inlineStr"/>
       <c r="H246" s="3" t="inlineStr">
         <is>
-          <t>key_client (100)</t>
-        </is>
-      </c>
-      <c r="I246" s="3" t="inlineStr"/>
+          <t>no_data (70)</t>
+        </is>
+      </c>
+      <c r="I246" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B247" s="6" t="inlineStr">
         <is>
-          <t>q41</t>
+          <t>q42</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>What share of your revenue comes from your single biggest ...</t>
+          <t>What share of revenue comes from your single biggest produ...</t>
         </is>
       </c>
       <c r="D247" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E247" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F247" s="7" t="inlineStr"/>
+          <t>Under 25%</t>
+        </is>
+      </c>
+      <c r="F247" s="7" t="inlineStr">
+        <is>
+          <t>under a quarter</t>
+        </is>
+      </c>
       <c r="G247" s="5" t="inlineStr"/>
-      <c r="H247" s="3" t="inlineStr">
-        <is>
-          <t>no_data (70)</t>
-        </is>
-      </c>
-      <c r="I247" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="H247" s="3" t="inlineStr"/>
+      <c r="I247" s="3" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="5" t="n">
@@ -14866,21 +14860,25 @@
       </c>
       <c r="D248" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E248" s="7" t="inlineStr">
         <is>
-          <t>Under 25%</t>
+          <t>25% to 50%</t>
         </is>
       </c>
       <c r="F248" s="7" t="inlineStr">
         <is>
-          <t>under a quarter</t>
+          <t>a quarter to a half</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr"/>
-      <c r="H248" s="3" t="inlineStr"/>
+      <c r="H248" s="3" t="inlineStr">
+        <is>
+          <t>key_product (40)</t>
+        </is>
+      </c>
       <c r="I248" s="3" t="inlineStr"/>
     </row>
     <row r="249">
@@ -14899,23 +14897,23 @@
       </c>
       <c r="D249" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E249" s="7" t="inlineStr">
         <is>
-          <t>25% to 50%</t>
+          <t>50% to 75%</t>
         </is>
       </c>
       <c r="F249" s="7" t="inlineStr">
         <is>
-          <t>a quarter to a half</t>
+          <t>half to three quarters</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr"/>
       <c r="H249" s="3" t="inlineStr">
         <is>
-          <t>key_product (40)</t>
+          <t>key_product (75)</t>
         </is>
       </c>
       <c r="I249" s="3" t="inlineStr"/>
@@ -14936,23 +14934,23 @@
       </c>
       <c r="D250" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E250" s="7" t="inlineStr">
         <is>
-          <t>50% to 75%</t>
+          <t>More than 75%</t>
         </is>
       </c>
       <c r="F250" s="7" t="inlineStr">
         <is>
-          <t>half to three quarters</t>
+          <t>more than three quarters</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr"/>
       <c r="H250" s="3" t="inlineStr">
         <is>
-          <t>key_product (75)</t>
+          <t>key_product (95)</t>
         </is>
       </c>
       <c r="I250" s="3" t="inlineStr"/>
@@ -14973,63 +14971,59 @@
       </c>
       <c r="D251" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E251" s="7" t="inlineStr">
         <is>
-          <t>More than 75%</t>
-        </is>
-      </c>
-      <c r="F251" s="7" t="inlineStr">
-        <is>
-          <t>more than three quarters</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F251" s="7" t="inlineStr"/>
       <c r="G251" s="5" t="inlineStr"/>
       <c r="H251" s="3" t="inlineStr">
         <is>
-          <t>key_product (95)</t>
-        </is>
-      </c>
-      <c r="I251" s="3" t="inlineStr"/>
+          <t>no_data (70)</t>
+        </is>
+      </c>
+      <c r="I251" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B252" s="6" t="inlineStr">
         <is>
-          <t>q42</t>
+          <t>q43</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>What share of revenue comes from your single biggest produ...</t>
+          <t>How spread out are the places your new customers come from...</t>
         </is>
       </c>
       <c r="D252" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E252" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F252" s="7" t="inlineStr"/>
+          <t>Spread across several</t>
+        </is>
+      </c>
+      <c r="F252" s="7" t="inlineStr">
+        <is>
+          <t>spread across several channels</t>
+        </is>
+      </c>
       <c r="G252" s="5" t="inlineStr"/>
-      <c r="H252" s="3" t="inlineStr">
-        <is>
-          <t>no_data (70)</t>
-        </is>
-      </c>
-      <c r="I252" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="H252" s="3" t="inlineStr"/>
+      <c r="I252" s="3" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="5" t="n">
@@ -15047,21 +15041,25 @@
       </c>
       <c r="D253" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E253" s="7" t="inlineStr">
         <is>
-          <t>Spread across several</t>
+          <t>Two channels carry it</t>
         </is>
       </c>
       <c r="F253" s="7" t="inlineStr">
         <is>
-          <t>spread across several channels</t>
+          <t>through two channels</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr"/>
-      <c r="H253" s="3" t="inlineStr"/>
+      <c r="H253" s="3" t="inlineStr">
+        <is>
+          <t>key_channel (50)</t>
+        </is>
+      </c>
       <c r="I253" s="3" t="inlineStr"/>
     </row>
     <row r="254">
@@ -15080,23 +15078,23 @@
       </c>
       <c r="D254" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E254" s="7" t="inlineStr">
         <is>
-          <t>Two channels carry it</t>
+          <t>One channel is nearly all of it</t>
         </is>
       </c>
       <c r="F254" s="7" t="inlineStr">
         <is>
-          <t>carried by two channels</t>
+          <t>almost entirely through one channel</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr"/>
       <c r="H254" s="3" t="inlineStr">
         <is>
-          <t>key_channel (50)</t>
+          <t>key_channel (95)</t>
         </is>
       </c>
       <c r="I254" s="3" t="inlineStr"/>
@@ -15117,63 +15115,59 @@
       </c>
       <c r="D255" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E255" s="7" t="inlineStr">
         <is>
-          <t>One channel is nearly all of it</t>
-        </is>
-      </c>
-      <c r="F255" s="7" t="inlineStr">
-        <is>
-          <t>almost entirely one channel</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F255" s="7" t="inlineStr"/>
       <c r="G255" s="5" t="inlineStr"/>
       <c r="H255" s="3" t="inlineStr">
         <is>
-          <t>key_channel (95)</t>
-        </is>
-      </c>
-      <c r="I255" s="3" t="inlineStr"/>
+          <t>no_data (70), key_channel (50)</t>
+        </is>
+      </c>
+      <c r="I255" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B256" s="6" t="inlineStr">
         <is>
-          <t>q43</t>
+          <t>q44</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>How spread out are the places your new customers come from...</t>
+          <t>Which of these is there exactly one of, with nobody and no...</t>
         </is>
       </c>
       <c r="D256" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E256" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>Your main supplier</t>
         </is>
       </c>
       <c r="F256" s="7" t="inlineStr"/>
       <c r="G256" s="5" t="inlineStr"/>
       <c r="H256" s="3" t="inlineStr">
         <is>
-          <t>no_data (70), key_channel (50)</t>
-        </is>
-      </c>
-      <c r="I256" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+          <t>key_supplier (80)</t>
+        </is>
+      </c>
+      <c r="I256" s="3" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="5" t="n">
@@ -15191,19 +15185,19 @@
       </c>
       <c r="D257" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E257" s="7" t="inlineStr">
         <is>
-          <t>Your main supplier</t>
+          <t>The person who wins the work</t>
         </is>
       </c>
       <c r="F257" s="7" t="inlineStr"/>
       <c r="G257" s="5" t="inlineStr"/>
       <c r="H257" s="3" t="inlineStr">
         <is>
-          <t>key_supplier (80)</t>
+          <t>key_person (80)</t>
         </is>
       </c>
       <c r="I257" s="3" t="inlineStr"/>
@@ -15224,19 +15218,19 @@
       </c>
       <c r="D258" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E258" s="7" t="inlineStr">
         <is>
-          <t>The person who wins the work</t>
+          <t>The person who knows how the work actually gets done</t>
         </is>
       </c>
       <c r="F258" s="7" t="inlineStr"/>
       <c r="G258" s="5" t="inlineStr"/>
       <c r="H258" s="3" t="inlineStr">
         <is>
-          <t>key_person (80)</t>
+          <t>key_employee (85)</t>
         </is>
       </c>
       <c r="I258" s="3" t="inlineStr"/>
@@ -15257,19 +15251,19 @@
       </c>
       <c r="D259" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E259" s="7" t="inlineStr">
         <is>
-          <t>The person who knows how the work actually gets done</t>
+          <t>One key piece of equipment, or one vehicle</t>
         </is>
       </c>
       <c r="F259" s="7" t="inlineStr"/>
       <c r="G259" s="5" t="inlineStr"/>
       <c r="H259" s="3" t="inlineStr">
         <is>
-          <t>key_employee (85)</t>
+          <t>key_asset (75)</t>
         </is>
       </c>
       <c r="I259" s="3" t="inlineStr"/>
@@ -15290,19 +15284,19 @@
       </c>
       <c r="D260" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E260" s="7" t="inlineStr">
         <is>
-          <t>One key piece of equipment, or one vehicle</t>
+          <t>The city or region you sell into</t>
         </is>
       </c>
       <c r="F260" s="7" t="inlineStr"/>
       <c r="G260" s="5" t="inlineStr"/>
       <c r="H260" s="3" t="inlineStr">
         <is>
-          <t>key_asset (75)</t>
+          <t>key_geography (70)</t>
         </is>
       </c>
       <c r="I260" s="3" t="inlineStr"/>
@@ -15323,19 +15317,19 @@
       </c>
       <c r="D261" s="6" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>f</t>
         </is>
       </c>
       <c r="E261" s="7" t="inlineStr">
         <is>
-          <t>The city or region you sell into</t>
+          <t>One licence, accreditation or insurance the business runs on</t>
         </is>
       </c>
       <c r="F261" s="7" t="inlineStr"/>
       <c r="G261" s="5" t="inlineStr"/>
       <c r="H261" s="3" t="inlineStr">
         <is>
-          <t>key_geography (70)</t>
+          <t>key_licence (85)</t>
         </is>
       </c>
       <c r="I261" s="3" t="inlineStr"/>
@@ -15356,19 +15350,19 @@
       </c>
       <c r="D262" s="6" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E262" s="7" t="inlineStr">
         <is>
-          <t>One licence, accreditation or insurance the business runs on</t>
+          <t>Your own name and reputation</t>
         </is>
       </c>
       <c r="F262" s="7" t="inlineStr"/>
       <c r="G262" s="5" t="inlineStr"/>
       <c r="H262" s="3" t="inlineStr">
         <is>
-          <t>key_licence (85)</t>
+          <t>key_person (85), owner_trapped (60)</t>
         </is>
       </c>
       <c r="I262" s="3" t="inlineStr"/>
@@ -15389,45 +15383,45 @@
       </c>
       <c r="D263" s="6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>n</t>
         </is>
       </c>
       <c r="E263" s="7" t="inlineStr">
         <is>
-          <t>Your own name and reputation</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="F263" s="7" t="inlineStr"/>
       <c r="G263" s="5" t="inlineStr"/>
-      <c r="H263" s="3" t="inlineStr">
-        <is>
-          <t>key_person (85), owner_trapped (60)</t>
-        </is>
-      </c>
-      <c r="I263" s="3" t="inlineStr"/>
+      <c r="H263" s="3" t="inlineStr"/>
+      <c r="I263" s="3" t="inlineStr">
+        <is>
+          <t>Clears every other tick</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B264" s="6" t="inlineStr">
         <is>
-          <t>q44</t>
+          <t>q58</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>Which of these is there exactly one of, with nobody and no...</t>
+          <t>Of the ones you just ticked, which would hurt most if it w...</t>
         </is>
       </c>
       <c r="D264" s="6" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E264" s="7" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Your main supplier</t>
         </is>
       </c>
       <c r="F264" s="7" t="inlineStr"/>
@@ -15435,7 +15429,7 @@
       <c r="H264" s="3" t="inlineStr"/>
       <c r="I264" s="3" t="inlineStr">
         <is>
-          <t>Clears every other tick</t>
+          <t>Promotes key_supplier to the top severity</t>
         </is>
       </c>
     </row>
@@ -15455,12 +15449,12 @@
       </c>
       <c r="D265" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E265" s="7" t="inlineStr">
         <is>
-          <t>Your main supplier</t>
+          <t>The person who wins the work</t>
         </is>
       </c>
       <c r="F265" s="7" t="inlineStr"/>
@@ -15468,7 +15462,7 @@
       <c r="H265" s="3" t="inlineStr"/>
       <c r="I265" s="3" t="inlineStr">
         <is>
-          <t>Promotes key_supplier to the top severity</t>
+          <t>Promotes key_person to the top severity</t>
         </is>
       </c>
     </row>
@@ -15488,12 +15482,12 @@
       </c>
       <c r="D266" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E266" s="7" t="inlineStr">
         <is>
-          <t>The person who wins the work</t>
+          <t>The person who knows how the work actually gets done</t>
         </is>
       </c>
       <c r="F266" s="7" t="inlineStr"/>
@@ -15501,7 +15495,7 @@
       <c r="H266" s="3" t="inlineStr"/>
       <c r="I266" s="3" t="inlineStr">
         <is>
-          <t>Promotes key_person to the top severity</t>
+          <t>Promotes key_employee to the top severity</t>
         </is>
       </c>
     </row>
@@ -15521,12 +15515,12 @@
       </c>
       <c r="D267" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E267" s="7" t="inlineStr">
         <is>
-          <t>The person who knows how the work actually gets done</t>
+          <t>One key piece of equipment, or one vehicle</t>
         </is>
       </c>
       <c r="F267" s="7" t="inlineStr"/>
@@ -15534,7 +15528,7 @@
       <c r="H267" s="3" t="inlineStr"/>
       <c r="I267" s="3" t="inlineStr">
         <is>
-          <t>Promotes key_employee to the top severity</t>
+          <t>Promotes key_asset to the top severity</t>
         </is>
       </c>
     </row>
@@ -15554,12 +15548,12 @@
       </c>
       <c r="D268" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E268" s="7" t="inlineStr">
         <is>
-          <t>One key piece of equipment, or one vehicle</t>
+          <t>The city or region you sell into</t>
         </is>
       </c>
       <c r="F268" s="7" t="inlineStr"/>
@@ -15567,7 +15561,7 @@
       <c r="H268" s="3" t="inlineStr"/>
       <c r="I268" s="3" t="inlineStr">
         <is>
-          <t>Promotes key_asset to the top severity</t>
+          <t>Promotes key_geography to the top severity</t>
         </is>
       </c>
     </row>
@@ -15587,12 +15581,12 @@
       </c>
       <c r="D269" s="6" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>f</t>
         </is>
       </c>
       <c r="E269" s="7" t="inlineStr">
         <is>
-          <t>The city or region you sell into</t>
+          <t>One licence, accreditation or insurance the business runs on</t>
         </is>
       </c>
       <c r="F269" s="7" t="inlineStr"/>
@@ -15600,7 +15594,7 @@
       <c r="H269" s="3" t="inlineStr"/>
       <c r="I269" s="3" t="inlineStr">
         <is>
-          <t>Promotes key_geography to the top severity</t>
+          <t>Promotes key_licence to the top severity</t>
         </is>
       </c>
     </row>
@@ -15620,12 +15614,12 @@
       </c>
       <c r="D270" s="6" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E270" s="7" t="inlineStr">
         <is>
-          <t>One licence, accreditation or insurance the business runs on</t>
+          <t>Your own name and reputation</t>
         </is>
       </c>
       <c r="F270" s="7" t="inlineStr"/>
@@ -15633,42 +15627,42 @@
       <c r="H270" s="3" t="inlineStr"/>
       <c r="I270" s="3" t="inlineStr">
         <is>
-          <t>Promotes key_licence to the top severity</t>
+          <t>Promotes key_person to the top severity</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B271" s="6" t="inlineStr">
         <is>
-          <t>q58</t>
+          <t>q45</t>
         </is>
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>Of the ones you just ticked, which would hurt most if it w...</t>
+          <t>How is your work actually committed by the customer?</t>
         </is>
       </c>
       <c r="D271" s="6" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E271" s="7" t="inlineStr">
         <is>
-          <t>Your own name and reputation</t>
-        </is>
-      </c>
-      <c r="F271" s="7" t="inlineStr"/>
+          <t>Term contracts covering most of it</t>
+        </is>
+      </c>
+      <c r="F271" s="7" t="inlineStr">
+        <is>
+          <t>term contracts</t>
+        </is>
+      </c>
       <c r="G271" s="5" t="inlineStr"/>
       <c r="H271" s="3" t="inlineStr"/>
-      <c r="I271" s="3" t="inlineStr">
-        <is>
-          <t>Promotes key_person to the top severity</t>
-        </is>
-      </c>
+      <c r="I271" s="3" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="5" t="n">
@@ -15686,21 +15680,25 @@
       </c>
       <c r="D272" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E272" s="7" t="inlineStr">
         <is>
-          <t>Term contracts covering most of it</t>
+          <t>Written agreements job by job</t>
         </is>
       </c>
       <c r="F272" s="7" t="inlineStr">
         <is>
-          <t>term contracts</t>
+          <t>job by job agreements</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr"/>
-      <c r="H272" s="3" t="inlineStr"/>
+      <c r="H272" s="3" t="inlineStr">
+        <is>
+          <t>no_contracts (35)</t>
+        </is>
+      </c>
       <c r="I272" s="3" t="inlineStr"/>
     </row>
     <row r="273">
@@ -15719,23 +15717,23 @@
       </c>
       <c r="D273" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E273" s="7" t="inlineStr">
         <is>
-          <t>Written agreements job by job</t>
+          <t>Month to month, cancellable anytime</t>
         </is>
       </c>
       <c r="F273" s="7" t="inlineStr">
         <is>
-          <t>job by job agreements</t>
+          <t>a month to month arrangement</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr"/>
       <c r="H273" s="3" t="inlineStr">
         <is>
-          <t>no_contracts (35)</t>
+          <t>no_contracts (75)</t>
         </is>
       </c>
       <c r="I273" s="3" t="inlineStr"/>
@@ -15756,23 +15754,23 @@
       </c>
       <c r="D274" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E274" s="7" t="inlineStr">
         <is>
-          <t>Month to month, cancellable anytime</t>
+          <t>Handshake and email</t>
         </is>
       </c>
       <c r="F274" s="7" t="inlineStr">
         <is>
-          <t>month to month</t>
+          <t>a handshake and an email</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr"/>
       <c r="H274" s="3" t="inlineStr">
         <is>
-          <t>no_contracts (75)</t>
+          <t>no_contracts (95)</t>
         </is>
       </c>
       <c r="I274" s="3" t="inlineStr"/>
@@ -15793,63 +15791,59 @@
       </c>
       <c r="D275" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E275" s="7" t="inlineStr">
         <is>
-          <t>Handshake and email</t>
-        </is>
-      </c>
-      <c r="F275" s="7" t="inlineStr">
-        <is>
-          <t>a handshake and an email</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F275" s="7" t="inlineStr"/>
       <c r="G275" s="5" t="inlineStr"/>
       <c r="H275" s="3" t="inlineStr">
         <is>
-          <t>no_contracts (95)</t>
-        </is>
-      </c>
-      <c r="I275" s="3" t="inlineStr"/>
+          <t>no_data (70), no_contracts (60)</t>
+        </is>
+      </c>
+      <c r="I275" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B276" s="6" t="inlineStr">
         <is>
-          <t>q45</t>
+          <t>q46</t>
         </is>
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>How is your work actually committed by the customer?</t>
+          <t>How much of the work is documented well enough that someon...</t>
         </is>
       </c>
       <c r="D276" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E276" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F276" s="7" t="inlineStr"/>
+          <t>Most of it</t>
+        </is>
+      </c>
+      <c r="F276" s="7" t="inlineStr">
+        <is>
+          <t>Most</t>
+        </is>
+      </c>
       <c r="G276" s="5" t="inlineStr"/>
-      <c r="H276" s="3" t="inlineStr">
-        <is>
-          <t>no_data (70), no_contracts (60)</t>
-        </is>
-      </c>
-      <c r="I276" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="H276" s="3" t="inlineStr"/>
+      <c r="I276" s="3" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="5" t="n">
@@ -15867,21 +15861,25 @@
       </c>
       <c r="D277" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E277" s="7" t="inlineStr">
         <is>
-          <t>Most of it</t>
+          <t>About half</t>
         </is>
       </c>
       <c r="F277" s="7" t="inlineStr">
         <is>
-          <t>Most</t>
+          <t>About half</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr"/>
-      <c r="H277" s="3" t="inlineStr"/>
+      <c r="H277" s="3" t="inlineStr">
+        <is>
+          <t>no_process (55)</t>
+        </is>
+      </c>
       <c r="I277" s="3" t="inlineStr"/>
     </row>
     <row r="278">
@@ -15900,23 +15898,23 @@
       </c>
       <c r="D278" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E278" s="7" t="inlineStr">
         <is>
-          <t>About half</t>
+          <t>Almost none, it lives in people's heads</t>
         </is>
       </c>
       <c r="F278" s="7" t="inlineStr">
         <is>
-          <t>About half</t>
+          <t>Almost none</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr"/>
       <c r="H278" s="3" t="inlineStr">
         <is>
-          <t>no_process (55)</t>
+          <t>no_process (95)</t>
         </is>
       </c>
       <c r="I278" s="3" t="inlineStr"/>
@@ -15937,63 +15935,59 @@
       </c>
       <c r="D279" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E279" s="7" t="inlineStr">
         <is>
-          <t>Almost none, it lives in people's heads</t>
-        </is>
-      </c>
-      <c r="F279" s="7" t="inlineStr">
-        <is>
-          <t>Almost none</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F279" s="7" t="inlineStr"/>
       <c r="G279" s="5" t="inlineStr"/>
       <c r="H279" s="3" t="inlineStr">
         <is>
-          <t>no_process (95)</t>
-        </is>
-      </c>
-      <c r="I279" s="3" t="inlineStr"/>
+          <t>no_process (80), no_data (60)</t>
+        </is>
+      </c>
+      <c r="I279" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B280" s="6" t="inlineStr">
         <is>
-          <t>q46</t>
+          <t>q47</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>How much of the work is documented well enough that someon...</t>
+          <t>How often do you look at numbers that tell you how the bus...</t>
         </is>
       </c>
       <c r="D280" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E280" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F280" s="7" t="inlineStr"/>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="F280" s="7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="G280" s="5" t="inlineStr"/>
-      <c r="H280" s="3" t="inlineStr">
-        <is>
-          <t>no_process (80), no_data (60)</t>
-        </is>
-      </c>
-      <c r="I280" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="H280" s="3" t="inlineStr"/>
+      <c r="I280" s="3" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="5" t="n">
@@ -16011,21 +16005,25 @@
       </c>
       <c r="D281" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E281" s="7" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="F281" s="7" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr"/>
-      <c r="H281" s="3" t="inlineStr"/>
+      <c r="H281" s="3" t="inlineStr">
+        <is>
+          <t>no_data (25)</t>
+        </is>
+      </c>
       <c r="I281" s="3" t="inlineStr"/>
     </row>
     <row r="282">
@@ -16044,23 +16042,23 @@
       </c>
       <c r="D282" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E282" s="7" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>At tax time</t>
         </is>
       </c>
       <c r="F282" s="7" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>once a year at tax time</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr"/>
       <c r="H282" s="3" t="inlineStr">
         <is>
-          <t>no_data (25)</t>
+          <t>no_data (90)</t>
         </is>
       </c>
       <c r="I282" s="3" t="inlineStr"/>
@@ -16081,23 +16079,23 @@
       </c>
       <c r="D283" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E283" s="7" t="inlineStr">
         <is>
-          <t>At tax time</t>
+          <t>We don't really</t>
         </is>
       </c>
       <c r="F283" s="7" t="inlineStr">
         <is>
-          <t>once a year at tax time</t>
+          <t>next to never</t>
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr"/>
       <c r="H283" s="3" t="inlineStr">
         <is>
-          <t>no_data (90)</t>
+          <t>no_data (100)</t>
         </is>
       </c>
       <c r="I283" s="3" t="inlineStr"/>
@@ -16118,63 +16116,59 @@
       </c>
       <c r="D284" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E284" s="7" t="inlineStr">
         <is>
-          <t>We don't really</t>
-        </is>
-      </c>
-      <c r="F284" s="7" t="inlineStr">
-        <is>
-          <t>next to never</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F284" s="7" t="inlineStr"/>
       <c r="G284" s="5" t="inlineStr"/>
       <c r="H284" s="3" t="inlineStr">
         <is>
-          <t>no_data (100)</t>
-        </is>
-      </c>
-      <c r="I284" s="3" t="inlineStr"/>
+          <t>no_data (90)</t>
+        </is>
+      </c>
+      <c r="I284" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B285" s="6" t="inlineStr">
         <is>
-          <t>q47</t>
+          <t>q48</t>
         </is>
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>How often do you look at numbers that tell you how the bus...</t>
+          <t>If you had to step out for three months starting Monday, w...</t>
         </is>
       </c>
       <c r="D285" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E285" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F285" s="7" t="inlineStr"/>
+          <t>A named person who already does most of it</t>
+        </is>
+      </c>
+      <c r="F285" s="7" t="inlineStr">
+        <is>
+          <t>someone who already does most of it</t>
+        </is>
+      </c>
       <c r="G285" s="5" t="inlineStr"/>
-      <c r="H285" s="3" t="inlineStr">
-        <is>
-          <t>no_data (90)</t>
-        </is>
-      </c>
-      <c r="I285" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="H285" s="3" t="inlineStr"/>
+      <c r="I285" s="3" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="5" t="n">
@@ -16192,21 +16186,25 @@
       </c>
       <c r="D286" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E286" s="7" t="inlineStr">
         <is>
-          <t>A named person who already does most of it</t>
+          <t>Someone would step up, but they'd struggle</t>
         </is>
       </c>
       <c r="F286" s="7" t="inlineStr">
         <is>
-          <t>someone who already does most of it</t>
+          <t>someone who'd struggle</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr"/>
-      <c r="H286" s="3" t="inlineStr"/>
+      <c r="H286" s="3" t="inlineStr">
+        <is>
+          <t>no_2ic (65)</t>
+        </is>
+      </c>
       <c r="I286" s="3" t="inlineStr"/>
     </row>
     <row r="287">
@@ -16225,23 +16223,23 @@
       </c>
       <c r="D287" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E287" s="7" t="inlineStr">
         <is>
-          <t>Someone would step up, but they'd struggle</t>
+          <t>Nobody</t>
         </is>
       </c>
       <c r="F287" s="7" t="inlineStr">
         <is>
-          <t>someone who'd struggle</t>
+          <t>nobody</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr"/>
       <c r="H287" s="3" t="inlineStr">
         <is>
-          <t>no_2ic (65)</t>
+          <t>no_2ic (100), key_person (90)</t>
         </is>
       </c>
       <c r="I287" s="3" t="inlineStr"/>
@@ -16262,63 +16260,59 @@
       </c>
       <c r="D288" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E288" s="7" t="inlineStr">
         <is>
-          <t>Nobody</t>
-        </is>
-      </c>
-      <c r="F288" s="7" t="inlineStr">
-        <is>
-          <t>nobody</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F288" s="7" t="inlineStr"/>
       <c r="G288" s="5" t="inlineStr"/>
       <c r="H288" s="3" t="inlineStr">
         <is>
-          <t>no_2ic (100), key_person (90)</t>
-        </is>
-      </c>
-      <c r="I288" s="3" t="inlineStr"/>
+          <t>no_2ic (80)</t>
+        </is>
+      </c>
+      <c r="I288" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B289" s="6" t="inlineStr">
         <is>
-          <t>q48</t>
+          <t>q49</t>
         </is>
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>If you had to step out for three months starting Monday, w...</t>
+          <t>If you sold the business tomorrow, how long would the buye...</t>
         </is>
       </c>
       <c r="D289" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E289" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F289" s="7" t="inlineStr"/>
+          <t>Not at all, they could take over</t>
+        </is>
+      </c>
+      <c r="F289" s="7" t="inlineStr">
+        <is>
+          <t>a buyer wouldn't need you at all</t>
+        </is>
+      </c>
       <c r="G289" s="5" t="inlineStr"/>
-      <c r="H289" s="3" t="inlineStr">
-        <is>
-          <t>no_2ic (80)</t>
-        </is>
-      </c>
-      <c r="I289" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="H289" s="3" t="inlineStr"/>
+      <c r="I289" s="3" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="5" t="n">
@@ -16336,21 +16330,25 @@
       </c>
       <c r="D290" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E290" s="7" t="inlineStr">
         <is>
-          <t>Not at all, they could take over</t>
+          <t>A few weeks of handover</t>
         </is>
       </c>
       <c r="F290" s="7" t="inlineStr">
         <is>
-          <t>not at all</t>
+          <t>a buyer would need you for a few weeks of handover</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr"/>
-      <c r="H290" s="3" t="inlineStr"/>
+      <c r="H290" s="3" t="inlineStr">
+        <is>
+          <t>owner_trapped (35)</t>
+        </is>
+      </c>
       <c r="I290" s="3" t="inlineStr"/>
     </row>
     <row r="291">
@@ -16369,23 +16367,23 @@
       </c>
       <c r="D291" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E291" s="7" t="inlineStr">
         <is>
-          <t>A few weeks of handover</t>
+          <t>Six to twelve months</t>
         </is>
       </c>
       <c r="F291" s="7" t="inlineStr">
         <is>
-          <t>a few weeks</t>
+          <t>a buyer would need you for the best part of a year</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr"/>
       <c r="H291" s="3" t="inlineStr">
         <is>
-          <t>owner_trapped (35)</t>
+          <t>owner_trapped (80)</t>
         </is>
       </c>
       <c r="I291" s="3" t="inlineStr"/>
@@ -16406,23 +16404,23 @@
       </c>
       <c r="D292" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E292" s="7" t="inlineStr">
         <is>
-          <t>Six to twelve months</t>
+          <t>Years, or it doesn't work without me</t>
         </is>
       </c>
       <c r="F292" s="7" t="inlineStr">
         <is>
-          <t>the best part of a year</t>
+          <t>a buyer would need you for years, if it works without you at all</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr"/>
       <c r="H292" s="3" t="inlineStr">
         <is>
-          <t>owner_trapped (80)</t>
+          <t>owner_trapped (100), key_person (90)</t>
         </is>
       </c>
       <c r="I292" s="3" t="inlineStr"/>
@@ -16443,63 +16441,59 @@
       </c>
       <c r="D293" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E293" s="7" t="inlineStr">
         <is>
-          <t>Years, or it doesn't work without me</t>
-        </is>
-      </c>
-      <c r="F293" s="7" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
+          <t>Never thought about it</t>
+        </is>
+      </c>
+      <c r="F293" s="7" t="inlineStr"/>
       <c r="G293" s="5" t="inlineStr"/>
       <c r="H293" s="3" t="inlineStr">
         <is>
-          <t>owner_trapped (100), key_person (90)</t>
-        </is>
-      </c>
-      <c r="I293" s="3" t="inlineStr"/>
+          <t>owner_trapped (70), no_succession (70)</t>
+        </is>
+      </c>
+      <c r="I293" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B294" s="6" t="inlineStr">
         <is>
-          <t>q49</t>
+          <t>q50</t>
         </is>
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>If you sold the business tomorrow, how long would the buye...</t>
+          <t>Is there a plan for what happens to the business if you st...</t>
         </is>
       </c>
       <c r="D294" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E294" s="7" t="inlineStr">
         <is>
-          <t>Never thought about it</t>
-        </is>
-      </c>
-      <c r="F294" s="7" t="inlineStr"/>
+          <t>Yes, written down</t>
+        </is>
+      </c>
+      <c r="F294" s="7" t="inlineStr">
+        <is>
+          <t>a written plan</t>
+        </is>
+      </c>
       <c r="G294" s="5" t="inlineStr"/>
-      <c r="H294" s="3" t="inlineStr">
-        <is>
-          <t>owner_trapped (70), no_succession (70)</t>
-        </is>
-      </c>
-      <c r="I294" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="H294" s="3" t="inlineStr"/>
+      <c r="I294" s="3" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="5" t="n">
@@ -16517,21 +16511,25 @@
       </c>
       <c r="D295" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E295" s="7" t="inlineStr">
         <is>
-          <t>Yes, written down</t>
+          <t>A rough idea in my head</t>
         </is>
       </c>
       <c r="F295" s="7" t="inlineStr">
         <is>
-          <t>a written plan</t>
+          <t>a rough idea</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr"/>
-      <c r="H295" s="3" t="inlineStr"/>
+      <c r="H295" s="3" t="inlineStr">
+        <is>
+          <t>no_succession (60)</t>
+        </is>
+      </c>
       <c r="I295" s="3" t="inlineStr"/>
     </row>
     <row r="296">
@@ -16550,23 +16548,23 @@
       </c>
       <c r="D296" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E296" s="7" t="inlineStr">
         <is>
-          <t>A rough idea in my head</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F296" s="7" t="inlineStr">
         <is>
-          <t>a rough idea</t>
+          <t>nothing</t>
         </is>
       </c>
       <c r="G296" s="5" t="inlineStr"/>
       <c r="H296" s="3" t="inlineStr">
         <is>
-          <t>no_succession (60)</t>
+          <t>no_succession (95)</t>
         </is>
       </c>
       <c r="I296" s="3" t="inlineStr"/>
@@ -16587,63 +16585,59 @@
       </c>
       <c r="D297" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E297" s="7" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F297" s="7" t="inlineStr">
-        <is>
-          <t>nothing</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F297" s="7" t="inlineStr"/>
       <c r="G297" s="5" t="inlineStr"/>
       <c r="H297" s="3" t="inlineStr">
         <is>
-          <t>no_succession (95)</t>
-        </is>
-      </c>
-      <c r="I297" s="3" t="inlineStr"/>
+          <t>no_succession (80)</t>
+        </is>
+      </c>
+      <c r="I297" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B298" s="6" t="inlineStr">
         <is>
-          <t>q50</t>
+          <t>q51</t>
         </is>
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>Is there a plan for what happens to the business if you st...</t>
+          <t>Have you personally guaranteed any of the business's debt,...</t>
         </is>
       </c>
       <c r="D298" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E298" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F298" s="7" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F298" s="7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="G298" s="5" t="inlineStr"/>
-      <c r="H298" s="3" t="inlineStr">
-        <is>
-          <t>no_succession (80)</t>
-        </is>
-      </c>
-      <c r="I298" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="H298" s="3" t="inlineStr"/>
+      <c r="I298" s="3" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="5" t="n">
@@ -16661,21 +16655,25 @@
       </c>
       <c r="D299" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E299" s="7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes, a small amount</t>
         </is>
       </c>
       <c r="F299" s="7" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>a small amount</t>
         </is>
       </c>
       <c r="G299" s="5" t="inlineStr"/>
-      <c r="H299" s="3" t="inlineStr"/>
+      <c r="H299" s="3" t="inlineStr">
+        <is>
+          <t>personal_guarantee (45)</t>
+        </is>
+      </c>
       <c r="I299" s="3" t="inlineStr"/>
     </row>
     <row r="300">
@@ -16694,23 +16692,23 @@
       </c>
       <c r="D300" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E300" s="7" t="inlineStr">
         <is>
-          <t>Yes, a small amount</t>
+          <t>Yes, significant</t>
         </is>
       </c>
       <c r="F300" s="7" t="inlineStr">
         <is>
-          <t>a small amount</t>
+          <t>a significant amount</t>
         </is>
       </c>
       <c r="G300" s="5" t="inlineStr"/>
       <c r="H300" s="3" t="inlineStr">
         <is>
-          <t>personal_guarantee (45)</t>
+          <t>personal_guarantee (95)</t>
         </is>
       </c>
       <c r="I300" s="3" t="inlineStr"/>
@@ -16731,63 +16729,59 @@
       </c>
       <c r="D301" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E301" s="7" t="inlineStr">
         <is>
-          <t>Yes, significant</t>
-        </is>
-      </c>
-      <c r="F301" s="7" t="inlineStr">
-        <is>
-          <t>a significant amount</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F301" s="7" t="inlineStr"/>
       <c r="G301" s="5" t="inlineStr"/>
       <c r="H301" s="3" t="inlineStr">
         <is>
-          <t>personal_guarantee (95)</t>
-        </is>
-      </c>
-      <c r="I301" s="3" t="inlineStr"/>
+          <t>personal_guarantee (75), no_data (60)</t>
+        </is>
+      </c>
+      <c r="I301" s="3" t="inlineStr">
+        <is>
+          <t>Not sure, scores nothing and feeds data blindness</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B302" s="6" t="inlineStr">
         <is>
-          <t>q51</t>
+          <t>q52</t>
         </is>
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>Have you personally guaranteed any of the business's debt,...</t>
+          <t>How well does the way you spend your week match what you w...</t>
         </is>
       </c>
       <c r="D302" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E302" s="7" t="inlineStr">
         <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F302" s="7" t="inlineStr"/>
+          <t>Well, this is roughly what I signed up for</t>
+        </is>
+      </c>
+      <c r="F302" s="7" t="inlineStr">
+        <is>
+          <t>close to what you signed up for</t>
+        </is>
+      </c>
       <c r="G302" s="5" t="inlineStr"/>
-      <c r="H302" s="3" t="inlineStr">
-        <is>
-          <t>personal_guarantee (75), no_data (60)</t>
-        </is>
-      </c>
-      <c r="I302" s="3" t="inlineStr">
-        <is>
-          <t>Not sure, scores nothing and feeds data blindness</t>
-        </is>
-      </c>
+      <c r="H302" s="3" t="inlineStr"/>
+      <c r="I302" s="3" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="5" t="n">
@@ -16805,21 +16799,25 @@
       </c>
       <c r="D303" s="6" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E303" s="7" t="inlineStr">
         <is>
-          <t>Well, this is roughly what I signed up for</t>
+          <t>Partly</t>
         </is>
       </c>
       <c r="F303" s="7" t="inlineStr">
         <is>
-          <t>close to what you signed up for</t>
+          <t>only partly a match for what you wanted</t>
         </is>
       </c>
       <c r="G303" s="5" t="inlineStr"/>
-      <c r="H303" s="3" t="inlineStr"/>
+      <c r="H303" s="3" t="inlineStr">
+        <is>
+          <t>model_misfit (50)</t>
+        </is>
+      </c>
       <c r="I303" s="3" t="inlineStr"/>
     </row>
     <row r="304">
@@ -16838,23 +16836,23 @@
       </c>
       <c r="D304" s="6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E304" s="7" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Not at all, I'm doing the opposite of what I wanted</t>
         </is>
       </c>
       <c r="F304" s="7" t="inlineStr">
         <is>
-          <t>only partly a match for what you wanted</t>
+          <t>the opposite of what you wanted</t>
         </is>
       </c>
       <c r="G304" s="5" t="inlineStr"/>
       <c r="H304" s="3" t="inlineStr">
         <is>
-          <t>model_misfit (50)</t>
+          <t>model_misfit (95)</t>
         </is>
       </c>
       <c r="I304" s="3" t="inlineStr"/>
@@ -16875,66 +16873,29 @@
       </c>
       <c r="D305" s="6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>z</t>
         </is>
       </c>
       <c r="E305" s="7" t="inlineStr">
         <is>
-          <t>Not at all, I'm doing the opposite of what I wanted</t>
-        </is>
-      </c>
-      <c r="F305" s="7" t="inlineStr">
-        <is>
-          <t>the opposite of what you wanted</t>
-        </is>
-      </c>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="F305" s="7" t="inlineStr"/>
       <c r="G305" s="5" t="inlineStr"/>
       <c r="H305" s="3" t="inlineStr">
         <is>
-          <t>model_misfit (95)</t>
-        </is>
-      </c>
-      <c r="I305" s="3" t="inlineStr"/>
-    </row>
-    <row r="306">
-      <c r="A306" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="B306" s="6" t="inlineStr">
-        <is>
-          <t>q52</t>
-        </is>
-      </c>
-      <c r="C306" s="3" t="inlineStr">
-        <is>
-          <t>How well does the way you spend your week match what you w...</t>
-        </is>
-      </c>
-      <c r="D306" s="6" t="inlineStr">
-        <is>
-          <t>z</t>
-        </is>
-      </c>
-      <c r="E306" s="7" t="inlineStr">
-        <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="F306" s="7" t="inlineStr"/>
-      <c r="G306" s="5" t="inlineStr"/>
-      <c r="H306" s="3" t="inlineStr">
-        <is>
           <t>model_misfit (60)</t>
         </is>
       </c>
-      <c r="I306" s="3" t="inlineStr">
+      <c r="I305" s="3" t="inlineStr">
         <is>
           <t>Not sure, scores nothing and feeds data blindness</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I306"/>
+  <autoFilter ref="A2:I305"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -17401,12 +17362,12 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>the balance takes {q7.band} to land</t>
+          <t>the balance lands {q7.band}</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>the balance takes {q7.exact} days to land</t>
+          <t>the balance lands {q7.exact} days later</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -17451,7 +17412,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>you've been delaying payments {q6.band}</t>
+          <t>{q6.band}</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
@@ -17779,7 +17740,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>something you wanted to grow has stalled for want of anyone to hand it to, {q14.band}</t>
+          <t>{q14.band}</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr"/>
@@ -18019,7 +17980,7 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>you've turned work away or pushed start dates {q17.band}</t>
+          <t>{q17.band}</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr"/>
@@ -18065,7 +18026,7 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>a typical job is only ready {q19.band}</t>
+          <t>a typical job is ready {q19.band}</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr"/>
@@ -18641,7 +18602,7 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>and they find out what you charge {q30.band}</t>
+          <t>they find out what you charge {q30.band}</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr"/>
@@ -18904,7 +18865,7 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>you're doing {q35.band} to generate more</t>
+          <t>{q35.band}</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr"/>
@@ -19171,7 +19132,7 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>you last raised prices {q38.band}</t>
+          <t>{q38.band}</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr"/>
@@ -19673,7 +19634,11 @@
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr"/>
-      <c r="F4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>You weren't sure where your customers actually come from, which usually means one channel is doing more of the work than you think. A channel can change without asking you first, and an algorithm shift, a search update or one referrer going quiet can halve your enquiries inside a month.</t>
+        </is>
+      </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
           <t>Stand up a second channel before you need it, and give it ninety days before you judge it. One channel is a decision somebody else gets to make on your behalf.</t>
@@ -20187,7 +20152,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Sold tomorrow, a buyer would need you to stay {q49.band}. That's the number that decides what the business is worth to anyone but you, and it's the same number that decides whether you can ever step back.</t>
+          <t>Sold tomorrow, {q49.band}. How long that handover runs is what decides whether the business is worth anything to anyone but you, and it's the same thing that decides whether you can ever step back.</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr"/>

--- a/diagnostic/Business-Diagnostic-Spec.xlsx
+++ b/diagnostic/Business-Diagnostic-Spec.xlsx
@@ -14,30 +14,26 @@
     <sheet name="Report, constraint" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Report, minor" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Report, risk flags" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Report, risk framing" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Report, minor risk" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Report, compound" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Report, don't do yet" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Report, open and close" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Thresholds" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Logic" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Data slots" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Report, risk section" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Report, don't do yet" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Report, open and close" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Thresholds" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Logic" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Data slots" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Questions'!$A$2:$J$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Answer options'!$A$2:$I$305</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Constraints and order'!$A$2:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Report, constraint'!$A$2:$E$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Report, constraint'!$A$2:$E$107</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Report, minor'!$A$2:$D$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Report, risk flags'!$A$2:$H$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Report, risk framing'!$A$2:$D$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Report, minor risk'!$A$2:$C$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Report, compound'!$A$2:$E$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Report, don''t do yet'!$A$2:$C$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Report, open and close'!$A$2:$E$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Thresholds'!$A$2:$C$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Logic'!$A$1:$B$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Data slots'!$A$2:$F$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Report, risk section'!$A$2:$B$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Report, don''t do yet'!$A$2:$C$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Report, open and close'!$A$2:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Thresholds'!$A$2:$C$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Logic'!$A$1:$B$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Data slots'!$A$2:$F$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -525,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -735,94 +731,70 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Report, risk framing</t>
+          <t>Report, risk section</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>The three family blocks that open the risk section.</t>
+          <t>The line that opens the risk section.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Report, minor risk</t>
+          <t>Report, don't do yet</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>One line per risk, printed when it is the second family's loudest finding.</t>
+          <t>The closing section. What not to touch until the constraint is fixed.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Report, compound</t>
+          <t>Report, open and close</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>The blocks that fire when a risk and the constraint are the same problem seen twice.</t>
+          <t>The opening and closing of the report, including the three opening variants.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Report, don't do yet</t>
+          <t>Thresholds</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>The closing section. What not to touch until the constraint is fixed.</t>
+          <t>Every tunable number, and what moving it does.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Report, open and close</t>
+          <t>Logic</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>The opening and closing of the report, including the three opening variants.</t>
+          <t>How the engine picks the primary, the minor, and the risks. Read this before changing a threshold.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Thresholds</t>
+          <t>Data slots</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Every tunable number, and what moving it does.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Logic</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>How the engine picks the primary, the minor, and the risks. Read this before changing a threshold.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Data slots</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Every variable, every phrase it can print, and which report blocks quote it. Check here before changing a band phrase, because it shows you the sentences that band lands in.</t>
         </is>
@@ -839,42 +811,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="112" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="98" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>One compound block prints at most, the lowest priority number that matches. These are the blocks that make the report read as written rather than assembled, so they are worth the most editing attention.</t>
+          <t>Blank line between paragraphs is written as two newlines in the source. Keep paragraphs short.</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Constraint</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Risk flag</t>
+          <t>Variant</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>When it is used</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Block. Prints when both are present</t>
+          <t>Wording</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
@@ -884,380 +856,295 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>cashflow</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Opening</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>key_client</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>1</v>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Used whenever a constraint actually failed</t>
+        </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Cash flow is your constraint and one customer carries {q41.band} of your revenue. That customer is also setting your payment terms, which means they're setting your cash position. Fixing terms with them is worth more than everything else on the list.</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>{q41.band}</t>
-        </is>
-      </c>
+          <t>Everything below is calculated on your answers. It's a guide rather than a custom diagnostic, so read the report as a rough shape of what your current challenges are and what solutions may look like.
+It names your biggest single constraint. There is likely more, and there may be other things wrong, there always are. They're not listed in here because the order you fix things in matters. Fix the constraints and risks in your business, then come back and get an updated report.</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>cashflow</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Opening</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>personal_guarantee</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>2</v>
+          <t>wellRun</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Nothing cleared the floor. Nothing is failing</t>
+        </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>You're cash constrained and personally guaranteeing the business's obligations. That's the combination that follows people home. Get the buffer built before you take on another dollar of guaranteed debt.</t>
+          <t>Everything below is calculated on your answers. Nothing in them is close to failing, which is a real result and rarer than you'd think.
+What follows is the tightest thing in the business rather than a problem. Treat it as where the next bit of growth comes from, not something to fix.</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>cashflow</t>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Opening</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>no_contracts</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>2</v>
+          <t>noneSevere</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Nothing failed outright but something is tight</t>
+        </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Cash flow is your constraint and your work isn't contracted. You're funding jobs upfront for customers who can walk without penalty. Deposits and written terms deal with both at once.</t>
+          <t>Everything below is calculated on your answers. Nothing in them is screaming, which is worth knowing on its own.
+What follows is the tightest thing in the business rather than something that's failing outright. It's the next thing to work on, not an emergency.</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>cashflow</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Opening</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>no_data</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>3</v>
+          <t>tooUnsure</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Too many Not sure answers to stand behind a diagnosis</t>
+        </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>You're cash constrained and you're not looking at the numbers often enough to see it coming. A thirteen week cash forecast, updated weekly, is the highest value hour in your month right now.</t>
+          <t>Everything below is calculated on your answers, and there were a lot of them you couldn't answer, so read it as provisional.
+The finding below is the best available reading of what you did tell us. The bigger issue is that the business isn't visible to you, and that's covered in the risks. Come back and run it again once you can answer the numbers.</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>demand</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Opening</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>key_channel</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>1</v>
+          <t>privacy</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Small print under the opening, on every report</t>
+        </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>You're demand constrained and the one channel you have isn't producing. A second channel is the fix and it's also the risk mitigation. Same move, two problems.</t>
+          <t>We do not use any AI in this tool, and none of your data is sent or stored offsite.</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>demand</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Heading</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>key_client</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>2</v>
+          <t>titleUnsure</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Replaces the constraint heading when there is not enough to call it</t>
+        </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>You're quiet and one customer carries {q41.band} of your revenue. Together those mean the business is one phone call from a crisis. New demand is urgent here for reasons that have nothing to do with growth.</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>{q41.band}</t>
-        </is>
-      </c>
+          <t>There isn't enough here to call it</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>fulfilment</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Body</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>no_process</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>1</v>
+          <t>looseBody</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Replaces the constraint block when nothing is failing</t>
+        </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>You're fulfilment constrained and almost nothing is written down. Those aren't two findings. Undocumented work is slow work, and it's why adding people hasn't given you the output you expected.</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr"/>
+          <t>Nothing in here is failing, so there's no evidence to walk you through. What you've got is {d.primaryShort} sitting as the tightest of the seven right now, which makes it the likeliest place the next bit of growth comes from. The actions below are worth doing and none of them are urgent.</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>{d.primaryShort}</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>fulfilment</t>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Body</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>key_employee</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>1</v>
+          <t>unsureBody</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Replaces the constraint block when there were too many Not sure answers</t>
+        </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>You're at capacity and one person holds how the work actually gets done. Every hire you make is rate limited by the one person who has to train them. Getting that knowledge out of one head is what unlocks the capacity.</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr"/>
+          <t>There isn't enough here to point at one thing with any confidence. On what you did answer, {d.primaryShort} is the tightest of the seven, so read the actions below as a starting point rather than a diagnosis.
+The risk section is the part of this report to take seriously. Not being able to answer the questions is the finding, and it's the one worth acting on first.</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>{d.primaryShort}</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>fulfilment</t>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Closing</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>key_person</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>2</v>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Normal close</t>
+        </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>You're at capacity and the business depends on one person to function. Adding work to that arrangement adds it to them. The capacity you're missing is currently locked in one diary.</t>
+          <t>That's the diagnosis. One constraint, the risks sitting around it, and the things to leave alone while you fix it.
+Work the constraint and check back in ninety days. That's long enough for it to move and short enough that you'll still remember what you changed.</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>margin</t>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Closing</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>no_data</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>1</v>
+          <t>loose</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Close used when nothing is failing</t>
+        </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Margin is your constraint and you don't know which work makes money. You're almost certainly subsidising some customers with others, and until you can see which, every pricing decision you make is a guess.</t>
+          <t>That's the read. One thing to push on, and nothing in the way of it.
+Run this again in ninety days, or whenever something material changes. The constraint moves as the business grows, and the answer you get next time probably won't be this one.</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>margin</t>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Closing</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>key_client</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>2</v>
+          <t>unsure</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Close used when there were too many Not sure answers</t>
+        </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Margin is tight and one customer carries {q41.band} of your revenue. Big customers get big customer pricing, and yours is probably the one holding the margin down. Repricing them is the fastest lever you have, and it's the scariest, which is why it hasn't happened.</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>{q41.band}</t>
-        </is>
-      </c>
+          <t>That's as far as your answers go. One provisional reading, and a clear picture of what the business can't currently tell you.
+Get the numbers visible, then run this again. The second time through it will be worth something.</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>offer</t>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Closing</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>key_channel</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>The offer is your constraint and nearly all your enquiries come through one channel. That's why this feels like a demand problem. The channel is working. The thing it's delivering people to isn't.</t>
-        </is>
-      </c>
+          <t>cta</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Call to action. Deliberately empty, still an open question</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
       <c r="E14" s="8" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>talent</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>key_person</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Your constraint is talent and your key person risk is the same thing seen from the other side. The layer that doesn't exist is the reason everything routes through one person, so hiring the role deals with both. Treat it as one job rather than two.</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>talent</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>owner_trapped</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>You're talent constrained and the business is close to unsellable, and both of those come from the same fact. The business runs on you. The role you haven't hired is also the thing standing between you and owning something a buyer would want.</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>talent</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>no_2ic</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>The missing layer and the missing second in command are one problem with two names. You don't need a succession plan and a hire. You need the hire, and the succession plan writes itself afterwards.</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>talent</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>key_client</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>You're carrying a talent gap and a single customer worth {q41.band} of revenue. Building the layer while one customer can end your year is the sequencing error we'd flag hardest. Get that customer onto a term agreement before you take on the salary.</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>{q41.band}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>no_data</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Retention is your constraint and you don't know why customers leave. Those are the same sentence. Ten phone calls this week would find the leak, and nothing you do before those calls is anything but a guess.</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:E19"/>
+  <autoFilter ref="A2:E14"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -1271,1069 +1158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="122" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Telling an owner to stop doing the wrong thing is usually worth more than another action item, because they are already mid action on it. This section does not print when nothing is failing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Constraint</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Part</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>Wording</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Lead line</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>Until the cash timing is fixed, leave these alone.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Item 1</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Don't chase bigger jobs. Bigger jobs mean bigger upfront costs and longer payment cycles.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Item 2</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Don't hire. Wages are the least flexible cost you can add to a cash problem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Item 3</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Don't buy equipment outright. Finance it, even if the interest annoys you.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Item 4</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Don't discount to get paid faster. That's borrowing at a rate you'd never accept from a bank.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Item 5</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Don't increase marketing spend. More demand you can't fund makes the hole deeper.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>talent</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Lead line</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Until the layer exists, leave these alone.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>talent</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Item 1</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Don't hire another doer. Every one you add reports to you, and you're the bottleneck.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>talent</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Item 2</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Don't take on a new market, product or location. All three land on your desk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>talent</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Item 3</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Don't start anything that needs your attention for six months.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>talent</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Item 4</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Don't increase lead generation. The work you win still has to route through you.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>talent</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Item 5</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Don't redraw the org chart. What's missing is a person who doesn't exist, not a diagram.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>fulfilment</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Lead line</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Until you can deliver what you've already sold, leave these alone.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>fulfilment</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Item 1</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Don't chase new customers. You'd be damaging the ones you have to serve the ones you win.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>fulfilment</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Item 2</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Don't increase marketing spend. Adding demand to a full pipeline is the classic accelerant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>fulfilment</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Item 3</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Don't launch a new service line. New work is slow work while the process is still being learned.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>fulfilment</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Item 4</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Don't drop your prices. You've got more demand than capacity, which is the one time raising them is easy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>fulfilment</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Item 5</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Don't promise a shorter lead time to win a job. That's where the quality problem starts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Lead line</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Until customers stay, leave these alone.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Item 1</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Don't spend more on acquisition. You'd be paying to fill a bucket with a hole in it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Item 2</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Don't raise prices. Value perception is already the problem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Item 3</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>Don't add a new product for existing customers who aren't buying the current one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Item 4</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Don't expand into a new market. You'd take the retention problem with you.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>Item 5</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Don't run a loyalty programme. A discount doesn't fix a value gap, it confirms one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>offer</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Lead line</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Until the offer lands, leave these alone.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>offer</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Item 1</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Don't buy more leads. You'd pay more money for the same conversion rate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>offer</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>Item 2</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Don't hire a salesperson. They'd fail against the same offer you're failing against.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>offer</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>Item 3</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Don't cut your price. Price is rarely the real reason, and you can't test it while the offer is unclear.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>offer</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>Item 4</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Don't add more options. More choice is part of why these deals are stalling.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>offer</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>Item 5</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Don't rebrand. The words are the problem, not the logo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>demand</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>Lead line</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>Until enquiries lift, leave these alone.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>demand</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>Item 1</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Don't hire. You'd be adding capacity to capacity you already can't fill.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>demand</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>Item 2</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Don't build a new product. The one you have hasn't been shown to enough people.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>demand</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>Item 3</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Don't cut prices to stimulate demand. It rarely moves volume, and it permanently resets what customers expect to pay.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>demand</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Item 4</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Don't spread across five channels at once. One channel run properly beats five run badly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>demand</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Item 5</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Don't wait for referrals to pick back up. Referral volume follows the number of customers you have, and that's the number that's short.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>margin</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Lead line</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Until the margin moves, leave these alone.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>margin</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>Item 1</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>Don't chase volume. More work at this margin is more risk for the same money.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>margin</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>Item 2</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>Don't hire. Every head you add at this margin needs a lot of revenue standing behind it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>margin</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>Item 3</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>Don't take the big thin job because it's good for the brand. Reputation doesn't pay wages.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>margin</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>Item 4</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>Don't discount anything. There's nothing left to give away.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>margin</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>Item 5</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>Don't invest in growth. Growing an unprofitable model makes it unprofitable faster.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A2:C44"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="98" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Blank line between paragraphs is written as two newlines in the source. Keep paragraphs short.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Variant</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>When it is used</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>Wording</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>Variables in this row</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Used whenever a constraint actually failed</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>Everything below comes out of your answers and nothing else. It's a guide rather than a custom diagnostic, so read the benchmarks as a rough shape of what good looks like at your size, not as a measurement of you against your industry.
-It names one constraint. There'll be other things wrong, there always are. They're not in here because the order you fix them in matters more than the list.</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>wellRun</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Nothing cleared the floor. Nothing is failing</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Nothing in your answers is close to failing. That's a real result and it's rarer than you'd think.
-What follows is the tightest thing in the business rather than a problem. Treat it as where the next bit of growth will come from, not something to fix.</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>noneSevere</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Nothing failed outright but something is tight</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Nothing in your answers is screaming. That's worth knowing on its own, and it's rarer than you'd think.
-What follows is the tightest thing in the business right now rather than something that's failing outright. Treat it as the next thing to work on, not an emergency.</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>tooUnsure</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Too many Not sure answers to stand behind a diagnosis</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>There were a lot of questions in here you couldn't answer, so read what follows as provisional.
-The finding below is the best available reading of what you did tell us. The bigger issue is that the business isn't visible to you, and that's covered in the risk section. Come back and run this again once you can answer the numbers.</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Body</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>looseBody</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Replaces the constraint block when nothing is failing</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Nothing in here is failing, so there's no evidence to walk you through. What you've got is {d.primaryShort} sitting as the tightest of the seven right now, which makes it the likeliest place the next bit of growth comes from. The actions below are worth doing and none of them are urgent.</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>{d.primaryShort}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Body</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>unsureBody</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Replaces the constraint block when there were too many Not sure answers</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>There isn't enough here to point at one thing with any confidence. On what you did answer, {d.primaryShort} is the tightest of the seven, so read the actions below as a starting point rather than a diagnosis.
-The risk section is the part of this report to take seriously. Not being able to answer the questions is the finding, and it's the one worth acting on first.</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>{d.primaryShort}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Closing</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Normal close</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>That's the diagnosis. One constraint, the risks sitting around it, and the things to leave alone while you fix it.
-Work the constraint and check back in ninety days. That's long enough for it to move and short enough that you'll still remember what you changed.</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Closing</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>loose</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Close used when nothing is failing</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>That's the read. One thing to push on, and nothing in the way of it.
-Run this again in ninety days, or whenever something material changes. The constraint moves as the business grows, and the answer you get next time probably won't be this one.</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Closing</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>unsure</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Close used when there were too many Not sure answers</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>That's as far as your answers go. One provisional reading, and a clear picture of what the business can't currently tell you.
-Get the numbers visible, then run this again. The second time through it will be worth something.</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Closing</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>cta</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Call to action. Deliberately empty, still an open question</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="8" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A2:E12"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2413,80 +1238,65 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>RISK_FAMILY_PRINT</t>
+          <t>FLAG_PRINT</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>A risk family has to reach this before its section prints at all.</t>
+          <t>An individual flag has to reach this before it is named. Below it the flag still counts toward its family score.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>MINOR_RISK_PRINT</t>
+          <t>MAX_FLAGS_SHOWN</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>The second family has to reach this before one line about it prints.</t>
+          <t>Hard cap on how many risks get named, across all three families. Four keeps the report short and certain.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>FLAG_PRINT</t>
+          <t>NOT_SURE_DATA_FLAG</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>An individual flag has to reach this before it is named. Below it the flag still counts toward its family score.</t>
+          <t>This many Not sure answers raises data blindness on its own, regardless of which questions they were.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>MAX_FLAGS_SHOWN</t>
+          <t>MAX_ACTIONS</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Hard cap on how many individual risks get named. Three keeps the report short and certain.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>NOT_SURE_DATA_FLAG</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>This many Not sure answers raises data blindness on its own, regardless of which questions they were.</t>
+          <t>Hard cap on how many fix actions print for the constraint. Conditional actions that did not fire never count toward it.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C10"/>
+  <autoFilter ref="A2:C9"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
@@ -2494,7 +1304,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2665,7 +1475,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3797,7 +2607,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>compound [15] / text  compound [17] / text  compound [4] / text  compound [5] / text  riskDef / key_client / banded</t>
+          <t>riskDef / key_client / banded</t>
         </is>
       </c>
     </row>
@@ -4374,7 +3184,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Tick everything that applies. Most businesses are more than one of these.</t>
+          <t>Tick everything that applies.</t>
         </is>
       </c>
       <c r="G5" s="5" t="n">
@@ -17225,7 +16035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17265,7 +16075,7 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>Variables in this row</t>
+          <t>Variables, or when a fix action prints</t>
         </is>
       </c>
     </row>
@@ -17282,7 +16092,7 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Your constraint is cash flow</t>
+          <t>You are {c} constrained</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr"/>
@@ -17301,7 +16111,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>The tightest thing is cash flow</t>
+          <t>The tightest thing is {c}</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr"/>
@@ -17496,11 +16306,15 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Take a deposit on every job. Half where you can get it, something where you can't. A deposit is the cheapest funding you'll ever raise.</t>
+          <t>You take nothing upfront, which is this whole problem in one answer. Change that before anything else on this list.</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="8" t="inlineStr"/>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>q54 is e/f</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -17515,11 +16329,15 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Invoice the day the work is finished rather than at the end of the month. Most of the wait is yours, not theirs.</t>
+          <t>Take a deposit on every job. Fifty percent thirty days out and the balance the week before, so the money is in before your costs go out.</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr"/>
-      <c r="E14" s="8" t="inlineStr"/>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -17534,11 +16352,15 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Put terms in writing before the job starts, and chase on day one past due. Not week two.</t>
+          <t>Line the deposit up to land before your cost of goods does. On jobs where the number moves on the day, charge the balance afterwards and refund the difference.</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr"/>
-      <c r="E15" s="8" t="inlineStr"/>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -17553,11 +16375,15 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Get an overdraft or a facility in place while you're still profitable. Banks lend to businesses that don't look like they need it.</t>
+          <t>Invoice within twenty four hours of the job finishing, rather than at the end of the month.</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr"/>
-      <c r="E16" s="8" t="inlineStr"/>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -17572,49 +16398,61 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Find out which of your top five customers pays slowest, then reprice or re term that one.</t>
+          <t>Collect what's already overdue before you chase anything new. It's the cheapest money available to you.</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr"/>
-      <c r="E17" s="8" t="inlineStr"/>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>q55 is c/d</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>talent</t>
+          <t>cashflow</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Fix action 6</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Your constraint is talent</t>
+          <t>Put terms in writing before the next job starts, and chase on day one past due.</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr"/>
-      <c r="E18" s="8" t="inlineStr"/>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>q45 is c/d</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>talent</t>
+          <t>cashflow</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Title, nothing failing</t>
+          <t>Fix action 7</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>The tightest thing is talent</t>
+          <t>Get a facility in place while you're still profitable. Banks lend to businesses that don't look like they need it.</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr"/>
-      <c r="E19" s="8" t="inlineStr"/>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -17624,12 +16462,12 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Opening sentence 1</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Talent here means a missing layer, not missing hands.</t>
+          <t>You are {c} constrained</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr"/>
@@ -17643,20 +16481,16 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Opening sentence 2</t>
+          <t>Title, nothing failing</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>{d.unownedLayers}</t>
+          <t>The tightest thing is {c}</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr"/>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>{d.unownedLayers}</t>
-        </is>
-      </c>
+      <c r="E21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -17666,20 +16500,16 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Opening sentence 3</t>
+          <t>Opening sentence 1</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Most of last week went to {d.ownerTasks}.</t>
+          <t>Talent here means a missing layer, not missing hands.</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>{d.ownerTasks}</t>
-        </is>
-      </c>
+      <c r="E22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -17689,18 +16519,18 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 1</t>
+          <t>Opening sentence 2</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>the work that actually moves the business forward got {q56.band}</t>
+          <t>{d.unownedLayers}</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr"/>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>{q56.band}</t>
+          <t>{d.unownedLayers}</t>
         </is>
       </c>
     </row>
@@ -17712,18 +16542,18 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 2</t>
+          <t>Opening sentence 3</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>if you went dark for a month the business {q12.band}</t>
+          <t>Most of last week went to {d.ownerTasks}.</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr"/>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>{q12.band}</t>
+          <t>{d.ownerTasks}</t>
         </is>
       </c>
     </row>
@@ -17735,18 +16565,18 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 3</t>
+          <t>Evidence clause 1</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>{q14.band}</t>
+          <t>the work that actually moves the business forward got {q56.band}</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr"/>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>{q14.band}</t>
+          <t>{q56.band}</t>
         </is>
       </c>
     </row>
@@ -17758,16 +16588,20 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Evidence clause 2</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Hiring another pair of hands underneath you doesn't touch this. What's missing is a whole role that doesn't exist yet, and until it does, everything you add lands on the same desk.</t>
+          <t>if you went dark for a month the business {q12.band}</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr"/>
-      <c r="E26" s="8" t="inlineStr"/>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>{q12.band}</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -17777,16 +16611,20 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Fix, lead line</t>
+          <t>Evidence clause 3</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>One role. Named, hired, and given the authority to actually run what you hand over.</t>
+          <t>{q14.band}</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr"/>
-      <c r="E27" s="8" t="inlineStr"/>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>{q14.band}</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -17796,12 +16634,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Fix action 1</t>
+          <t>Closing</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Write down everything you did last week, then mark what only you could have done. What's left is the job description.</t>
+          <t>Hiring another pair of hands underneath you doesn't touch this. What's missing is a whole role that doesn't exist yet, and until it does, everything you add lands on the same desk.</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr"/>
@@ -17815,12 +16653,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Fix action 2</t>
+          <t>Fix, lead line</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Hire the layer rather than the hands. Another delivery person gives you more capacity, a person who runs delivery gives you your week back.</t>
+          <t>One role. Named, hired, and given the authority to actually run what you hand over.</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr"/>
@@ -17834,16 +16672,20 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Fix action 3</t>
+          <t>Fix action 1</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Hand over one whole area with the decisions attached. Half a handover is worse than none, because you keep the work and they get the confusion.</t>
+          <t>Every layer sits with you. Hire the one that would free the most of your week first, not the one that's easiest to fill.</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr"/>
-      <c r="E30" s="8" t="inlineStr"/>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>q11 is n</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -17853,16 +16695,20 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Fix action 4</t>
+          <t>Fix action 2</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Give it ninety days before you judge it. The first month of any handover looks like a mistake.</t>
+          <t>Write down everything you did last week, then mark what only you could have done. What's left is the job description.</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr"/>
-      <c r="E31" s="8" t="inlineStr"/>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -17872,73 +16718,89 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Fix action 5</t>
+          <t>Fix action 3</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Stop being the escalation point for the area you handed over. Send it back to them, in front of the team.</t>
+          <t>Hire the layer rather than the hands. Another delivery person gives you more capacity. A person who runs delivery gives you your week back.</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr"/>
-      <c r="E32" s="8" t="inlineStr"/>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>fulfilment</t>
+          <t>talent</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Fix action 4</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Your constraint is fulfilment</t>
+          <t>You've got more direct reports than one person can run properly. The hire that fixes this sits between you and most of them.</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr"/>
-      <c r="E33" s="8" t="inlineStr"/>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>q15 is d/e</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>fulfilment</t>
+          <t>talent</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Title, nothing failing</t>
+          <t>Fix action 5</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>The tightest thing is fulfilment</t>
+          <t>Hand over one whole area with the decisions attached. Half a handover leaves you doing the work and them carrying the confusion.</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr"/>
-      <c r="E34" s="8" t="inlineStr"/>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>fulfilment</t>
+          <t>talent</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Opening</t>
+          <t>Fix action 6</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>This is capacity, not capability. You know how to do the work and you can't get enough hours of it out the door.</t>
+          <t>Give it ninety days before you judge it, and stop being the escalation point for what you handed over.</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr"/>
-      <c r="E35" s="8" t="inlineStr"/>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -17948,24 +16810,16 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 1</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>you're running {q16.band}</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>you're running at {q16.exact}% booked</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>{q16.band}, {q16.exact}</t>
-        </is>
-      </c>
+          <t>You are {c} constrained</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr"/>
+      <c r="E36" s="8" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -17975,20 +16829,16 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 2</t>
+          <t>Title, nothing failing</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>{q17.band}</t>
+          <t>The tightest thing is {c}</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr"/>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>{q17.band}</t>
-        </is>
-      </c>
+      <c r="E37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -17998,20 +16848,16 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 3</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>lead times have {q18.band}</t>
+          <t>This is capacity, not capability. You know how to do the work and you can't get enough hours of it out the door.</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr"/>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>{q18.band}</t>
-        </is>
-      </c>
+      <c r="E38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -18021,18 +16867,22 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 4</t>
+          <t>Evidence clause 1</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>a typical job is ready {q19.band}</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr"/>
+          <t>you're running {q16.band}</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>you're running at {q16.exact}% booked</t>
+        </is>
+      </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>{q19.band}</t>
+          <t>{q16.band}, {q16.exact}</t>
         </is>
       </c>
     </row>
@@ -18044,16 +16894,20 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Evidence clause 2</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Nothing at the front of the business needs attention until the back of it can breathe. Anything you do to bring in more work right now gets paid for by the customers you already have.</t>
+          <t>{q17.band}</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr"/>
-      <c r="E40" s="8" t="inlineStr"/>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>{q17.band}</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -18063,16 +16917,20 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Fix, lead line</t>
+          <t>Evidence clause 3</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>More output from what you already have, before you buy any more of anything.</t>
+          <t>lead times have {q18.band}</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr"/>
-      <c r="E41" s="8" t="inlineStr"/>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>{q18.band}</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -18082,16 +16940,20 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Fix action 1</t>
+          <t>Evidence clause 4</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Find the one step everything queues behind. There's always one, and it's rarely the one people complain about.</t>
+          <t>a typical job is ready {q19.band}</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr"/>
-      <c r="E42" s="8" t="inlineStr"/>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>{q19.band}</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -18101,12 +16963,12 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Fix action 2</t>
+          <t>Closing</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Pull the work that doesn't need your best people off your best people. Most delivery teams lose a third of their week to things a junior could do.</t>
+          <t>Nothing at the front of the business needs attention until the back of it can breathe. Anything you do to bring in more work right now gets paid for by the customers you already have.</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr"/>
@@ -18120,12 +16982,12 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Fix action 3</t>
+          <t>Fix, lead line</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Stop selling the jobs that eat the most capacity for the least return, at least until the queue clears.</t>
+          <t>More output from what you already have, before you buy any more of anything.</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr"/>
@@ -18139,16 +17001,20 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Fix action 4</t>
+          <t>Fix action 1</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Quote your real lead time rather than your hopeful one. A blown promise costs you a customer you'd already won.</t>
+          <t>Find the one step everything queues behind, then put your next hour into that step and nothing else.</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr"/>
-      <c r="E45" s="8" t="inlineStr"/>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -18158,98 +17024,110 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Fix action 5</t>
+          <t>Fix action 2</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Add capacity last. Hiring into a broken process gets you a bigger broken process.</t>
+          <t>Write the five things that go wrong most often into one page checklists. Undocumented work is slow work.</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr"/>
-      <c r="E46" s="8" t="inlineStr"/>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>q46 is b/c/z</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>fulfilment</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Fix action 3</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Your constraint is value</t>
+          <t>Pull the work that doesn't need your best people off your best people.</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr"/>
-      <c r="E47" s="8" t="inlineStr"/>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>fulfilment</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Title, nothing failing</t>
+          <t>Fix action 4</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>The tightest thing is value</t>
+          <t>Quote the lead time you actually deliver rather than the one you hope for. A blown promise costs a customer you'd already won.</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr"/>
-      <c r="E48" s="8" t="inlineStr"/>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>q19 is c/d</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>fulfilment</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Opening</t>
+          <t>Fix action 5</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Value here means what the customer perceives, and it has nothing to do with your pricing or your margin. They buy, and then they stop, or they stay and give most of the work to somebody else.</t>
+          <t>Stop selling the jobs that eat the most capacity for the least return, at least until the queue clears.</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr"/>
-      <c r="E49" s="8" t="inlineStr"/>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>fulfilment</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 1</t>
+          <t>Fix action 6</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>of the customers you had a year ago, {q21.band} still buy from you</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>of the customers you had a year ago, {q21.exact}% still buy from you</t>
-        </is>
-      </c>
+          <t>Add capacity last. Hiring into a broken process gets you a bigger broken process.</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr"/>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>{q21.band}, {q21.exact}</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
@@ -18261,24 +17139,16 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 2</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>you get {q57.band} of the work they put out</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>you get {q57.exact}% of the work they put out</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t>{q57.band}, {q57.exact}</t>
-        </is>
-      </c>
+          <t>You are {c} constrained</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr"/>
+      <c r="E51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -18288,20 +17158,16 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 3</t>
+          <t>Title, nothing failing</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>they come back unprompted {q22.band}</t>
+          <t>The tightest thing is {c}</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr"/>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t>{q22.band}</t>
-        </is>
-      </c>
+      <c r="E52" s="8" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -18311,20 +17177,16 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 4</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>referrals bring in {q23.band} of your new customers</t>
+          <t>Value here means what the customer perceives, and it has nothing to do with your pricing or your margin. They buy, and then they stop, or they stay and give most of the work to somebody else.</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr"/>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>{q23.band}</t>
-        </is>
-      </c>
+      <c r="E53" s="8" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -18334,16 +17196,24 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Evidence clause 1</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>You're filling a leaky bucket. Every dollar going into finding new customers is currently paying to replace the ones walking out the other side, which is why the business feels busy and stays the same size.</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr"/>
-      <c r="E54" s="8" t="inlineStr"/>
+          <t>of the customers you had a year ago, {q21.band} still buy from you</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>of the customers you had a year ago, {q21.exact}% still buy from you</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>{q21.band}, {q21.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -18353,16 +17223,24 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Fix, lead line</t>
+          <t>Evidence clause 2</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Find out why they leave, then fix the thing they tell you about. It's almost always smaller than you'd expect.</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr"/>
-      <c r="E55" s="8" t="inlineStr"/>
+          <t>you get {q57.band} of the work they put out</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>you get {q57.exact}% of the work they put out</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>{q57.band}, {q57.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -18372,16 +17250,20 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Fix action 1</t>
+          <t>Evidence clause 3</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Ring ten customers who stopped buying and ask them straight. Not a survey. A phone call.</t>
+          <t>they come back unprompted {q22.band}</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr"/>
-      <c r="E56" s="8" t="inlineStr"/>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>{q22.band}</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -18391,16 +17273,20 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Fix action 2</t>
+          <t>Evidence clause 4</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Look hard at the first thirty days after someone buys. That's where most of the leaving gets decided.</t>
+          <t>referrals bring in {q23.band} of your new customers</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr"/>
-      <c r="E57" s="8" t="inlineStr"/>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>{q23.band}</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -18410,12 +17296,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Fix action 3</t>
+          <t>Closing</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Give them a reason to come back that you initiate. Waiting to be remembered isn't a retention plan.</t>
+          <t>You're filling a leaky bucket. Every dollar going into finding new customers is currently paying to replace the ones walking out the other side, which is why the business feels busy and stays the same size.</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr"/>
@@ -18429,12 +17315,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Fix action 4</t>
+          <t>Fix, lead line</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Close the gap between what you sell and what they actually get. Value is the size of that gap.</t>
+          <t>Find out why they leave or why they shrink, then fix the thing they tell you about.</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr"/>
@@ -18448,98 +17334,110 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Fix action 5</t>
+          <t>Fix action 1</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Measure it monthly. You can't run a business on a retention number you find out about once a year.</t>
+          <t>Ring ten customers who stopped buying, or who cut back, and ask them straight. Not a survey. A phone call.</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr"/>
-      <c r="E60" s="8" t="inlineStr"/>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Fix action 2</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Your constraint is the offer</t>
+          <t>Ask your biggest customers what they give to somebody else, and why. That work already exists, you're just not getting it.</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr"/>
-      <c r="E61" s="8" t="inlineStr"/>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>q57 is c/d/e</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Title, nothing failing</t>
+          <t>Fix action 3</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>The tightest thing is the offer</t>
+          <t>Look hard at the first thirty days after somebody buys. That's where most of the leaving gets decided.</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr"/>
-      <c r="E62" s="8" t="inlineStr"/>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Opening</t>
+          <t>Fix action 4</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Enquiries arrive and they don't convert.</t>
+          <t>Give them a reason to come back that you initiate. Waiting to be remembered isn't a retention plan.</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr"/>
-      <c r="E63" s="8" t="inlineStr"/>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 1</t>
+          <t>Fix action 5</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>your close rate sits {q26.band}</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>your close rate sits at {q26.exact}%</t>
-        </is>
-      </c>
+          <t>Measure it monthly. You can't run a business on a number you find out about once a year.</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr"/>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>{q26.band}, {q26.exact}</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
@@ -18551,20 +17449,16 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 2</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>the most common reason you lose is {q27.band}</t>
+          <t>You are {c} constrained</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr"/>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>{q27.band}</t>
-        </is>
-      </c>
+      <c r="E65" s="8" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -18574,20 +17468,16 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 3</t>
+          <t>Title, nothing failing</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>prospects come back on your quote asking what's included {q28.band}</t>
+          <t>The tightest thing is {c}</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr"/>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>{q28.band}</t>
-        </is>
-      </c>
+      <c r="E66" s="8" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
@@ -18597,20 +17487,16 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 4</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>they find out what you charge {q30.band}</t>
+          <t>Enquiries arrive and they don't convert.</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr"/>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>{q30.band}</t>
-        </is>
-      </c>
+      <c r="E67" s="8" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -18620,16 +17506,24 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Evidence clause 1</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>This isn't a sales technique problem. When the thing on the table is clear, priced, and it fits what the buyer came in for, an average salesperson closes it. Right now yours needs you in the room to make sense of it.</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr"/>
-      <c r="E68" s="8" t="inlineStr"/>
+          <t>your close rate sits {q26.band}</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>your close rate sits at {q26.exact}%</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>{q26.band}, {q26.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -18639,16 +17533,20 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Fix, lead line</t>
+          <t>Evidence clause 2</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>Make the thing you sell understandable without you standing next to it.</t>
+          <t>the most common reason you lose is {q27.band}</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr"/>
-      <c r="E69" s="8" t="inlineStr"/>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>{q27.band}</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -18658,16 +17556,20 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Fix action 1</t>
+          <t>Evidence clause 3</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Write the offer on one page. What it is, what it costs, what the buyer gets, who it isn't for.</t>
+          <t>prospects come back on your quote asking what's included {q28.band}</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr"/>
-      <c r="E70" s="8" t="inlineStr"/>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>{q28.band}</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -18677,16 +17579,20 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Fix action 2</t>
+          <t>Evidence clause 4</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Price it publicly, or at least in a range. Every quote you build from scratch is a delay you're funding.</t>
+          <t>they find out what you charge {q30.band}</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr"/>
-      <c r="E71" s="8" t="inlineStr"/>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>{q30.band}</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -18696,12 +17602,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Fix action 3</t>
+          <t>Closing</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Sort your last twenty losses by reason. The pattern is usually one thing, not five.</t>
+          <t>This isn't a sales technique problem. When the thing on the table is clear, priced, and it fits what the buyer came in for, an average salesperson closes it. Right now yours needs you in the room to make sense of it.</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr"/>
@@ -18715,12 +17621,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Fix action 4</t>
+          <t>Fix, lead line</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Cut the options. A buyer choosing between three clear things buys. A buyer choosing between eleven goes away to think about it.</t>
+          <t>Make the thing you sell understandable without you standing next to it.</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr"/>
@@ -18734,121 +17640,133 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Fix action 5</t>
+          <t>Fix action 1</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>Test the new version on the next ten enquiries before you change anything else.</t>
+          <t>Write the offer on one page. What it is, what it costs, what the buyer gets, who it isn't for.</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr"/>
-      <c r="E74" s="8" t="inlineStr"/>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>offer</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Fix action 2</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>Your constraint is demand</t>
+          <t>Price it publicly, or at least in a range. Every quote you build from scratch is a delay you're funding.</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr"/>
-      <c r="E75" s="8" t="inlineStr"/>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>q30 is c/d</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>offer</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Title, nothing failing</t>
+          <t>Fix action 3</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>The tightest thing is demand</t>
+          <t>Sort your last twenty losses by reason and count them. The pattern is usually one thing.</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr"/>
-      <c r="E76" s="8" t="inlineStr"/>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>offer</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>Opening</t>
+          <t>Fix action 4</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>You've got capacity sitting idle and not enough people asking.</t>
+          <t>Rewrite the quote so it answers what's included and why it costs that, before they have to ask.</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr"/>
-      <c r="E77" s="8" t="inlineStr"/>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>q28 is c/d</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>offer</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 1</t>
+          <t>Fix action 5</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>enquiries run {q31.band}</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>enquiries run at about {q31.exact} a month</t>
-        </is>
-      </c>
+          <t>Cut the options. Fewer, clearer choices close more often than a menu does.</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr"/>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>{q31.band}, {q31.exact}</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>offer</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 2</t>
+          <t>Fix action 6</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>volume has {q33.band} over the last year</t>
+          <t>Test the new version on the next ten enquiries before you change anything else.</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr"/>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>{q33.band}</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
@@ -18860,20 +17778,16 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 3</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>{q35.band}</t>
+          <t>You are {c} constrained</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr"/>
-      <c r="E80" s="8" t="inlineStr">
-        <is>
-          <t>{q35.band}</t>
-        </is>
-      </c>
+      <c r="E80" s="8" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
@@ -18883,12 +17797,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Title, nothing failing</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>You could take on more work tomorrow, which is what separates this from a delivery problem. Nothing downstream is broken. The business just isn't being fed, and it won't start feeding itself.</t>
+          <t>The tightest thing is {c}</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr"/>
@@ -18902,12 +17816,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Fix, lead line</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>Turn the tap on deliberately. One channel, run properly, before you touch a second.</t>
+          <t>You've got capacity sitting idle and not enough people asking.</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr"/>
@@ -18921,16 +17835,24 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Fix action 1</t>
+          <t>Evidence clause 1</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>Pick the channel that already brings your best customers and put real weight behind it.</t>
-        </is>
-      </c>
-      <c r="D83" s="7" t="inlineStr"/>
-      <c r="E83" s="8" t="inlineStr"/>
+          <t>enquiries run {q31.band}</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>enquiries run at about {q31.exact} a month</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>{q31.band}, {q31.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
@@ -18940,16 +17862,20 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>Fix action 2</t>
+          <t>Evidence clause 2</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>Go and ask for work. Outbound to the twenty businesses you'd most like to work with beats waiting on referrals.</t>
+          <t>volume has {q33.band} over the last year</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr"/>
-      <c r="E84" s="8" t="inlineStr"/>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>{q33.band}</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
@@ -18959,16 +17885,20 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Fix action 3</t>
+          <t>Evidence clause 3</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>Make it obvious what you do and who you do it for, everywhere you appear. Most quiet businesses are quiet because nobody can tell.</t>
+          <t>{q35.band}</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr"/>
-      <c r="E85" s="8" t="inlineStr"/>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>{q35.band}</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
@@ -18978,12 +17908,12 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Fix action 4</t>
+          <t>Closing</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>Ask every happy customer for one introduction. It's the cheapest demand you'll ever generate.</t>
+          <t>You could take on more work tomorrow, which is what separates this from a delivery problem. Nothing downstream is broken. The business just isn't being fed, and it won't start feeding itself.</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr"/>
@@ -18997,12 +17927,12 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Fix action 5</t>
+          <t>Fix, lead line</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Give a channel ninety days before you judge it. Anything shorter is guesswork.</t>
+          <t>Turn the tap on deliberately. One channel, run properly, before you touch a second.</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr"/>
@@ -19011,134 +17941,138 @@
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>margin</t>
+          <t>demand</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Fix action 1</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>Your constraint is margin</t>
+          <t>Nothing is running right now, so start with the one thing you can do every week without fail.</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr"/>
-      <c r="E88" s="8" t="inlineStr"/>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>q35 is b/c</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>margin</t>
+          <t>demand</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Title, nothing failing</t>
+          <t>Fix action 2</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>The tightest thing is margin</t>
+          <t>Pick the channel that already brings your best customers and put real weight behind it.</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr"/>
-      <c r="E89" s="8" t="inlineStr"/>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>margin</t>
+          <t>demand</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Opening</t>
+          <t>Fix action 3</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>You're busy, you're full, and there's nothing left at the end of it.</t>
+          <t>Go and ask for work. Outbound to the twenty businesses you'd most like to work with beats waiting on referrals.</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr"/>
-      <c r="E90" s="8" t="inlineStr"/>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>margin</t>
+          <t>demand</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 1</t>
+          <t>Fix action 4</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>what's left after direct costs sits {q36.band}</t>
-        </is>
-      </c>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>what's left after direct costs sits at {q36.exact}%</t>
-        </is>
-      </c>
+          <t>Everything arrives through one channel. Stand up a second before that one changes.</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr"/>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>{q36.band}, {q36.exact}</t>
+          <t>q43 is c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>margin</t>
+          <t>demand</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 2</t>
+          <t>Fix action 5</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>after everything it's {q37.band}</t>
-        </is>
-      </c>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t>after everything it's {q37.exact}%</t>
-        </is>
-      </c>
+          <t>Ask every happy customer for one introduction.</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr"/>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>{q37.band}, {q37.exact}</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>margin</t>
+          <t>demand</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 3</t>
+          <t>Fix action 6</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>{q38.band}</t>
+          <t>Give a channel ninety days before you judge it. Anything shorter is guesswork.</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr"/>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>{q38.band}</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
@@ -19150,20 +18084,16 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 4</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>jobs run over what you quoted {q39.band}</t>
+          <t>You are {c} constrained</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr"/>
-      <c r="E94" s="8" t="inlineStr">
-        <is>
-          <t>{q39.band}</t>
-        </is>
-      </c>
+      <c r="E94" s="8" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
@@ -19173,12 +18103,12 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Title, nothing failing</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Volume won't rescue this. At the margin you're running, more work gets you more of the same result and it arrives faster.</t>
+          <t>The tightest thing is {c}</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr"/>
@@ -19192,12 +18122,12 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Fix, lead line</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>Price first, then cost. Price moves faster and costs nothing to change.</t>
+          <t>You're busy, you're full, and there's nothing left at the end of it.</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr"/>
@@ -19211,16 +18141,24 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Fix action 1</t>
+          <t>Evidence clause 1</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>Raise prices on new work now. Ten percent, across the board, and watch what actually happens.</t>
-        </is>
-      </c>
-      <c r="D97" s="7" t="inlineStr"/>
-      <c r="E97" s="8" t="inlineStr"/>
+          <t>what's left after direct costs sits {q36.band}</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>what's left after direct costs sits at {q36.exact}%</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>{q36.band}, {q36.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
@@ -19230,16 +18168,24 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>Fix action 2</t>
+          <t>Evidence clause 2</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>Work out what each job really costs, your own time included. Half the jobs you're proud of are losing money.</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="inlineStr"/>
-      <c r="E98" s="8" t="inlineStr"/>
+          <t>after everything it's {q37.band}</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>after everything it's {q37.exact}%</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>{q37.band}, {q37.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
@@ -19249,16 +18195,20 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Fix action 3</t>
+          <t>Evidence clause 3</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>Find your worst three customers by margin, then reprice them or let them go.</t>
+          <t>{q38.band}</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr"/>
-      <c r="E99" s="8" t="inlineStr"/>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>{q38.band}</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
@@ -19268,16 +18218,20 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Fix action 4</t>
+          <t>Evidence clause 4</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Quote a contingency into every job that historically runs over. You already know which ones they are.</t>
+          <t>jobs run over what you quoted {q39.band}</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr"/>
-      <c r="E100" s="8" t="inlineStr"/>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>{q39.band}</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
@@ -19287,19 +18241,153 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Fix action 5</t>
+          <t>Closing</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>Stop discounting to win. A discount is the fastest way to buy work you'll resent delivering.</t>
+          <t>Volume won't rescue this. At the margin you're running, more work gets you more of the same result and it arrives faster.</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr"/>
       <c r="E101" s="8" t="inlineStr"/>
     </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>margin</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>Fix, lead line</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>Price first, then cost. Price moves faster and costs nothing to change.</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr"/>
+      <c r="E102" s="8" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>margin</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>Fix action 1</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>Raise prices on new work now. Ten percent across the board, and watch what actually happens.</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr"/>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>q38 is c/d/e</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>margin</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>Fix action 2</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>Work out what each job really costs, your own time included, then rank your last twenty by what was left.</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr"/>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>margin</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>Fix action 3</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>Quote a contingency into the jobs that historically run over. You already know which ones they are.</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr"/>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>q39 is c/d</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>margin</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>Fix action 4</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>Find your worst three customers by margin, then reprice them or let them go.</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr"/>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>margin</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>Fix action 5</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>Stop discounting to win. A discount is the fastest way to buy work you'll resent delivering.</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr"/>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:E101"/>
+  <autoFilter ref="A2:E107"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -19520,7 +18608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -19607,10 +18695,15 @@
       <c r="F3" s="7" t="inlineStr"/>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>Find out today what it costs to hire a replacement at short notice, and who has one. A relationship you already have beats a phone number you find on the day.</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr"/>
+          <t>Find out today what a replacement costs at short notice, and who actually has one.</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>Put it on a service schedule and hold to it. Most failures give some warning.</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -19641,10 +18734,15 @@
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>Stand up a second channel before you need it, and give it ninety days before you judge it. One channel is a decision somebody else gets to make on your behalf.</t>
+          <t>Stand up a second channel before you need it, and give it ninety days before you judge it.</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>Write down what you'd do if the current one halved tomorrow. That plan is worth having on paper before you need it.</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>{q43.band}</t>
         </is>
@@ -19679,10 +18777,15 @@
       <c r="F5" s="7" t="inlineStr"/>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Set a ceiling, say twenty percent of revenue from any one customer, and treat crossing it as the trigger to go and win two more. Get them onto a term agreement in the meantime.</t>
+          <t>Set a ceiling, say twenty percent of revenue from any one customer, and treat crossing it as the trigger to go and win two more.</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Get them onto a term agreement with a notice period, so a decision to leave gives you time to react.</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>{q41.band}, {q41.exact}</t>
         </is>
@@ -19713,10 +18816,15 @@
       <c r="F6" s="7" t="inlineStr"/>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Have them document the work while they're still here, and pay them properly to do it. It's the cheapest insurance available to you.</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr"/>
+          <t>Have them document the work while they're still here, and pay them properly to do it.</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Put a second person alongside them on the next three jobs, doing rather than watching.</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -19743,10 +18851,15 @@
       <c r="F7" s="7" t="inlineStr"/>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Take one thing you do well and sell it somewhere else, even at a small scale. Proving it travels is the whole exercise.</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr"/>
+          <t>Take one thing you do well and sell it somewhere else, even at a small scale.</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Track what share of revenue comes from outside the home patch, and set a target for it.</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -19773,10 +18886,15 @@
       <c r="F8" s="7" t="inlineStr"/>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Put every renewal date in a calendar with a ninety day warning, and make sure a second person can hold or renew it. A lapse is nearly always an admin failure rather than a real one.</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr"/>
+          <t>Put every renewal date in a calendar with a ninety day warning on it.</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Make sure a second person can hold or renew it, so a lapse can't come down to one person's inbox.</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -19803,10 +18921,15 @@
       <c r="F9" s="7" t="inlineStr"/>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Write down what they hold, then move one piece of it to somebody else this month. Repeat until nothing sits in one head.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr"/>
+          <t>Write down what they hold, then move one piece of it to somebody else this month.</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Repeat until nothing sits in one head, and test it by having them take a week off.</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -19837,10 +18960,15 @@
       <c r="F10" s="7" t="inlineStr"/>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Build a second line and sell it to the customers you already have. It's cheaper than finding new customers for the line you've got.</t>
+          <t>Build a second line and sell it to the customers you already have.</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Set a target for what share of revenue it should carry in twelve months, and check it quarterly.</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>{q42.band}, {q42.exact}</t>
         </is>
@@ -19871,10 +18999,15 @@
       <c r="F11" s="7" t="inlineStr"/>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Qualify a second supplier and give them ten percent of your volume. A backup you've never actually bought from isn't a backup.</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr"/>
+          <t>Qualify a second supplier and give them ten percent of your volume. A backup you've never bought from isn't a backup.</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Get lead times and pricing from your current one in writing, so a change is a conversation rather than a surprise.</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -19901,10 +19034,15 @@
       <c r="F12" s="7" t="inlineStr"/>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Name the person, tell them, and start handing over one area at a time with the decisions attached. A deputy who can't decide anything is a job title.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr"/>
+          <t>Name the person, tell them, and start handing over one area at a time with the decisions attached.</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Give them a budget and a limit they can act inside. A deputy who can't decide anything is a job title.</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -19935,10 +19073,15 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Build to one month of fixed costs in a separate account, then three. Move a fixed percentage of every payment that comes in, automatically, so it isn't a decision you make each time.</t>
+          <t>Build to one month of fixed costs in a separate account, then three.</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>Move a fixed percentage of every payment across automatically, so it isn't a decision you make each time.</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>{q8.band}</t>
         </is>
@@ -19973,10 +19116,15 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Put a written agreement behind every piece of work, with terms, scope and a notice period. Start with your largest customers.</t>
+          <t>Put a written agreement behind every piece of work, with terms, scope and a notice period.</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>Start with your largest customers, because that's where the exposure actually sits.</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>{q45.band}</t>
         </is>
@@ -20011,10 +19159,15 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Pick five numbers and look at them weekly. Cash in the bank, enquiries, close rate, jobs delivered, and margin on the last ten jobs. One page, same day every week.</t>
+          <t>Pick five numbers and look at them weekly. Cash in the bank, enquiries, close rate, jobs delivered, and margin on the last ten jobs.</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>One page, same day every week. The habit matters more than the tool you keep it in.</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>{q47.band}</t>
         </is>
@@ -20049,10 +19202,15 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Record yourself doing the five things that go wrong most often, then turn each one into a one page checklist. Checklists beat manuals, because people actually use them.</t>
+          <t>Record yourself doing the five things that go wrong most often, then turn each one into a one page checklist.</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>Checklists beat manuals, because people actually use them.</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>{q46.band}</t>
         </is>
@@ -20076,21 +19234,26 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>The way you spend your week is {q52.band}. It decides how long you'll keep doing this, and most businesses that fail slowly fail because the owner ran out of want.</t>
+          <t>The way you spend your week is {q52.band}. It decides how long you'll keep doing this, and a business rarely outlives the owner's appetite for running it.</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr"/>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>You weren't sure whether the way you spend your week matches what you wanted out of this. That question decides how long you'll keep doing it, and most businesses that fail slowly fail because the owner ran out of want.</t>
+          <t>You weren't sure whether the way you spend your week matches what you wanted out of this. That question decides how long you'll keep doing it, and a business rarely outlives the owner's appetite for running it.</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Write down what you actually wanted out of this, then hold your week up against it. The gap is the brief for the next twelve months.</t>
+          <t>Write down what you actually wanted out of this, then hold your week up against it.</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>The gap between those two is the brief for the next twelve months.</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>{q52.band}</t>
         </is>
@@ -20125,10 +19288,15 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Write the one page version. Who runs it, what happens to the customers, what it's worth and who'd buy it. It doesn't need to be right, it needs to exist.</t>
+          <t>Write the one page version. Who runs it, what happens to the customers, what it's worth and who'd buy it.</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>It doesn't need to be right, it needs to exist.</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>{q50.band}</t>
         </is>
@@ -20163,10 +19331,15 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Work out what only you can do, then start moving everything else. The test is whether the business survives you taking a month off, so book the month and find out.</t>
+          <t>Work out what only you can do, then start moving everything else.</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>Book a month off twelve months out and work backwards from it. That's the deadline that makes it real.</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>{q49.band}</t>
         </is>
@@ -20201,10 +19374,15 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>List every guarantee you've signed and put a date against each one to renegotiate or release it. Most get renewed on autopilot because nobody asks.</t>
+          <t>List every guarantee you've signed and put a date against each one to renegotiate or release it.</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>Most get renewed on autopilot, because nobody asks.</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>{q51.band}</t>
         </is>
@@ -20225,132 +19403,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="96" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="108" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Scoring is by family, never by listing sixteen individual flags at somebody. Key person, no second in command, no documented process and owner trapped are usually one disease showing up in four places.</t>
+          <t>Risks print as one list, loudest first, regardless of which family they came from. Families still weight the internal ordering, they no longer split the section. The old family framing block, the separate minor risk section and the compound blocks were all removed after they read as filler in testing.</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>Part</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Family</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>One line definition</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>Framing block, opens the risk section</t>
+          <t>Wording</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>concentration</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Concentration</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>One of something that should be many.</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>Your risk sits in concentration. There's one of something that ought to be several. It costs nothing to carry while it holds, and the cost of it not holding is a year of revenue.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>fragility</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Fragility</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>The business can't absorb a hit.</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Your risk sits in fragility. The business runs well enough while nothing goes wrong, and there's very little underneath it if something does. Fragility is what turns an ordinary bad month into a hole you spend two years climbing out of.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>The business owns you.</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Your risk sits with you. The business owns you rather than the other way around, and that shows up in what you're personally on the hook for, what the business is worth, and what happens if you stop. It's the risk owners notice last, because it feels like commitment rather than exposure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Nothing loud enough</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr"/>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Nothing in your risk answers is loud enough to put in front of you. Come back to this as the business changes, because the risks that matter change with it.</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Section lead, printed once above the risks</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>These are the things that would hurt most if they went wrong. They sit behind the constraint above in the order, not in front of it.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D6"/>
+  <autoFilter ref="A2:B3"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20362,359 +19456,754 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="100" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="122" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>This prints one specific finding from the second risk family, never the family itself. Naming a family and nothing else is the failure this replaced. The flag has to clear the print threshold and must not already appear in the main risk section.</t>
+          <t>Telling an owner to stop doing the wrong thing is usually worth more than another action item, because they are already mid action on it. This section does not print when nothing is failing.</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>Constraint</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>Part</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>The one line printed when this is the second family's loudest flag</t>
+          <t>Wording</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr"/>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Section framing, printed once above the line below</t>
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Lead line</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>One more, from a different family to the risks above. It's behind them in the order, not in front of them.</t>
+          <t>Until the cash timing is fixed, leave these alone.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>key_asset</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Key asset</t>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Item 1</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>One piece of equipment or one vehicle is doing work you have no backup for.</t>
+          <t>Don't chase bigger jobs. Bigger jobs mean bigger upfront costs and longer payment cycles.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>key_channel</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Key channel</t>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Item 2</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Nearly all your customers arrive through one channel you don't control.</t>
+          <t>Don't hire. Wages are the least flexible cost you can add to a cash problem.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>key_client</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Key client</t>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Item 3</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>One customer carries enough of your revenue that losing them is a bad year rather than a bad month.</t>
+          <t>Don't buy equipment outright. Finance it, even if the interest annoys you.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>key_employee</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Key employee</t>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Item 4</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>One person holds how the work actually gets done, and it isn't written down anywhere else.</t>
+          <t>Don't discount to get paid faster. That's borrowing at a rate you'd never accept from a bank.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>key_geography</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Key geography</t>
+          <t>cashflow</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Item 5</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>All of your revenue comes out of one city or region.</t>
+          <t>Don't increase marketing spend. More demand you can't fund makes the hole deeper.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>key_licence</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Key licence</t>
+          <t>talent</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Lead line</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>One licence or accreditation is the thing that lets you trade at all.</t>
+          <t>Until the layer exists, leave these alone.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>key_person</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Key person</t>
+          <t>talent</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Item 1</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>The business depends on one person to function, and going by your answers that person is probably you.</t>
+          <t>Don't hire another doer. Every one you add reports to you, and you're the bottleneck.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>key_product</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Key product</t>
+          <t>talent</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Item 2</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>One product or service line carries most of what you sell.</t>
+          <t>Don't take on a new market, product or location. All three land on your desk.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>key_supplier</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Key supplier</t>
+          <t>talent</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Item 3</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>One supplier with no ready replacement is setting your prices and your timelines.</t>
+          <t>Don't start anything that needs your attention for six months.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>no_2ic</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>No second in command</t>
+          <t>talent</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Item 4</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>There's nobody who could run this if you stepped out.</t>
+          <t>Don't increase lead generation. The work you win still has to route through you.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>no_buffer</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>No cash buffer</t>
+          <t>talent</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Item 5</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>There isn't enough cash behind the business to absorb an ordinary bad month.</t>
+          <t>Don't redraw the org chart. What's missing is a person who doesn't exist, not a diagram.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>no_contracts</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>No contracts</t>
+          <t>fulfilment</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Lead line</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Your work isn't committed in writing, so the revenue can leave on a phone call.</t>
+          <t>Until you can deliver what you've already sold, leave these alone.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>no_data</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>No data</t>
+          <t>fulfilment</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Item 1</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>You aren't looking at the numbers often enough to see something coming.</t>
+          <t>Don't chase new customers. You'd be damaging the ones you have to serve the ones you win.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>no_process</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>No documented process</t>
+          <t>fulfilment</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Item 2</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Almost nothing is documented well enough for somebody else to pick up.</t>
+          <t>Don't increase marketing spend. Adding demand to a full pipeline is the classic accelerant.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>model_misfit</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Model misfit</t>
+          <t>fulfilment</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Item 3</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>The way you spend your week isn't what you wanted out of this.</t>
+          <t>Don't launch a new service line. New work is slow work while the process is still being learned.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>no_succession</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>No succession</t>
+          <t>fulfilment</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Item 4</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>There's no plan for what happens if you stop, sell or step back.</t>
+          <t>Don't drop your prices. You've got more demand than capacity, which is the one time raising them is easy.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>owner_trapped</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Owner trapped</t>
+          <t>fulfilment</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Item 5</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>A buyer would need you to stay on for a long time, which is what makes the business hard to sell and hard to leave.</t>
+          <t>Don't promise a shorter lead time to win a job. That's where the quality problem starts.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>personal_guarantee</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Personally guaranteed</t>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Lead line</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>You've personally guaranteed obligations the business took on.</t>
+          <t>Until customers stay, leave these alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Item 1</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Don't spend more on acquisition. You'd be paying to fill a bucket with a hole in it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Item 2</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Don't raise prices. Value perception is already the problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Item 3</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Don't add a new product for existing customers who aren't buying the current one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Item 4</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Don't expand into a new market. You'd take the retention problem with you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Item 5</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Don't run a loyalty programme. A discount doesn't fix a value gap, it confirms one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>offer</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Lead line</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Until the offer lands, leave these alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>offer</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Item 1</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Don't buy more leads. You'd pay more money for the same conversion rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>offer</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Item 2</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Don't hire a salesperson. They'd fail against the same offer you're failing against.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>offer</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Item 3</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Don't cut your price. Price is rarely the real reason, and you can't test it while the offer is unclear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>offer</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Item 4</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Don't add more options. More choice is part of why these deals are stalling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>offer</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Item 5</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Don't rebrand. The words are the problem, not the logo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Lead line</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Until enquiries lift, leave these alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Item 1</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Don't hire. You'd be adding capacity to capacity you already can't fill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Item 2</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Don't build a new product. The one you have hasn't been shown to enough people.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Item 3</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Don't cut prices to stimulate demand. It rarely moves volume, and it permanently resets what customers expect to pay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Item 4</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Don't spread across five channels at once. One channel run properly beats five run badly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>demand</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Item 5</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Don't wait for referrals to pick back up. Referral volume follows the number of customers you have, and that's the number that's short.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>margin</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Lead line</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Until the margin moves, leave these alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>margin</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Item 1</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Don't chase volume. More work at this margin is more risk for the same money.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>margin</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Item 2</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Don't hire. Every head you add at this margin needs a lot of revenue standing behind it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>margin</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Item 3</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Don't take the big thin job because it's good for the brand. Reputation doesn't pay wages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>margin</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Item 4</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Don't discount anything. There's nothing left to give away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>margin</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Item 5</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Don't invest in growth. Growing an unprofitable model makes it unprofitable faster.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C21"/>
+  <autoFilter ref="A2:C44"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>

--- a/diagnostic/Business-Diagnostic-Spec.xlsx
+++ b/diagnostic/Business-Diagnostic-Spec.xlsx
@@ -12,28 +12,26 @@
     <sheet name="Answer options" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Constraints and order" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Report, constraint" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Report, minor" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Report, risk flags" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Report, risk section" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Report, don't do yet" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Report, open and close" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Thresholds" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Logic" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Data slots" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Report, risk flags" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Report, risk section" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Report, don't do yet" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Report, open and close" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Thresholds" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Logic" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Data slots" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Questions'!$A$2:$J$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Answer options'!$A$2:$I$305</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Constraints and order'!$A$2:$G$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Report, constraint'!$A$2:$E$107</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Report, minor'!$A$2:$D$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Report, risk flags'!$A$2:$H$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Report, risk section'!$A$2:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Report, don''t do yet'!$A$2:$C$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Report, open and close'!$A$2:$E$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Thresholds'!$A$2:$C$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Logic'!$A$1:$B$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Data slots'!$A$2:$F$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Report, risk flags'!$A$2:$H$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Report, risk section'!$A$2:$B$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Report, don''t do yet'!$A$2:$C$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Report, open and close'!$A$2:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Thresholds'!$A$2:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Logic'!$A$1:$B$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Data slots'!$A$2:$F$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -521,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -707,94 +705,82 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Report, minor</t>
+          <t>Report, risk flags</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>The one line that prints when a second constraint is loud but downstream.</t>
+          <t>All 16 risk flags. Definition, the version used when the answer was Not sure, and the fix.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Report, risk flags</t>
+          <t>Report, risk section</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>All 16 risk flags. Definition, the version used when the answer was Not sure, and the fix.</t>
+          <t>The line that opens the risk section.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Report, risk section</t>
+          <t>Report, don't do yet</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>The line that opens the risk section.</t>
+          <t>The closing section. What not to touch until the constraint is fixed.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Report, don't do yet</t>
+          <t>Report, open and close</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>The closing section. What not to touch until the constraint is fixed.</t>
+          <t>The opening and closing of the report, including the three opening variants.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Report, open and close</t>
+          <t>Thresholds</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>The opening and closing of the report, including the three opening variants.</t>
+          <t>Every tunable number, and what moving it does.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Thresholds</t>
+          <t>Logic</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Every tunable number, and what moving it does.</t>
+          <t>How the engine picks the primary, the minor, and the risks. Read this before changing a threshold.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Logic</t>
+          <t>Data slots</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>How the engine picks the primary, the minor, and the risks. Read this before changing a threshold.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Data slots</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Every variable, every phrase it can print, and which report blocks quote it. Check here before changing a band phrase, because it shows you the sentences that band lands in.</t>
         </is>
@@ -811,354 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="98" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Blank line between paragraphs is written as two newlines in the source. Keep paragraphs short.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Variant</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>When it is used</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>Wording</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>Variables in this row</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Used whenever a constraint actually failed</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>Everything below is calculated on your answers. It's a guide rather than a custom diagnostic, so read the report as a rough shape of what your current challenges are and what solutions may look like.
-It names your biggest single constraint. There is likely more, and there may be other things wrong, there always are. They're not listed in here because the order you fix things in matters. Fix the constraints and risks in your business, then come back and get an updated report.</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>wellRun</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Nothing cleared the floor. Nothing is failing</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Everything below is calculated on your answers. Nothing in them is close to failing, which is a real result and rarer than you'd think.
-What follows is the tightest thing in the business rather than a problem. Treat it as where the next bit of growth comes from, not something to fix.</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>noneSevere</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Nothing failed outright but something is tight</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Everything below is calculated on your answers. Nothing in them is screaming, which is worth knowing on its own.
-What follows is the tightest thing in the business rather than something that's failing outright. It's the next thing to work on, not an emergency.</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>tooUnsure</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Too many Not sure answers to stand behind a diagnosis</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Everything below is calculated on your answers, and there were a lot of them you couldn't answer, so read it as provisional.
-The finding below is the best available reading of what you did tell us. The bigger issue is that the business isn't visible to you, and that's covered in the risks. Come back and run it again once you can answer the numbers.</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>privacy</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Small print under the opening, on every report</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>We do not use any AI in this tool, and none of your data is sent or stored offsite.</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Heading</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>titleUnsure</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Replaces the constraint heading when there is not enough to call it</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>There isn't enough here to call it</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Body</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>looseBody</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Replaces the constraint block when nothing is failing</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Nothing in here is failing, so there's no evidence to walk you through. What you've got is {d.primaryShort} sitting as the tightest of the seven right now, which makes it the likeliest place the next bit of growth comes from. The actions below are worth doing and none of them are urgent.</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>{d.primaryShort}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Body</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>unsureBody</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Replaces the constraint block when there were too many Not sure answers</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>There isn't enough here to point at one thing with any confidence. On what you did answer, {d.primaryShort} is the tightest of the seven, so read the actions below as a starting point rather than a diagnosis.
-The risk section is the part of this report to take seriously. Not being able to answer the questions is the finding, and it's the one worth acting on first.</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>{d.primaryShort}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Closing</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Normal close</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>That's the diagnosis. One constraint, the risks sitting around it, and the things to leave alone while you fix it.
-Work the constraint and check back in ninety days. That's long enough for it to move and short enough that you'll still remember what you changed.</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Closing</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>loose</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Close used when nothing is failing</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>That's the read. One thing to push on, and nothing in the way of it.
-Run this again in ninety days, or whenever something material changes. The constraint moves as the business grows, and the answer you get next time probably won't be this one.</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Closing</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>unsure</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Close used when there were too many Not sure answers</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>That's as far as your answers go. One provisional reading, and a clear picture of what the business can't currently tell you.
-Get the numbers visible, then run this again. The second time through it will be worth something.</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Closing</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>cta</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Call to action. Deliberately empty, still an open question</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr"/>
-      <c r="E14" s="8" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A2:E14"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1208,52 +847,52 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>MINOR_PRINT</t>
+          <t>FALLBACK_FLOOR</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>A second constraint has to reach this before it prints as a minor. Deliberately higher than PRIMARY_FAIL, so a minor has to be louder than the bar that would have made it a primary in its own right.</t>
+          <t>When nothing failed, anything under this counts as a well run business and the report switches to the softer wording. Above it, the report says nothing is failing but here is the tightest thing.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>FALLBACK_FLOOR</t>
+          <t>FLAG_PRINT</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>When nothing failed, anything under this counts as a well run business and the report switches to the softer wording. Above it, the report says nothing is failing but here is the tightest thing.</t>
+          <t>An individual flag has to reach this before it is named. Below it the flag still counts toward its family score.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>FLAG_PRINT</t>
+          <t>MAX_FLAGS_SHOWN</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>An individual flag has to reach this before it is named. Below it the flag still counts toward its family score.</t>
+          <t>Hard cap on how many risks get named, across all three families. Four keeps the report short and certain.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>MAX_FLAGS_SHOWN</t>
+          <t>NOT_SURE_DATA_FLAG</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
@@ -1261,42 +900,27 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Hard cap on how many risks get named, across all three families. Four keeps the report short and certain.</t>
+          <t>This many Not sure answers raises data blindness on its own, regardless of which questions they were.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>NOT_SURE_DATA_FLAG</t>
+          <t>MAX_ACTIONS</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>This many Not sure answers raises data blindness on its own, regardless of which questions they were.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>MAX_ACTIONS</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
           <t>Hard cap on how many fix actions print for the constraint. Conditional actions that did not fire never count toward it.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C9"/>
+  <autoFilter ref="A2:C8"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
@@ -1304,7 +928,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1475,7 +1099,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2847,7 +2471,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>riskDef / owner_trapped / banded</t>
+          <t>riskDef / owner_dependency / banded</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2589,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>looseBody  minorConstraint / cashflow  minorConstraint / demand  minorConstraint / fulfilment  minorConstraint / margin  minorConstraint / offer  minorConstraint / talent  minorConstraint / value  unsureBody</t>
+          <t>looseBody  unsureBody</t>
         </is>
       </c>
     </row>
@@ -6898,7 +6522,7 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>no_buffer</t>
+          <t>no_buffer (75)</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr"/>
@@ -6937,7 +6561,7 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>no_buffer</t>
+          <t>no_buffer (75)</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr"/>
@@ -6972,7 +6596,7 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>no_buffer</t>
+          <t>no_buffer (75)</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -7664,7 +7288,7 @@
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>no_2ic</t>
+          <t>owner_dependency (75)</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -7777,7 +7401,7 @@
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>key_person</t>
+          <t>owner_dependency (75)</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr"/>
@@ -7816,7 +7440,7 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>key_person</t>
+          <t>owner_dependency (75)</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr"/>
@@ -10609,7 +10233,7 @@
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>no_data</t>
+          <t>no_data (75)</t>
         </is>
       </c>
       <c r="I161" s="3" t="inlineStr"/>
@@ -10644,7 +10268,7 @@
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>no_data</t>
+          <t>no_data (75)</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
@@ -10823,7 +10447,7 @@
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>no_data</t>
+          <t>no_data (75)</t>
         </is>
       </c>
       <c r="I167" s="3" t="inlineStr">
@@ -11006,7 +10630,7 @@
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>no_data</t>
+          <t>no_data (75)</t>
         </is>
       </c>
       <c r="I172" s="3" t="inlineStr"/>
@@ -11041,7 +10665,7 @@
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
-          <t>no_data</t>
+          <t>no_data (75)</t>
         </is>
       </c>
       <c r="I173" s="3" t="inlineStr">
@@ -11395,7 +11019,7 @@
       </c>
       <c r="H183" s="3" t="inlineStr">
         <is>
-          <t>no_data</t>
+          <t>no_data (75)</t>
         </is>
       </c>
       <c r="I183" s="3" t="inlineStr">
@@ -11784,7 +11408,7 @@
       </c>
       <c r="H194" s="3" t="inlineStr">
         <is>
-          <t>no_data</t>
+          <t>no_data (75)</t>
         </is>
       </c>
       <c r="I194" s="3" t="inlineStr">
@@ -12040,7 +11664,7 @@
       </c>
       <c r="H202" s="3" t="inlineStr">
         <is>
-          <t>no_data</t>
+          <t>no_data (75)</t>
         </is>
       </c>
       <c r="I202" s="3" t="inlineStr">
@@ -12219,7 +11843,7 @@
       </c>
       <c r="H207" s="3" t="inlineStr">
         <is>
-          <t>no_data</t>
+          <t>no_data (75)</t>
         </is>
       </c>
       <c r="I207" s="3" t="inlineStr">
@@ -12682,7 +12306,7 @@
       </c>
       <c r="H220" s="3" t="inlineStr">
         <is>
-          <t>no_data</t>
+          <t>no_data (75)</t>
         </is>
       </c>
       <c r="I220" s="3" t="inlineStr">
@@ -12861,7 +12485,7 @@
       </c>
       <c r="H225" s="3" t="inlineStr">
         <is>
-          <t>no_data</t>
+          <t>no_data (75)</t>
         </is>
       </c>
       <c r="I225" s="3" t="inlineStr">
@@ -13359,7 +12983,7 @@
       </c>
       <c r="H239" s="3" t="inlineStr">
         <is>
-          <t>no_data</t>
+          <t>no_data (75)</t>
         </is>
       </c>
       <c r="I239" s="3" t="inlineStr"/>
@@ -13394,7 +13018,7 @@
       </c>
       <c r="H240" s="3" t="inlineStr">
         <is>
-          <t>no_data</t>
+          <t>no_data (75)</t>
         </is>
       </c>
       <c r="I240" s="3" t="inlineStr">
@@ -14007,7 +13631,7 @@
       <c r="G257" s="5" t="inlineStr"/>
       <c r="H257" s="3" t="inlineStr">
         <is>
-          <t>key_person (80)</t>
+          <t>owner_dependency (80)</t>
         </is>
       </c>
       <c r="I257" s="3" t="inlineStr"/>
@@ -14172,7 +13796,7 @@
       <c r="G262" s="5" t="inlineStr"/>
       <c r="H262" s="3" t="inlineStr">
         <is>
-          <t>key_person (85), owner_trapped (60)</t>
+          <t>owner_dependency (85)</t>
         </is>
       </c>
       <c r="I262" s="3" t="inlineStr"/>
@@ -14272,7 +13896,7 @@
       <c r="H265" s="3" t="inlineStr"/>
       <c r="I265" s="3" t="inlineStr">
         <is>
-          <t>Promotes key_person to the top severity</t>
+          <t>Promotes owner_dependency to the top severity</t>
         </is>
       </c>
     </row>
@@ -14437,7 +14061,7 @@
       <c r="H270" s="3" t="inlineStr"/>
       <c r="I270" s="3" t="inlineStr">
         <is>
-          <t>Promotes key_person to the top severity</t>
+          <t>Promotes owner_dependency to the top severity</t>
         </is>
       </c>
     </row>
@@ -15012,7 +14636,7 @@
       <c r="G286" s="5" t="inlineStr"/>
       <c r="H286" s="3" t="inlineStr">
         <is>
-          <t>no_2ic (65)</t>
+          <t>owner_dependency (65)</t>
         </is>
       </c>
       <c r="I286" s="3" t="inlineStr"/>
@@ -15049,7 +14673,7 @@
       <c r="G287" s="5" t="inlineStr"/>
       <c r="H287" s="3" t="inlineStr">
         <is>
-          <t>no_2ic (100), key_person (90)</t>
+          <t>owner_dependency (100)</t>
         </is>
       </c>
       <c r="I287" s="3" t="inlineStr"/>
@@ -15082,7 +14706,7 @@
       <c r="G288" s="5" t="inlineStr"/>
       <c r="H288" s="3" t="inlineStr">
         <is>
-          <t>no_2ic (80)</t>
+          <t>owner_dependency (80)</t>
         </is>
       </c>
       <c r="I288" s="3" t="inlineStr">
@@ -15156,7 +14780,7 @@
       <c r="G290" s="5" t="inlineStr"/>
       <c r="H290" s="3" t="inlineStr">
         <is>
-          <t>owner_trapped (35)</t>
+          <t>owner_dependency (35)</t>
         </is>
       </c>
       <c r="I290" s="3" t="inlineStr"/>
@@ -15193,7 +14817,7 @@
       <c r="G291" s="5" t="inlineStr"/>
       <c r="H291" s="3" t="inlineStr">
         <is>
-          <t>owner_trapped (80)</t>
+          <t>owner_dependency (80)</t>
         </is>
       </c>
       <c r="I291" s="3" t="inlineStr"/>
@@ -15230,7 +14854,7 @@
       <c r="G292" s="5" t="inlineStr"/>
       <c r="H292" s="3" t="inlineStr">
         <is>
-          <t>owner_trapped (100), key_person (90)</t>
+          <t>owner_dependency (100)</t>
         </is>
       </c>
       <c r="I292" s="3" t="inlineStr"/>
@@ -15263,7 +14887,7 @@
       <c r="G293" s="5" t="inlineStr"/>
       <c r="H293" s="3" t="inlineStr">
         <is>
-          <t>owner_trapped (70), no_succession (70)</t>
+          <t>owner_dependency (70), no_succession (70)</t>
         </is>
       </c>
       <c r="I293" s="3" t="inlineStr">
@@ -16130,7 +15754,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>You're profitable on paper and short of cash in practice. The work is sold, the money hasn't landed, and there's nothing sitting there to fund the next job.</t>
+          <t>You're profitable on paper and short of cash in practice. The work is sold and the money hasn't landed, so there's nothing sitting there to fund the next job.</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr"/>
@@ -16658,7 +16282,7 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>One role. Named, hired, and given the authority to actually run what you hand over.</t>
+          <t>One role, hired with the authority to actually run what you hand over.</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr"/>
@@ -16700,7 +16324,7 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Write down everything you did last week, then mark what only you could have done. What's left is the job description.</t>
+          <t>List every task you touched last week. Against each one, write the name of the person who'd do it if you were away for a month. Any task with no name against it is the hire.</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr"/>
@@ -17182,7 +16806,7 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Value here means what the customer perceives, and it has nothing to do with your pricing or your margin. They buy, and then they stop, or they stay and give most of the work to somebody else.</t>
+          <t>Value here means what the customer perceives, and it has nothing to do with your pricing or your margin. They buy, then they either stop or start giving most of the work to somebody else.</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr"/>
@@ -17339,7 +16963,7 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Ring ten customers who stopped buying, or who cut back, and ask them straight. Not a survey. A phone call.</t>
+          <t>Ring ten customers who stopped buying or cut back, and ask them straight. Not a survey. A phone call.</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr"/>
@@ -17607,7 +17231,7 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>This isn't a sales technique problem. When the thing on the table is clear, priced, and it fits what the buyer came in for, an average salesperson closes it. Right now yours needs you in the room to make sense of it.</t>
+          <t>This isn't a sales technique problem. When the thing on the table is clearly priced and it fits what the buyer came in for, an average salesperson closes it. Right now yours needs you in the room to make sense of it.</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr"/>
@@ -17932,7 +17556,7 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Turn the tap on deliberately. One channel, run properly, before you touch a second.</t>
+          <t>Turn the tap on deliberately. One channel run properly, before you touch a second.</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr"/>
@@ -18127,7 +17751,7 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>You're busy, you're full, and there's nothing left at the end of it.</t>
+          <t>You're full and busy, and there's nothing left at the end of it.</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr"/>
@@ -18401,214 +18025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="100" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>One line only, no fix and no detail. Naming it proves the tool knows the difference between a cause and a shadow, and a full fix section would undo that. {d.primaryShort} resolves to the primary constraint's short name.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Constraint</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>The one line printed when this is a loud but downstream second finding</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>Variables in this row</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>cashflow</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Cash flow constrained</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>There's cash flow strain in your answers too. It sits downstream of the {d.primaryShort} problem and it should ease as that one moves.</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>{d.primaryShort}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>talent</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Talent constrained</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>A talent gap shows up in your answers as well. It's downstream of the {d.primaryShort} problem, so it isn't the thing to work on first.</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>{d.primaryShort}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>fulfilment</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Fulfilment constrained</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>You'll see fulfilment strain in here as well. That's downstream of the {d.primaryShort} problem, and it should settle once the layer above it is in place.</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>{d.primaryShort}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Value constrained</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Retention looks soft too. That's downstream of the {d.primaryShort} problem rather than a separate finding.</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>{d.primaryShort}</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>offer</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Offer constrained</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>The offer looks weak in places as well. Downstream of the {d.primaryShort} problem, and not worth touching yet.</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>{d.primaryShort}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>demand</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Demand constrained</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Demand reads thin too. It's downstream of the {d.primaryShort} problem, so leave it where it is.</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>{d.primaryShort}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>margin</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Margin constrained</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Margin looks tight as well. That's downstream of the {d.primaryShort} problem and it'll move when that does.</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>{d.primaryShort}</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A2:D9"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -18688,7 +18105,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>One piece of equipment or one vehicle is doing work you have no backup for. A breakdown, a theft or a long repair stops revenue you've already sold, and hire rates at short notice are set by people who know you're stuck.</t>
+          <t>One piece of equipment or one vehicle is doing work you have no backup for. A breakdown or a long repair stops revenue you've already sold, and hire rates at short notice are set by people who know you're stuck.</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -18723,13 +18140,13 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Your customers arrive {q43.band}. Channels change without asking you first, and an algorithm shift, a search update or one referrer going quiet can halve your enquiries inside a month.</t>
+          <t>Your customers arrive {q43.band}. Channels change without asking you first, and an algorithm shift or one referrer going quiet can halve your enquiries inside a month.</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>You weren't sure where your customers actually come from, which usually means one channel is doing more of the work than you think. A channel can change without asking you first, and an algorithm shift, a search update or one referrer going quiet can halve your enquiries inside a month.</t>
+          <t>You weren't sure where your customers actually come from, which usually means one channel is doing more of the work than you think. A channel can change without asking you first, and one referrer going quiet can halve your enquiries inside a month.</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -18766,12 +18183,12 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>One customer carries {q41.band} of your revenue. That customer can leave, go quiet, or get bought by someone who already has their own suppliers, and none of those are things you get a say in.</t>
+          <t>One customer carries {q41.band} of your revenue. That customer can leave, or get bought by someone who already has their own suppliers, and neither is something you get a say in.</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>One customer carries {q41.exact}% of your revenue. That customer can leave, go quiet, or get bought by someone who already has their own suppliers, and none of those are things you get a say in.</t>
+          <t>One customer carries {q41.exact}% of your revenue. That customer can leave, or get bought by someone who already has their own suppliers, and neither is something you get a say in.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
@@ -18844,7 +18261,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>The business sells into one city or region. A local downturn, a big competitor arriving, or a regulatory change hits all of your revenue at once rather than part of it.</t>
+          <t>The business sells into one city or region. A local downturn or a big competitor arriving hits all of your revenue at once rather than part of it.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr"/>
@@ -18879,7 +18296,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>One licence, accreditation or policy is the thing that lets you trade at all. Lose it, let it lapse, or fail an audit, and the business stops completely rather than slows down.</t>
+          <t>One licence or accreditation is the thing that lets you trade at all. Let it lapse and the business stops completely rather than slows down.</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr"/>
@@ -18904,32 +18321,40 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>key_person</t>
+          <t>key_product</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Key person</t>
+          <t>Key product</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>The business leans heavily on one person, and going by your answers that person is probably you. Illness, a resignation or a fortnight offline stops things that shouldn't be stoppable.</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr"/>
+          <t>{q42.band} of your revenue comes from one product or service line. That's fine while the market wants it, and it's a single point of failure the day the market moves or a competitor undercuts it.</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>{q42.exact}% of your revenue comes from one product or service line. That's fine while the market wants it, and it's a single point of failure the day the market moves or a competitor undercuts it.</t>
+        </is>
+      </c>
       <c r="F9" s="7" t="inlineStr"/>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Write down what they hold, then move one piece of it to somebody else this month.</t>
+          <t>Build a second line and sell it to the customers you already have.</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Repeat until nothing sits in one head, and test it by having them take a week off.</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr"/>
+          <t>Set a target for what share of revenue it should carry in twelve months, and check it quarterly.</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>{q42.band}, {q42.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -18939,75 +18364,75 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>key_product</t>
+          <t>key_supplier</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Key product</t>
+          <t>Key supplier</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>{q42.band} of your revenue comes from one product or service line. That's fine while the market wants it, and it's a single point of failure the day the market moves or a competitor undercuts it.</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>{q42.exact}% of your revenue comes from one product or service line. That's fine while the market wants it, and it's a single point of failure the day the market moves or a competitor undercuts it.</t>
-        </is>
-      </c>
+          <t>You've got one supplier with no ready replacement. Their price rise is your price rise, and their bad year is your bad year.</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr"/>
       <c r="F10" s="7" t="inlineStr"/>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Build a second line and sell it to the customers you already have.</t>
+          <t>Qualify a second supplier and give them ten percent of your volume. A backup you've never bought from isn't a backup.</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Set a target for what share of revenue it should carry in twelve months, and check it quarterly.</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>{q42.band}, {q42.exact}</t>
-        </is>
-      </c>
+          <t>Get lead times and pricing from your current one in writing, so a change is a conversation rather than a surprise.</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>concentration</t>
+          <t>fragility</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>key_supplier</t>
+          <t>no_buffer</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Key supplier</t>
+          <t>Thin cash buffer</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>You've got one supplier with no ready replacement. Their price rise is your price rise, their delay is your delay, and their bad year is your bad year.</t>
+          <t>You're holding {q8.band}. Every business runs into a bad month. Without a buffer, a bad month turns into a decision about who you can't pay.</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>You couldn't put a number on how long the business would last with no revenue, which is its own answer. Every business runs into a bad month, and without a buffer a bad month turns into a decision about who you can't pay.</t>
+        </is>
+      </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Qualify a second supplier and give them ten percent of your volume. A backup you've never bought from isn't a backup.</t>
+          <t>Build to one month of fixed costs in a separate account, then three.</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Get lead times and pricing from your current one in writing, so a change is a conversation rather than a surprise.</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr"/>
+          <t>Move a fixed percentage of every payment across automatically, so it isn't a decision you make each time.</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>{q8.band}</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -19017,32 +18442,40 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>no_2ic</t>
+          <t>no_contracts</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>No second in command</t>
+          <t>Uncommitted revenue</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>There's nobody who could run this if you stepped out. Every decision routes through you, which caps the business at the size of your week.</t>
+          <t>Your work is committed by {q45.band}. Revenue that can be cancelled in a phone call isn't revenue you can plan against or borrow against.</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr"/>
-      <c r="F12" s="7" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>You weren't sure how your work is actually committed by the customer. Revenue you can't describe the terms of isn't revenue you can plan against or borrow against.</t>
+        </is>
+      </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Name the person, tell them, and start handing over one area at a time with the decisions attached.</t>
+          <t>Put a written agreement behind every piece of work, with a scope and a notice period.</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Give them a budget and a limit they can act inside. A deputy who can't decide anything is a job title.</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr"/>
+          <t>Start with your largest customers, because that's where the exposure actually sits.</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>{q45.band}</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -19052,38 +18485,38 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>no_buffer</t>
+          <t>no_data</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>No cash buffer</t>
+          <t>Blind spot</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>You're holding {q8.band}. Every business runs into a bad month. Without a buffer, a bad month turns into a decision about who you can't pay.</t>
+          <t>You look at the numbers {q47.band}, and there were questions in here you couldn't answer. Running on feel works while the business is small enough to hold in your head. Past that, you're making decisions on a version of the business that's a few months out of date.</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr"/>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>You couldn't put a number on how long the business would last with no revenue, which is its own answer. Every business runs into a bad month, and without a buffer a bad month turns into a decision about who you can't pay.</t>
+          <t>There were questions in here you couldn't answer, and that's the finding. Running on feel works while the business is small enough to hold in your head. Past that, you're making decisions on a version of the business that's a few months out of date.</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Build to one month of fixed costs in a separate account, then three.</t>
+          <t>Pick five numbers and look at them weekly. Start with cash in the bank and margin on the last ten jobs.</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>Move a fixed percentage of every payment across automatically, so it isn't a decision you make each time.</t>
+          <t>One page, same day every week. The habit matters more than the tool you keep it in.</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>{q8.band}</t>
+          <t>{q47.band}</t>
         </is>
       </c>
     </row>
@@ -19095,124 +18528,124 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>no_contracts</t>
+          <t>no_process</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>No contracts</t>
+          <t>Undocumented delivery</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Your work is committed by {q45.band}. Revenue that can be cancelled in a phone call isn't revenue you can plan against, hire against or borrow against.</t>
+          <t>{q46.band} of the work is documented well enough that somebody else could pick it up and finish it. Every new hire takes longer than it should, and nothing can be handed over cleanly.</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr"/>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>You weren't sure how your work is actually committed by the customer. Revenue you can't describe the terms of isn't revenue you can plan against, hire against or borrow against.</t>
+          <t>You weren't sure how much of the work is documented, which almost always means less than you'd hope. Every new hire takes longer than it should, and nothing can be handed over cleanly.</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Put a written agreement behind every piece of work, with terms, scope and a notice period.</t>
+          <t>Record yourself doing the five things that go wrong most often, then turn each one into a one page checklist.</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>Start with your largest customers, because that's where the exposure actually sits.</t>
+          <t>Checklists beat manuals, because people actually use them.</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>{q45.band}</t>
+          <t>{q46.band}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>fragility</t>
+          <t>owner</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>no_data</t>
+          <t>model_misfit</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>Model misfit</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>You look at the numbers {q47.band}, and there were questions in here you couldn't answer. Running on feel works while the business is small enough to hold in your head. Past that, you're making decisions on a version of the business that's a few months out of date.</t>
+          <t>The way you spend your week is {q52.band}. It decides how long you'll keep doing this, and a business rarely outlives the owner's appetite for running it.</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr"/>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>There were questions in here you couldn't answer, and that's the finding. Running on feel works while the business is small enough to hold in your head. Past that, you're making decisions on a version of the business that's a few months out of date.</t>
+          <t>You weren't sure whether the way you spend your week matches what you wanted out of this. That question decides how long you'll keep doing it, and a business rarely outlives the owner's appetite for running it.</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Pick five numbers and look at them weekly. Cash in the bank, enquiries, close rate, jobs delivered, and margin on the last ten jobs.</t>
+          <t>Write down what you actually wanted out of this, then hold your week up against it.</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>One page, same day every week. The habit matters more than the tool you keep it in.</t>
+          <t>The gap between those two is the brief for the next twelve months.</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>{q47.band}</t>
+          <t>{q52.band}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>fragility</t>
+          <t>owner</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>no_process</t>
+          <t>no_succession</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>No documented process</t>
+          <t>Succession gap</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>{q46.band} of the work is documented well enough that somebody else could pick it up and finish it. Every new hire takes longer than it should, quality moves depending on who's on the job, and nothing can be handed over cleanly.</t>
+          <t>There's {q50.band} for what happens if you stop or sell. Every business has an exit, planned or not. The unplanned version is the one where somebody else sets the price.</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr"/>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>You weren't sure how much of the work is documented, which almost always means less than you'd hope. Every new hire takes longer than it should, quality moves depending on who's on the job, and nothing can be handed over cleanly.</t>
+          <t>You weren't sure what happens to the business if you stop or sell. Every business has an exit, planned or not. The unplanned version is the one where somebody else sets the price.</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Record yourself doing the five things that go wrong most often, then turn each one into a one page checklist.</t>
+          <t>Write the one page version. Who runs it, and what happens to the customers.</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>Checklists beat manuals, because people actually use them.</t>
+          <t>It doesn't need to be right, it needs to exist.</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>{q46.band}</t>
+          <t>{q50.band}</t>
         </is>
       </c>
     </row>
@@ -19224,38 +18657,38 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>model_misfit</t>
+          <t>owner_dependency</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Model misfit</t>
+          <t>Owner dependency</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>The way you spend your week is {q52.band}. It decides how long you'll keep doing this, and a business rarely outlives the owner's appetite for running it.</t>
+          <t>The business runs on you. Sold tomorrow a buyer would need you to stay {q49.band}, and there's nobody who could run it if you stepped out. That caps the business at the size of your week and it's what makes it hard to sell.</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr"/>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>You weren't sure whether the way you spend your week matches what you wanted out of this. That question decides how long you'll keep doing it, and a business rarely outlives the owner's appetite for running it.</t>
+          <t>The business runs on you, and you haven't put a number on how long a buyer would need you to stay. Until somebody else can run it, this is a job that owns you rather than an asset you own.</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Write down what you actually wanted out of this, then hold your week up against it.</t>
+          <t>Name the person who'd run it, tell them, and hand over one area at a time with the decisions attached.</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>The gap between those two is the brief for the next twelve months.</t>
+          <t>Give them a budget they can act inside. A deputy who can't decide anything is a job title.</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>{q52.band}</t>
+          <t>{q49.band}</t>
         </is>
       </c>
     </row>
@@ -19267,129 +18700,43 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>no_succession</t>
+          <t>personal_guarantee</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>No succession</t>
+          <t>Personal guarantee</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>There's {q50.band} for what happens if you stop, sell or step back. Every business has an exit, planned or otherwise. The unplanned version is the one where somebody else sets the price.</t>
+          <t>You've personally guaranteed {q51.band} of the business's obligations. The wall between business risk and personal risk isn't up, so a bad year in the business reaches your house.</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>You weren't sure what happens to the business if you stop, sell or step back. Every business has an exit, planned or otherwise. The unplanned version is the one where somebody else sets the price.</t>
+          <t>You weren't sure what you've personally guaranteed, and that's worth finding out this week. Where the wall between business risk and personal risk isn't up, a bad year in the business reaches your house.</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Write the one page version. Who runs it, what happens to the customers, what it's worth and who'd buy it.</t>
+          <t>List every guarantee you've signed and put a date against each one to renegotiate or release it.</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>It doesn't need to be right, it needs to exist.</t>
+          <t>Most get renewed on autopilot, because nobody asks.</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>{q50.band}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>owner_trapped</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Owner trapped</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Sold tomorrow, {q49.band}. How long that handover runs is what decides whether the business is worth anything to anyone but you, and it's the same thing that decides whether you can ever step back.</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr"/>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>You haven't thought about how long a buyer would need you to stay on, which is its own answer. Until somebody else can run it, the business is a job that owns you rather than an asset you own.</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>Work out what only you can do, then start moving everything else.</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>Book a month off twelve months out and work backwards from it. That's the deadline that makes it real.</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>{q49.band}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>personal_guarantee</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Personally guaranteed</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>You've personally guaranteed {q51.band} of the business's obligations. The wall between business risk and personal risk isn't up, so a bad year in the business reaches your house.</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr"/>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>You weren't sure what you've personally guaranteed, and that's worth finding out this week. Where the wall between business risk and personal risk isn't up, a bad year in the business reaches your house.</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>List every guarantee you've signed and put a date against each one to renegotiate or release it.</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>Most get renewed on autopilot, because nobody asks.</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
           <t>{q51.band}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H20"/>
+  <autoFilter ref="A2:H18"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -19397,7 +18744,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19450,7 +18797,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19637,7 +18984,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Don't take on a new market, product or location. All three land on your desk.</t>
+          <t>Don't take on a new market or a new location. Both land on your desk.</t>
         </is>
       </c>
     </row>
@@ -20209,4 +19556,351 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="98" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Blank line between paragraphs is written as two newlines in the source. Keep paragraphs short.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>When it is used</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Variables in this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Used whenever a constraint actually failed</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Everything below is calculated on your answers. It's a guide rather than a custom diagnostic, so read the report as a rough shape of what your current challenges are and what solutions may look like.
+It names your biggest single constraint. There is likely more, and there may be other things wrong, there always are. They're not listed in here because the order you fix things in matters. Fix the constraints and risks in your business, then come back and get an updated report.</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>wellRun</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Nothing cleared the floor. Nothing is failing</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Everything below is calculated on your answers. Nothing in them is close to failing, which is a real result and rarer than you'd think.
+What follows is the tightest thing in the business rather than a problem. Treat it as where the next bit of growth comes from, not something to fix.</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>noneSevere</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Nothing failed outright but something is tight</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Everything below is calculated on your answers. Nothing in them is screaming, which is worth knowing on its own.
+What follows is the tightest thing in the business rather than something that's failing outright. It's the next thing to work on, not an emergency.</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>tooUnsure</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Too many Not sure answers to stand behind a diagnosis</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Everything below is calculated on your answers, and there were a lot of them you couldn't answer, so read it as provisional.
+The finding below is the best available reading of what you did tell us. The bigger issue is that the business isn't visible to you, and that's covered in the risks. Come back and run it again once you can answer the numbers.</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>privacy</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Small print under the opening, on every report</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>We do not use any AI in this tool, and none of your data is sent or stored offsite.</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Heading</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>titleUnsure</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Replaces the constraint heading when there is not enough to call it</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>There isn't enough here to call it</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>looseBody</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Replaces the constraint block when nothing is failing</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Nothing in here is failing, so there's no evidence to walk you through. What you've got is {d.primaryShort} sitting as the tightest of the seven right now, which makes it the likeliest place the next bit of growth comes from. The actions below are worth doing and none of them are urgent.</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>{d.primaryShort}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>unsureBody</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Replaces the constraint block when there were too many Not sure answers</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>There isn't enough here to point at one thing with any confidence. On what you did answer, {d.primaryShort} is the tightest of the seven, so read the actions below as a starting point rather than a diagnosis.
+The risk section is the part of this report to take seriously. Not being able to answer the questions is the finding, and it's the one worth acting on first.</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>{d.primaryShort}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Normal close</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>That's the diagnosis. One constraint, and the things to leave alone while you fix it.
+Work the constraint and check back in ninety days. That's long enough for it to move and short enough that you'll still remember what you changed.</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>loose</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Close used when nothing is failing</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>That's the read. One thing to push on, and nothing in the way of it.
+Run this again in ninety days, or whenever something material changes. The constraint moves as the business grows, and the answer you get next time probably won't be this one.</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>unsure</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Close used when there were too many Not sure answers</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>That's as far as your answers go. One provisional reading, and a clear picture of what the business can't currently tell you.
+Get the numbers visible, then run this again. The second time through it will be worth something.</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>cta</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Call to action. Deliberately empty, still an open question</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:E14"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/diagnostic/Business-Diagnostic-Spec.xlsx
+++ b/diagnostic/Business-Diagnostic-Spec.xlsx
@@ -25,13 +25,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Answer options'!$A$2:$I$305</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Constraints and order'!$A$2:$G$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Report, constraint'!$A$2:$E$107</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Report, risk flags'!$A$2:$H$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Report, risk flags'!$A$2:$H$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Report, risk section'!$A$2:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Report, don''t do yet'!$A$2:$C$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Report, open and close'!$A$2:$E$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Thresholds'!$A$2:$C$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Logic'!$A$1:$B$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Data slots'!$A$2:$F$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Data slots'!$A$2:$F$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1105,7 +1105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>constraintDef / cashflow / evidence [5] / banded  riskDef / no_buffer / banded</t>
+          <t>constraintDef / cashflow / evidence [5] / banded</t>
         </is>
       </c>
     </row>
@@ -2358,50 +2358,50 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>{q45.band}</t>
+          <t>{q49.band}</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>How is your work actually committed by the customer?</t>
+          <t>If you sold the business tomorrow, how long would the buyer need you to stay on?</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>term contracts | job by job agreements | a month to month arrangement | a handshake and an email</t>
+          <t>a buyer wouldn't need you at all | a buyer would need you for a few weeks of handover | a buyer would need you for the best part of a year | a buyer would need you for years, if it works without you at all</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>clause is dropped on: Not sure</t>
+          <t>clause is dropped on: Never thought about it</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>riskDef / no_contracts / banded</t>
+          <t>riskDef / owner_dependency / banded</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>{q46.band}</t>
+          <t>{q50.band}</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>How much of the work is documented well enough that someone else could pick it up and finish it?</t>
+          <t>Is there a plan for what happens to the business if you stop, sell or step back?</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Most | About half | Almost none</t>
+          <t>a written plan | a rough idea | nothing</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2411,27 +2411,27 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>riskDef / no_process / banded</t>
+          <t>riskDef / no_succession / banded</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>{q47.band}</t>
+          <t>{q51.band}</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>How often do you look at numbers that tell you how the business is travelling?</t>
+          <t>Have you personally guaranteed any of the business's debt, leases or facilities?</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>weekly | monthly | once a year at tax time | next to never</t>
+          <t>none | a small amount | a significant amount</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -2441,188 +2441,98 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>riskDef / no_data / banded</t>
+          <t>riskDef / personal_guarantee / banded</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>{q49.band}</t>
+          <t>{q52.band}</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>If you sold the business tomorrow, how long would the buyer need you to stay on?</t>
+          <t>How well does the way you spend your week match what you wanted out of this business?</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>a buyer wouldn't need you at all | a buyer would need you for a few weeks of handover | a buyer would need you for the best part of a year | a buyer would need you for years, if it works without you at all</t>
+          <t>close to what you signed up for | only partly a match for what you wanted | the opposite of what you wanted</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>clause is dropped on: Never thought about it</t>
+          <t>clause is dropped on: Not sure</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>riskDef / owner_dependency / banded</t>
+          <t>riskDef / model_misfit / banded</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>{q50.band}</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="n">
-        <v>56</v>
-      </c>
+          <t>{d.primaryShort}</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr"/>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Is there a plan for what happens to the business if you stop, sell or step back?</t>
+          <t>derived, not a question</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>a written plan | a rough idea | nothing</t>
+          <t>the primary constraint's short name, lower case</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>clause is dropped on: Not sure</t>
+          <t>always resolves</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>riskDef / no_succession / banded</t>
+          <t>looseBody  unsureBody</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>{q51.band}</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="n">
-        <v>57</v>
-      </c>
+          <t>{d.unownedLayers}</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr"/>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Have you personally guaranteed any of the business's debt, leases or facilities?</t>
+          <t>derived, not a question</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>none | a small amount | a significant amount</t>
+          <t>a sentence naming which layers sit with the owner</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>clause is dropped on: Not sure</t>
+          <t>always resolves</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>riskDef / personal_guarantee / banded</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>{q52.band}</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>How well does the way you spend your week match what you wanted out of this business?</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>close to what you signed up for | only partly a match for what you wanted | the opposite of what you wanted</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>clause is dropped on: Not sure</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>riskDef / model_misfit / banded</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>{d.primaryShort}</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr"/>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>derived, not a question</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>the primary constraint's short name, lower case</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>always resolves</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>looseBody  unsureBody</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>{d.unownedLayers}</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr"/>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>derived, not a question</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>a sentence naming which layers sit with the owner</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>always resolves</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
           <t>constraintDef / talent / open [2]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F51"/>
+  <autoFilter ref="A2:F48"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -6520,11 +6430,7 @@
       <c r="G54" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>no_buffer (75)</t>
-        </is>
-      </c>
+      <c r="H54" s="3" t="inlineStr"/>
       <c r="I54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
@@ -6559,11 +6465,7 @@
       <c r="G55" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>no_buffer (75)</t>
-        </is>
-      </c>
+      <c r="H55" s="3" t="inlineStr"/>
       <c r="I55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
@@ -6594,11 +6496,7 @@
       <c r="G56" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>no_buffer (75)</t>
-        </is>
-      </c>
+      <c r="H56" s="3" t="inlineStr"/>
       <c r="I56" s="3" t="inlineStr">
         <is>
           <t>Not sure, scores nothing and feeds data blindness</t>
@@ -7092,11 +6990,7 @@
       <c r="G70" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>no_data (80)</t>
-        </is>
-      </c>
+      <c r="H70" s="3" t="inlineStr"/>
       <c r="I70" s="3" t="inlineStr">
         <is>
           <t>Not sure, scores nothing and feeds data blindness</t>
@@ -9593,11 +9487,7 @@
       <c r="G143" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H143" s="3" t="inlineStr">
-        <is>
-          <t>no_data (70)</t>
-        </is>
-      </c>
+      <c r="H143" s="3" t="inlineStr"/>
       <c r="I143" s="3" t="inlineStr">
         <is>
           <t>Not sure, scores nothing and feeds data blindness</t>
@@ -10231,11 +10121,7 @@
       <c r="G161" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="H161" s="3" t="inlineStr">
-        <is>
-          <t>no_data (75)</t>
-        </is>
-      </c>
+      <c r="H161" s="3" t="inlineStr"/>
       <c r="I161" s="3" t="inlineStr"/>
     </row>
     <row r="162">
@@ -10266,11 +10152,7 @@
       <c r="G162" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H162" s="3" t="inlineStr">
-        <is>
-          <t>no_data (75)</t>
-        </is>
-      </c>
+      <c r="H162" s="3" t="inlineStr"/>
       <c r="I162" s="3" t="inlineStr">
         <is>
           <t>Not sure, scores nothing and feeds data blindness</t>
@@ -10445,11 +10327,7 @@
       <c r="G167" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H167" s="3" t="inlineStr">
-        <is>
-          <t>no_data (75)</t>
-        </is>
-      </c>
+      <c r="H167" s="3" t="inlineStr"/>
       <c r="I167" s="3" t="inlineStr">
         <is>
           <t>Not sure, scores nothing and feeds data blindness</t>
@@ -10628,11 +10506,7 @@
       <c r="G172" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="H172" s="3" t="inlineStr">
-        <is>
-          <t>no_data (75)</t>
-        </is>
-      </c>
+      <c r="H172" s="3" t="inlineStr"/>
       <c r="I172" s="3" t="inlineStr"/>
     </row>
     <row r="173">
@@ -10663,11 +10537,7 @@
       <c r="G173" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H173" s="3" t="inlineStr">
-        <is>
-          <t>no_data (75)</t>
-        </is>
-      </c>
+      <c r="H173" s="3" t="inlineStr"/>
       <c r="I173" s="3" t="inlineStr">
         <is>
           <t>Not sure, scores nothing and feeds data blindness</t>
@@ -11017,11 +10887,7 @@
       <c r="G183" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H183" s="3" t="inlineStr">
-        <is>
-          <t>no_data (75)</t>
-        </is>
-      </c>
+      <c r="H183" s="3" t="inlineStr"/>
       <c r="I183" s="3" t="inlineStr">
         <is>
           <t>Not sure, scores nothing and feeds data blindness</t>
@@ -11406,11 +11272,7 @@
       <c r="G194" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H194" s="3" t="inlineStr">
-        <is>
-          <t>no_data (75)</t>
-        </is>
-      </c>
+      <c r="H194" s="3" t="inlineStr"/>
       <c r="I194" s="3" t="inlineStr">
         <is>
           <t>Not sure, scores nothing and feeds data blindness</t>
@@ -11662,11 +11524,7 @@
       <c r="G202" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="H202" s="3" t="inlineStr">
-        <is>
-          <t>no_data (75)</t>
-        </is>
-      </c>
+      <c r="H202" s="3" t="inlineStr"/>
       <c r="I202" s="3" t="inlineStr">
         <is>
           <t>Clears every other tick</t>
@@ -11841,11 +11699,7 @@
       <c r="G207" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H207" s="3" t="inlineStr">
-        <is>
-          <t>no_data (75)</t>
-        </is>
-      </c>
+      <c r="H207" s="3" t="inlineStr"/>
       <c r="I207" s="3" t="inlineStr">
         <is>
           <t>Not sure, scores nothing and feeds data blindness</t>
@@ -12304,11 +12158,7 @@
       <c r="G220" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H220" s="3" t="inlineStr">
-        <is>
-          <t>no_data (75)</t>
-        </is>
-      </c>
+      <c r="H220" s="3" t="inlineStr"/>
       <c r="I220" s="3" t="inlineStr">
         <is>
           <t>Not sure, scores nothing and feeds data blindness</t>
@@ -12483,11 +12333,7 @@
       <c r="G225" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H225" s="3" t="inlineStr">
-        <is>
-          <t>no_data (75)</t>
-        </is>
-      </c>
+      <c r="H225" s="3" t="inlineStr"/>
       <c r="I225" s="3" t="inlineStr">
         <is>
           <t>Not sure, scores nothing and feeds data blindness</t>
@@ -12981,11 +12827,7 @@
       <c r="G239" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="H239" s="3" t="inlineStr">
-        <is>
-          <t>no_data (75)</t>
-        </is>
-      </c>
+      <c r="H239" s="3" t="inlineStr"/>
       <c r="I239" s="3" t="inlineStr"/>
     </row>
     <row r="240">
@@ -13016,11 +12858,7 @@
       <c r="G240" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H240" s="3" t="inlineStr">
-        <is>
-          <t>no_data (75)</t>
-        </is>
-      </c>
+      <c r="H240" s="3" t="inlineStr"/>
       <c r="I240" s="3" t="inlineStr">
         <is>
           <t>Not sure, scores nothing and feeds data blindness</t>
@@ -13234,11 +13072,7 @@
       </c>
       <c r="F246" s="7" t="inlineStr"/>
       <c r="G246" s="5" t="inlineStr"/>
-      <c r="H246" s="3" t="inlineStr">
-        <is>
-          <t>no_data (70)</t>
-        </is>
-      </c>
+      <c r="H246" s="3" t="inlineStr"/>
       <c r="I246" s="3" t="inlineStr">
         <is>
           <t>Not sure, scores nothing and feeds data blindness</t>
@@ -13415,11 +13249,7 @@
       </c>
       <c r="F251" s="7" t="inlineStr"/>
       <c r="G251" s="5" t="inlineStr"/>
-      <c r="H251" s="3" t="inlineStr">
-        <is>
-          <t>no_data (70)</t>
-        </is>
-      </c>
+      <c r="H251" s="3" t="inlineStr"/>
       <c r="I251" s="3" t="inlineStr">
         <is>
           <t>Not sure, scores nothing and feeds data blindness</t>
@@ -13561,7 +13391,7 @@
       <c r="G255" s="5" t="inlineStr"/>
       <c r="H255" s="3" t="inlineStr">
         <is>
-          <t>no_data (70), key_channel (50)</t>
+          <t>key_channel (50)</t>
         </is>
       </c>
       <c r="I255" s="3" t="inlineStr">
@@ -14128,11 +13958,7 @@
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr"/>
-      <c r="H272" s="3" t="inlineStr">
-        <is>
-          <t>no_contracts (35)</t>
-        </is>
-      </c>
+      <c r="H272" s="3" t="inlineStr"/>
       <c r="I272" s="3" t="inlineStr"/>
     </row>
     <row r="273">
@@ -14167,7 +13993,7 @@
       <c r="G273" s="5" t="inlineStr"/>
       <c r="H273" s="3" t="inlineStr">
         <is>
-          <t>no_contracts (75)</t>
+          <t>key_client (70)</t>
         </is>
       </c>
       <c r="I273" s="3" t="inlineStr"/>
@@ -14204,7 +14030,7 @@
       <c r="G274" s="5" t="inlineStr"/>
       <c r="H274" s="3" t="inlineStr">
         <is>
-          <t>no_contracts (95)</t>
+          <t>key_client (90)</t>
         </is>
       </c>
       <c r="I274" s="3" t="inlineStr"/>
@@ -14237,7 +14063,7 @@
       <c r="G275" s="5" t="inlineStr"/>
       <c r="H275" s="3" t="inlineStr">
         <is>
-          <t>no_data (70), no_contracts (60)</t>
+          <t>key_client (60)</t>
         </is>
       </c>
       <c r="I275" s="3" t="inlineStr">
@@ -14311,7 +14137,7 @@
       <c r="G277" s="5" t="inlineStr"/>
       <c r="H277" s="3" t="inlineStr">
         <is>
-          <t>no_process (55)</t>
+          <t>key_employee (45)</t>
         </is>
       </c>
       <c r="I277" s="3" t="inlineStr"/>
@@ -14348,7 +14174,7 @@
       <c r="G278" s="5" t="inlineStr"/>
       <c r="H278" s="3" t="inlineStr">
         <is>
-          <t>no_process (95)</t>
+          <t>key_employee (85)</t>
         </is>
       </c>
       <c r="I278" s="3" t="inlineStr"/>
@@ -14381,7 +14207,7 @@
       <c r="G279" s="5" t="inlineStr"/>
       <c r="H279" s="3" t="inlineStr">
         <is>
-          <t>no_process (80), no_data (60)</t>
+          <t>key_employee (50)</t>
         </is>
       </c>
       <c r="I279" s="3" t="inlineStr">
@@ -14453,11 +14279,7 @@
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr"/>
-      <c r="H281" s="3" t="inlineStr">
-        <is>
-          <t>no_data (25)</t>
-        </is>
-      </c>
+      <c r="H281" s="3" t="inlineStr"/>
       <c r="I281" s="3" t="inlineStr"/>
     </row>
     <row r="282">
@@ -14490,11 +14312,7 @@
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr"/>
-      <c r="H282" s="3" t="inlineStr">
-        <is>
-          <t>no_data (90)</t>
-        </is>
-      </c>
+      <c r="H282" s="3" t="inlineStr"/>
       <c r="I282" s="3" t="inlineStr"/>
     </row>
     <row r="283">
@@ -14527,11 +14345,7 @@
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr"/>
-      <c r="H283" s="3" t="inlineStr">
-        <is>
-          <t>no_data (100)</t>
-        </is>
-      </c>
+      <c r="H283" s="3" t="inlineStr"/>
       <c r="I283" s="3" t="inlineStr"/>
     </row>
     <row r="284">
@@ -14560,11 +14374,7 @@
       </c>
       <c r="F284" s="7" t="inlineStr"/>
       <c r="G284" s="5" t="inlineStr"/>
-      <c r="H284" s="3" t="inlineStr">
-        <is>
-          <t>no_data (90)</t>
-        </is>
-      </c>
+      <c r="H284" s="3" t="inlineStr"/>
       <c r="I284" s="3" t="inlineStr">
         <is>
           <t>Not sure, scores nothing and feeds data blindness</t>
@@ -14636,7 +14446,7 @@
       <c r="G286" s="5" t="inlineStr"/>
       <c r="H286" s="3" t="inlineStr">
         <is>
-          <t>owner_dependency (65)</t>
+          <t>owner_dependency (45)</t>
         </is>
       </c>
       <c r="I286" s="3" t="inlineStr"/>
@@ -14961,7 +14771,7 @@
       <c r="G295" s="5" t="inlineStr"/>
       <c r="H295" s="3" t="inlineStr">
         <is>
-          <t>no_succession (60)</t>
+          <t>no_succession (40)</t>
         </is>
       </c>
       <c r="I295" s="3" t="inlineStr"/>
@@ -15175,7 +14985,7 @@
       <c r="G301" s="5" t="inlineStr"/>
       <c r="H301" s="3" t="inlineStr">
         <is>
-          <t>personal_guarantee (75), no_data (60)</t>
+          <t>personal_guarantee (75)</t>
         </is>
       </c>
       <c r="I301" s="3" t="inlineStr">
@@ -15319,7 +15129,7 @@
       <c r="G305" s="5" t="inlineStr"/>
       <c r="H305" s="3" t="inlineStr">
         <is>
-          <t>model_misfit (60)</t>
+          <t>model_misfit (45)</t>
         </is>
       </c>
       <c r="I305" s="3" t="inlineStr">
@@ -18025,7 +17835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -18048,7 +17858,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -18090,7 +17900,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>concentration</t>
+          <t>Concentration</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -18121,11 +17931,12 @@
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>concentration</t>
+          <t>Concentration</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -18159,7 +17970,8 @@
           <t>Write down what you'd do if the current one halved tomorrow. That plan is worth having on paper before you need it.</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>{q43.band}</t>
         </is>
@@ -18168,7 +17980,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>concentration</t>
+          <t>Concentration</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -18204,6 +18016,11 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
+          <t>If the work is committed on a handshake, that is the first conversation to have, before the ceiling.</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
           <t>{q41.band}, {q41.exact}</t>
         </is>
       </c>
@@ -18211,7 +18028,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>concentration</t>
+          <t>Concentration</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -18226,7 +18043,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>One person knows how the work actually gets done and it isn't written down anywhere else. If they leave, the knowledge goes with them, and you'll be rebuilding it from scratch while still trying to deliver.</t>
+          <t>One person knows how the work actually gets done, and very little of it is written down anywhere else. If they leave, the knowledge goes with them, and you'll be rebuilding it from scratch while still trying to deliver.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr"/>
@@ -18241,12 +18058,17 @@
           <t>Put a second person alongside them on the next three jobs, doing rather than watching.</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Record the five things that go wrong most often as one page checklists. People use checklists, they don't use manuals.</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>concentration</t>
+          <t>Concentration</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -18277,11 +18099,12 @@
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>concentration</t>
+          <t>Concentration</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -18312,11 +18135,12 @@
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>concentration</t>
+          <t>Concentration</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -18350,7 +18174,8 @@
           <t>Set a target for what share of revenue it should carry in twelve months, and check it quarterly.</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>{q42.band}, {q42.exact}</t>
         </is>
@@ -18359,7 +18184,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>concentration</t>
+          <t>Concentration</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -18390,353 +18215,190 @@
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>fragility</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>no_buffer</t>
+          <t>model_misfit</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Thin cash buffer</t>
+          <t>Model misfit</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>You're holding {q8.band}. Every business runs into a bad month. Without a buffer, a bad month turns into a decision about who you can't pay.</t>
+          <t>The way you spend your week is {q52.band}. It decides how long you'll keep doing this, and a business rarely outlives the owner's appetite for running it.</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr"/>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>You couldn't put a number on how long the business would last with no revenue, which is its own answer. Every business runs into a bad month, and without a buffer a bad month turns into a decision about who you can't pay.</t>
+          <t>You weren't sure whether the way you spend your week matches what you wanted out of this. That question decides how long you'll keep doing it, and a business rarely outlives the owner's appetite for running it.</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Build to one month of fixed costs in a separate account, then three.</t>
+          <t>Write down what you actually wanted out of this, then hold your week up against it.</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Move a fixed percentage of every payment across automatically, so it isn't a decision you make each time.</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>{q8.band}</t>
+          <t>The gap between those two is the brief for the next twelve months.</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>{q52.band}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>fragility</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>no_contracts</t>
+          <t>no_succession</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Uncommitted revenue</t>
+          <t>Succession gap</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Your work is committed by {q45.band}. Revenue that can be cancelled in a phone call isn't revenue you can plan against or borrow against.</t>
+          <t>There's {q50.band} for what happens if you stop or sell. Every business has an exit, planned or not. The unplanned version is the one where somebody else sets the price.</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr"/>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>You weren't sure how your work is actually committed by the customer. Revenue you can't describe the terms of isn't revenue you can plan against or borrow against.</t>
+          <t>You weren't sure what happens to the business if you stop or sell. Every business has an exit, planned or not. The unplanned version is the one where somebody else sets the price.</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Put a written agreement behind every piece of work, with a scope and a notice period.</t>
+          <t>Write the one page version. Who runs it, and what happens to the customers.</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Start with your largest customers, because that's where the exposure actually sits.</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>{q45.band}</t>
+          <t>It doesn't need to be right, it needs to exist.</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>{q50.band}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>fragility</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>no_data</t>
+          <t>owner_dependency</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Blind spot</t>
+          <t>Owner dependency</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>You look at the numbers {q47.band}, and there were questions in here you couldn't answer. Running on feel works while the business is small enough to hold in your head. Past that, you're making decisions on a version of the business that's a few months out of date.</t>
+          <t>The business runs on you. Sold tomorrow a buyer would need you to stay {q49.band}, and there's nobody who could run it if you stepped out. That caps the business at the size of your week and it's what makes it hard to sell.</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr"/>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>There were questions in here you couldn't answer, and that's the finding. Running on feel works while the business is small enough to hold in your head. Past that, you're making decisions on a version of the business that's a few months out of date.</t>
+          <t>The business runs on you, and you haven't put a number on how long a buyer would need you to stay. Until somebody else can run it, this is a job that owns you rather than an asset you own.</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Pick five numbers and look at them weekly. Start with cash in the bank and margin on the last ten jobs.</t>
+          <t>Name the person who'd run it, tell them, and hand over one area at a time with the decisions attached.</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>One page, same day every week. The habit matters more than the tool you keep it in.</t>
+          <t>Give them a budget they can act inside. A deputy who can't decide anything is a job title.</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>{q47.band}</t>
+          <t>Book a month off twelve months out and work backwards from it. That's the deadline that makes it real.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>{q49.band}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>fragility</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>no_process</t>
+          <t>personal_guarantee</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Undocumented delivery</t>
+          <t>Personal guarantee</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>{q46.band} of the work is documented well enough that somebody else could pick it up and finish it. Every new hire takes longer than it should, and nothing can be handed over cleanly.</t>
+          <t>You've personally guaranteed {q51.band} of the business's obligations. The wall between business risk and personal risk isn't up, so a bad year in the business reaches your house.</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr"/>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>You weren't sure how much of the work is documented, which almost always means less than you'd hope. Every new hire takes longer than it should, and nothing can be handed over cleanly.</t>
+          <t>You weren't sure what you've personally guaranteed, and that's worth finding out this week. Where the wall between business risk and personal risk isn't up, a bad year in the business reaches your house.</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Record yourself doing the five things that go wrong most often, then turn each one into a one page checklist.</t>
+          <t>List every guarantee you've signed and put a date against each one to renegotiate or release it.</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>Checklists beat manuals, because people actually use them.</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>{q46.band}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>model_misfit</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Model misfit</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>The way you spend your week is {q52.band}. It decides how long you'll keep doing this, and a business rarely outlives the owner's appetite for running it.</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr"/>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>You weren't sure whether the way you spend your week matches what you wanted out of this. That question decides how long you'll keep doing it, and a business rarely outlives the owner's appetite for running it.</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Write down what you actually wanted out of this, then hold your week up against it.</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>The gap between those two is the brief for the next twelve months.</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>{q52.band}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>no_succession</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Succession gap</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>There's {q50.band} for what happens if you stop or sell. Every business has an exit, planned or not. The unplanned version is the one where somebody else sets the price.</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr"/>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>You weren't sure what happens to the business if you stop or sell. Every business has an exit, planned or not. The unplanned version is the one where somebody else sets the price.</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>Write the one page version. Who runs it, and what happens to the customers.</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>It doesn't need to be right, it needs to exist.</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>{q50.band}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>owner_dependency</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Owner dependency</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>The business runs on you. Sold tomorrow a buyer would need you to stay {q49.band}, and there's nobody who could run it if you stepped out. That caps the business at the size of your week and it's what makes it hard to sell.</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr"/>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>The business runs on you, and you haven't put a number on how long a buyer would need you to stay. Until somebody else can run it, this is a job that owns you rather than an asset you own.</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>Name the person who'd run it, tell them, and hand over one area at a time with the decisions attached.</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>Give them a budget they can act inside. A deputy who can't decide anything is a job title.</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>{q49.band}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>personal_guarantee</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Personal guarantee</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>You've personally guaranteed {q51.band} of the business's obligations. The wall between business risk and personal risk isn't up, so a bad year in the business reaches your house.</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr"/>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>You weren't sure what you've personally guaranteed, and that's worth finding out this week. Where the wall between business risk and personal risk isn't up, a bad year in the business reaches your house.</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>List every guarantee you've signed and put a date against each one to renegotiate or release it.</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
           <t>Most get renewed on autopilot, because nobody asks.</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>{q51.band}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H18"/>
+  <autoFilter ref="A2:H14"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -18760,7 +18422,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Risks print as one list, loudest first, regardless of which family they came from. Families still weight the internal ordering, they no longer split the section. The old family framing block, the separate minor risk section and the compound blocks were all removed after they read as filler in testing.</t>
+          <t>Risks print as one list, loudest first, regardless of group. The old family framing, the separate minor risk section and the compound blocks were all removed after they read as filler in testing.</t>
         </is>
       </c>
     </row>

--- a/diagnostic/Business-Diagnostic-Spec.xlsx
+++ b/diagnostic/Business-Diagnostic-Spec.xlsx
@@ -25,7 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Answer options'!$A$2:$I$305</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Constraints and order'!$A$2:$G$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Report, constraint'!$A$2:$E$107</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Report, risk flags'!$A$2:$H$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Report, risk flags'!$A$2:$H$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Report, risk section'!$A$2:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Report, don''t do yet'!$A$2:$C$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Report, open and close'!$A$2:$E$14</definedName>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>riskDef / owner_dependency / banded</t>
+          <t>riskDef / key_person / banded</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>owner_dependency (75)</t>
+          <t>key_person (75)</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>owner_dependency (75)</t>
+          <t>key_person (75)</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr"/>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>owner_dependency (75)</t>
+          <t>key_person (75)</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr"/>
@@ -13461,7 +13461,7 @@
       <c r="G257" s="5" t="inlineStr"/>
       <c r="H257" s="3" t="inlineStr">
         <is>
-          <t>owner_dependency (80)</t>
+          <t>key_person (80)</t>
         </is>
       </c>
       <c r="I257" s="3" t="inlineStr"/>
@@ -13494,7 +13494,7 @@
       <c r="G258" s="5" t="inlineStr"/>
       <c r="H258" s="3" t="inlineStr">
         <is>
-          <t>key_employee (85)</t>
+          <t>key_person (85)</t>
         </is>
       </c>
       <c r="I258" s="3" t="inlineStr"/>
@@ -13527,7 +13527,7 @@
       <c r="G259" s="5" t="inlineStr"/>
       <c r="H259" s="3" t="inlineStr">
         <is>
-          <t>key_asset (75)</t>
+          <t>key_supplier (75)</t>
         </is>
       </c>
       <c r="I259" s="3" t="inlineStr"/>
@@ -13558,11 +13558,7 @@
       </c>
       <c r="F260" s="7" t="inlineStr"/>
       <c r="G260" s="5" t="inlineStr"/>
-      <c r="H260" s="3" t="inlineStr">
-        <is>
-          <t>key_geography (70)</t>
-        </is>
-      </c>
+      <c r="H260" s="3" t="inlineStr"/>
       <c r="I260" s="3" t="inlineStr"/>
     </row>
     <row r="261">
@@ -13626,7 +13622,7 @@
       <c r="G262" s="5" t="inlineStr"/>
       <c r="H262" s="3" t="inlineStr">
         <is>
-          <t>owner_dependency (85)</t>
+          <t>key_person (85)</t>
         </is>
       </c>
       <c r="I262" s="3" t="inlineStr"/>
@@ -13726,7 +13722,7 @@
       <c r="H265" s="3" t="inlineStr"/>
       <c r="I265" s="3" t="inlineStr">
         <is>
-          <t>Promotes owner_dependency to the top severity</t>
+          <t>Promotes key_person to the top severity</t>
         </is>
       </c>
     </row>
@@ -13759,7 +13755,7 @@
       <c r="H266" s="3" t="inlineStr"/>
       <c r="I266" s="3" t="inlineStr">
         <is>
-          <t>Promotes key_employee to the top severity</t>
+          <t>Promotes key_person to the top severity</t>
         </is>
       </c>
     </row>
@@ -13792,7 +13788,7 @@
       <c r="H267" s="3" t="inlineStr"/>
       <c r="I267" s="3" t="inlineStr">
         <is>
-          <t>Promotes key_asset to the top severity</t>
+          <t>Promotes key_supplier to the top severity</t>
         </is>
       </c>
     </row>
@@ -13891,7 +13887,7 @@
       <c r="H270" s="3" t="inlineStr"/>
       <c r="I270" s="3" t="inlineStr">
         <is>
-          <t>Promotes owner_dependency to the top severity</t>
+          <t>Promotes key_person to the top severity</t>
         </is>
       </c>
     </row>
@@ -14137,7 +14133,7 @@
       <c r="G277" s="5" t="inlineStr"/>
       <c r="H277" s="3" t="inlineStr">
         <is>
-          <t>key_employee (45)</t>
+          <t>key_person (45)</t>
         </is>
       </c>
       <c r="I277" s="3" t="inlineStr"/>
@@ -14174,7 +14170,7 @@
       <c r="G278" s="5" t="inlineStr"/>
       <c r="H278" s="3" t="inlineStr">
         <is>
-          <t>key_employee (85)</t>
+          <t>key_person (85)</t>
         </is>
       </c>
       <c r="I278" s="3" t="inlineStr"/>
@@ -14207,7 +14203,7 @@
       <c r="G279" s="5" t="inlineStr"/>
       <c r="H279" s="3" t="inlineStr">
         <is>
-          <t>key_employee (50)</t>
+          <t>key_person (50)</t>
         </is>
       </c>
       <c r="I279" s="3" t="inlineStr">
@@ -14446,7 +14442,7 @@
       <c r="G286" s="5" t="inlineStr"/>
       <c r="H286" s="3" t="inlineStr">
         <is>
-          <t>owner_dependency (45)</t>
+          <t>key_person (45)</t>
         </is>
       </c>
       <c r="I286" s="3" t="inlineStr"/>
@@ -14483,7 +14479,7 @@
       <c r="G287" s="5" t="inlineStr"/>
       <c r="H287" s="3" t="inlineStr">
         <is>
-          <t>owner_dependency (100)</t>
+          <t>key_person (100)</t>
         </is>
       </c>
       <c r="I287" s="3" t="inlineStr"/>
@@ -14516,7 +14512,7 @@
       <c r="G288" s="5" t="inlineStr"/>
       <c r="H288" s="3" t="inlineStr">
         <is>
-          <t>owner_dependency (80)</t>
+          <t>key_person (80)</t>
         </is>
       </c>
       <c r="I288" s="3" t="inlineStr">
@@ -14590,7 +14586,7 @@
       <c r="G290" s="5" t="inlineStr"/>
       <c r="H290" s="3" t="inlineStr">
         <is>
-          <t>owner_dependency (35)</t>
+          <t>key_person (35)</t>
         </is>
       </c>
       <c r="I290" s="3" t="inlineStr"/>
@@ -14627,7 +14623,7 @@
       <c r="G291" s="5" t="inlineStr"/>
       <c r="H291" s="3" t="inlineStr">
         <is>
-          <t>owner_dependency (80)</t>
+          <t>key_person (80)</t>
         </is>
       </c>
       <c r="I291" s="3" t="inlineStr"/>
@@ -14664,7 +14660,7 @@
       <c r="G292" s="5" t="inlineStr"/>
       <c r="H292" s="3" t="inlineStr">
         <is>
-          <t>owner_dependency (100)</t>
+          <t>key_person (100)</t>
         </is>
       </c>
       <c r="I292" s="3" t="inlineStr"/>
@@ -14697,7 +14693,7 @@
       <c r="G293" s="5" t="inlineStr"/>
       <c r="H293" s="3" t="inlineStr">
         <is>
-          <t>owner_dependency (70), no_succession (70)</t>
+          <t>key_person (70), no_succession (70)</t>
         </is>
       </c>
       <c r="I293" s="3" t="inlineStr">
@@ -17835,7 +17831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -17905,33 +17901,41 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>key_asset</t>
+          <t>key_channel</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Key asset</t>
+          <t>Key lead source</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>One piece of equipment or one vehicle is doing work you have no backup for. A breakdown or a long repair stops revenue you've already sold, and hire rates at short notice are set by people who know you're stuck.</t>
+          <t>Your customers arrive {q43.band}. A lead source changes without asking you first, and an algorithm shift or one referrer going quiet can halve your enquiries inside a month.</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
-      <c r="F3" s="7" t="inlineStr"/>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>You weren't sure where your customers actually come from, which usually means one source is doing more of the work than you think. A lead source can change without asking you first, and one referrer going quiet can halve your enquiries inside a month.</t>
+        </is>
+      </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>Find out today what a replacement costs at short notice, and who actually has one.</t>
+          <t>Stand up a second lead source before you need it, and give it ninety days before you judge it.</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>Put it on a service schedule and hold to it. Most failures give some warning.</t>
+          <t>Write down what you'd do if the current one halved tomorrow. That plan is worth having on paper before you need it.</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>{q43.band}</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -17941,39 +17945,43 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>key_channel</t>
+          <t>key_client</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Key channel</t>
+          <t>Key client</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Your customers arrive {q43.band}. Channels change without asking you first, and an algorithm shift or one referrer going quiet can halve your enquiries inside a month.</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr"/>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>You weren't sure where your customers actually come from, which usually means one channel is doing more of the work than you think. A channel can change without asking you first, and one referrer going quiet can halve your enquiries inside a month.</t>
-        </is>
-      </c>
+          <t>One customer carries {q41.band} of your revenue. That customer can leave, or get bought by someone who already has their own suppliers, and neither is something you get a say in.</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>One customer carries {q41.exact}% of your revenue. That customer can leave, or get bought by someone who already has their own suppliers, and neither is something you get a say in.</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr"/>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>Stand up a second channel before you need it, and give it ninety days before you judge it.</t>
+          <t>Set a ceiling, say twenty percent of revenue from any one customer, and treat crossing it as the trigger to go and win two more.</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>Write down what you'd do if the current one halved tomorrow. That plan is worth having on paper before you need it.</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr"/>
+          <t>Get them onto a term agreement with a notice period, so a decision to leave gives you time to react.</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>If the work is committed on a handshake, that is the first conversation to have, before the ceiling.</t>
+        </is>
+      </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>{q43.band}</t>
+          <t>{q41.band}, {q41.exact}</t>
         </is>
       </c>
     </row>
@@ -17985,45 +17993,33 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>key_client</t>
+          <t>key_licence</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Key client</t>
+          <t>Key licence</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>One customer carries {q41.band} of your revenue. That customer can leave, or get bought by someone who already has their own suppliers, and neither is something you get a say in.</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>One customer carries {q41.exact}% of your revenue. That customer can leave, or get bought by someone who already has their own suppliers, and neither is something you get a say in.</t>
-        </is>
-      </c>
+          <t>One licence or accreditation is the thing that lets you trade at all. Let it lapse and the business stops completely rather than slows down.</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="7" t="inlineStr"/>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Set a ceiling, say twenty percent of revenue from any one customer, and treat crossing it as the trigger to go and win two more.</t>
+          <t>Put every renewal date in a calendar with a ninety day warning on it.</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Get them onto a term agreement with a notice period, so a decision to leave gives you time to react.</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>If the work is committed on a handshake, that is the first conversation to have, before the ceiling.</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>{q41.band}, {q41.exact}</t>
-        </is>
-      </c>
+          <t>Make sure a second person can hold or renew it, so a lapse can't come down to one person's inbox.</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -18033,37 +18029,45 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>key_employee</t>
+          <t>key_person</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Key employee</t>
+          <t>Key person</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>One person knows how the work actually gets done, and very little of it is written down anywhere else. If they leave, the knowledge goes with them, and you'll be rebuilding it from scratch while still trying to deliver.</t>
+          <t>The business can't run without one person. Sold tomorrow, {q49.band}, and there's nobody who could run it if you stepped out. That caps the business at the size of one person's week.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>The business can't run without one person, and nobody has put a number on what that would cost. Until somebody else can run it, this is a job that owns you rather than an asset you own.</t>
+        </is>
+      </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Have them document the work while they're still here, and pay them properly to do it.</t>
+          <t>Write down what that person holds, then move one piece of it to somebody else this month.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Put a second person alongside them on the next three jobs, doing rather than watching.</t>
+          <t>Name who would run it, tell them, and give them a budget they can act inside. A deputy who can't decide anything is a job title.</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Record the five things that go wrong most often as one page checklists. People use checklists, they don't use manuals.</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr"/>
+          <t>Book a month off twelve months out and work backwards from it. That's the deadline that makes it real.</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>{q49.band}</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -18073,33 +18077,41 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>key_geography</t>
+          <t>key_product</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Key geography</t>
+          <t>Key product</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>The business sells into one city or region. A local downturn or a big competitor arriving hits all of your revenue at once rather than part of it.</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr"/>
+          <t>{q42.band} of your revenue comes from one product or service line. That's fine while the market wants it, and it's a single point of failure the day the market moves or a competitor undercuts it.</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>{q42.exact}% of your revenue comes from one product or service line. That's fine while the market wants it, and it's a single point of failure the day the market moves or a competitor undercuts it.</t>
+        </is>
+      </c>
       <c r="F7" s="7" t="inlineStr"/>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Take one thing you do well and sell it somewhere else, even at a small scale.</t>
+          <t>Build a second line and sell it to the customers you already have.</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Track what share of revenue comes from outside the home patch, and set a target for it.</t>
+          <t>Set a target for what share of revenue it should carry in twelve months, and check it quarterly.</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>{q42.band}, {q42.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -18109,113 +18121,125 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>key_licence</t>
+          <t>key_supplier</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Key licence</t>
+          <t>Key supplier</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>One licence or accreditation is the thing that lets you trade at all. Let it lapse and the business stops completely rather than slows down.</t>
+          <t>There's one supplier, or one piece of gear, with no ready replacement. Their price rise is your price rise, and a breakdown or a bad year at their end stops revenue you have already sold.</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr"/>
       <c r="F8" s="7" t="inlineStr"/>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Put every renewal date in a calendar with a ninety day warning on it.</t>
+          <t>Qualify a second supplier and give them ten percent of your volume. A backup you've never bought from isn't a backup.</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Make sure a second person can hold or renew it, so a lapse can't come down to one person's inbox.</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr"/>
+          <t>Find out today what a replacement costs at short notice, and who actually has one.</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Put anything you own on a service schedule and hold to it. Most failures give some warning.</t>
+        </is>
+      </c>
       <c r="J8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Concentration</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>key_product</t>
+          <t>model_misfit</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Key product</t>
+          <t>Model misfit</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>{q42.band} of your revenue comes from one product or service line. That's fine while the market wants it, and it's a single point of failure the day the market moves or a competitor undercuts it.</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>{q42.exact}% of your revenue comes from one product or service line. That's fine while the market wants it, and it's a single point of failure the day the market moves or a competitor undercuts it.</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr"/>
+          <t>The way you spend your week is {q52.band}. It decides how long you'll keep doing this, and a business rarely outlives the owner's appetite for running it.</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>You weren't sure whether the way you spend your week matches what you wanted out of this. That question decides how long you'll keep doing it, and a business rarely outlives the owner's appetite for running it.</t>
+        </is>
+      </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Build a second line and sell it to the customers you already have.</t>
+          <t>Write down what you actually wanted out of this, then hold your week up against it.</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Set a target for what share of revenue it should carry in twelve months, and check it quarterly.</t>
+          <t>The gap between those two is the brief for the next twelve months.</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr"/>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>{q42.band}, {q42.exact}</t>
+          <t>{q52.band}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Concentration</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>key_supplier</t>
+          <t>no_succession</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Key supplier</t>
+          <t>Succession gap</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>You've got one supplier with no ready replacement. Their price rise is your price rise, and their bad year is your bad year.</t>
+          <t>There's {q50.band} for what happens if you stop or sell. Every business has an exit, planned or not. The unplanned version is the one where somebody else sets the price.</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>You weren't sure what happens to the business if you stop or sell. Every business has an exit, planned or not. The unplanned version is the one where somebody else sets the price.</t>
+        </is>
+      </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Qualify a second supplier and give them ten percent of your volume. A backup you've never bought from isn't a backup.</t>
+          <t>Write the one page version. Who runs it, and what happens to the customers.</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Get lead times and pricing from your current one in writing, so a change is a conversation rather than a surprise.</t>
+          <t>It doesn't need to be right, it needs to exist.</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>{q50.band}</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -18225,180 +18249,44 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>model_misfit</t>
+          <t>personal_guarantee</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Model misfit</t>
+          <t>Personal guarantee</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>The way you spend your week is {q52.band}. It decides how long you'll keep doing this, and a business rarely outlives the owner's appetite for running it.</t>
+          <t>You've personally guaranteed {q51.band} of the business's obligations. The wall between business risk and personal risk isn't up, so a bad year in the business reaches your house.</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr"/>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>You weren't sure whether the way you spend your week matches what you wanted out of this. That question decides how long you'll keep doing it, and a business rarely outlives the owner's appetite for running it.</t>
+          <t>You weren't sure what you've personally guaranteed, and that's worth finding out this week. Where the wall between business risk and personal risk isn't up, a bad year in the business reaches your house.</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Write down what you actually wanted out of this, then hold your week up against it.</t>
+          <t>List every guarantee you've signed and put a date against each one to renegotiate or release it.</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>The gap between those two is the brief for the next twelve months.</t>
+          <t>Most get renewed on autopilot, because nobody asks.</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr"/>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>{q52.band}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>no_succession</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Succession gap</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>There's {q50.band} for what happens if you stop or sell. Every business has an exit, planned or not. The unplanned version is the one where somebody else sets the price.</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr"/>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>You weren't sure what happens to the business if you stop or sell. Every business has an exit, planned or not. The unplanned version is the one where somebody else sets the price.</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>Write the one page version. Who runs it, and what happens to the customers.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>It doesn't need to be right, it needs to exist.</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>{q50.band}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>owner_dependency</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Owner dependency</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>The business runs on you. Sold tomorrow a buyer would need you to stay {q49.band}, and there's nobody who could run it if you stepped out. That caps the business at the size of your week and it's what makes it hard to sell.</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr"/>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>The business runs on you, and you haven't put a number on how long a buyer would need you to stay. Until somebody else can run it, this is a job that owns you rather than an asset you own.</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>Name the person who'd run it, tell them, and hand over one area at a time with the decisions attached.</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>Give them a budget they can act inside. A deputy who can't decide anything is a job title.</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>Book a month off twelve months out and work backwards from it. That's the deadline that makes it real.</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>{q49.band}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>personal_guarantee</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Personal guarantee</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>You've personally guaranteed {q51.band} of the business's obligations. The wall between business risk and personal risk isn't up, so a bad year in the business reaches your house.</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr"/>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>You weren't sure what you've personally guaranteed, and that's worth finding out this week. Where the wall between business risk and personal risk isn't up, a bad year in the business reaches your house.</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>List every guarantee you've signed and put a date against each one to renegotiate or release it.</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>Most get renewed on autopilot, because nobody asks.</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
           <t>{q51.band}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H14"/>
+  <autoFilter ref="A2:H11"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>

--- a/diagnostic/Business-Diagnostic-Spec.xlsx
+++ b/diagnostic/Business-Diagnostic-Spec.xlsx
@@ -24,8 +24,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Questions'!$A$2:$J$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Answer options'!$A$2:$I$305</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Constraints and order'!$A$2:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Report, constraint'!$A$2:$E$107</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Report, risk flags'!$A$2:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Report, constraint'!$A$2:$E$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Report, risk flags'!$A$2:$H$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Report, risk section'!$A$2:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Report, don''t do yet'!$A$2:$C$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Report, open and close'!$A$2:$E$14</definedName>
@@ -12967,7 +12967,7 @@
       <c r="G243" s="5" t="inlineStr"/>
       <c r="H243" s="3" t="inlineStr">
         <is>
-          <t>key_client (65)</t>
+          <t>key_client (45)</t>
         </is>
       </c>
       <c r="I243" s="3" t="inlineStr"/>
@@ -13527,7 +13527,7 @@
       <c r="G259" s="5" t="inlineStr"/>
       <c r="H259" s="3" t="inlineStr">
         <is>
-          <t>key_supplier (75)</t>
+          <t>key_asset (75)</t>
         </is>
       </c>
       <c r="I259" s="3" t="inlineStr"/>
@@ -13788,7 +13788,7 @@
       <c r="H267" s="3" t="inlineStr"/>
       <c r="I267" s="3" t="inlineStr">
         <is>
-          <t>Promotes key_supplier to the top severity</t>
+          <t>Promotes key_asset to the top severity</t>
         </is>
       </c>
     </row>
@@ -15465,7 +15465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15717,7 +15717,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>The job is to shorten the gap between doing the work and getting paid for it. Nothing else moves until that does.</t>
+          <t>You need to close the gap between doing the work and getting paid for it. Every other fix in the business is waiting on this one.</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr"/>
@@ -16088,7 +16088,7 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>One role, hired with the authority to actually run what you hand over.</t>
+          <t>You need one role hired with the authority to actually run what you hand over, rather than another pair of hands underneath you.</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr"/>
@@ -16417,7 +16417,7 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>More output from what you already have, before you buy any more of anything.</t>
+          <t>You need more output from what you already have, or more capacity, before you go and win any more work.</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr"/>
@@ -16750,7 +16750,7 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Find out why they leave or why they shrink, then fix the thing they tell you about.</t>
+          <t>You need to find out why customers leave or shrink, and fix that, before you spend another dollar finding new ones.</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr"/>
@@ -16917,7 +16917,7 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Opening</t>
+          <t>Opening sentence 1</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
@@ -16936,24 +16936,16 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 1</t>
+          <t>Opening sentence 2</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>your close rate sits {q26.band}</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>your close rate sits at {q26.exact}%</t>
-        </is>
-      </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t>{q26.band}, {q26.exact}</t>
-        </is>
-      </c>
+          <t>That isn't a sales technique problem, it's what's on the table. Either the value in the offer doesn't justify the price you're asking, or there's something in the way of somebody saying yes.</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr"/>
+      <c r="E68" s="8" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -16963,18 +16955,22 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 2</t>
+          <t>Evidence clause 1</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>the most common reason you lose is {q27.band}</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr"/>
+          <t>your close rate sits {q26.band}</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>your close rate sits at {q26.exact}%</t>
+        </is>
+      </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>{q27.band}</t>
+          <t>{q26.band}, {q26.exact}</t>
         </is>
       </c>
     </row>
@@ -16986,18 +16982,18 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 3</t>
+          <t>Evidence clause 2</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>prospects come back on your quote asking what's included {q28.band}</t>
+          <t>the most common reason you lose is {q27.band}</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr"/>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>{q28.band}</t>
+          <t>{q27.band}</t>
         </is>
       </c>
     </row>
@@ -17009,18 +17005,18 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 4</t>
+          <t>Evidence clause 3</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>they find out what you charge {q30.band}</t>
+          <t>prospects come back on your quote asking what's included {q28.band}</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr"/>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>{q30.band}</t>
+          <t>{q28.band}</t>
         </is>
       </c>
     </row>
@@ -17032,16 +17028,20 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Evidence clause 4</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>This isn't a sales technique problem. When the thing on the table is clearly priced and it fits what the buyer came in for, an average salesperson closes it. Right now yours needs you in the room to make sense of it.</t>
+          <t>they find out what you charge {q30.band}</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr"/>
-      <c r="E72" s="8" t="inlineStr"/>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>{q30.band}</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
@@ -17051,12 +17051,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Fix, lead line</t>
+          <t>Closing</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Make the thing you sell understandable without you standing next to it.</t>
+          <t>You don't fix this by dropping the price. You fix it by putting things into the offer that cost you very little and are worth real money to the buyer, and by removing whatever a prospect has to get over before they can say yes.</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr"/>
@@ -17070,20 +17070,16 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Fix action 1</t>
+          <t>Fix, lead line</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>Write the offer on one page. What it is, what it costs, what the buyer gets, who it isn't for.</t>
+          <t>You need more value in the offer than the price is asking for, and the hurdles taken out of the way of somebody saying yes.</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr"/>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>always prints</t>
-        </is>
-      </c>
+      <c r="E74" s="8" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -17093,18 +17089,18 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Fix action 2</t>
+          <t>Fix action 1</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>Price it publicly, or at least in a range. Every quote you build from scratch is a delay you're funding.</t>
+          <t>List everything you already do for a customer that you never charge for and never mention. That is value sitting in the offer that nobody can see.</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr"/>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>q30 is c/d</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
@@ -17116,12 +17112,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Fix action 3</t>
+          <t>Fix action 2</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>Sort your last twenty losses by reason and count them. The pattern is usually one thing.</t>
+          <t>Add two things that cost you close to nothing and are worth real money to the buyer. A guarantee, or something they would otherwise have to go and source themselves.</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr"/>
@@ -17139,12 +17135,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>Fix action 4</t>
+          <t>Fix action 3</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>Rewrite the quote so it answers what's included and why it costs that, before they have to ask.</t>
+          <t>Write down every question a prospect asks after they get the quote, then answer all of them inside the quote itself.</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr"/>
@@ -17162,18 +17158,18 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Fix action 5</t>
+          <t>Fix action 4</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>Cut the options. Fewer, clearer choices close more often than a menu does.</t>
+          <t>Put a price or a range where they can see it. Making somebody wait for a number is a hurdle before they have even decided.</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr"/>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>always prints</t>
+          <t>q30 is c/d</t>
         </is>
       </c>
     </row>
@@ -17185,12 +17181,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Fix action 6</t>
+          <t>Fix action 5</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Test the new version on the next ten enquiries before you change anything else.</t>
+          <t>Sort your last twenty losses by reason and count them. If price keeps coming up, the value isn't visible enough, it isn't too high.</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr"/>
@@ -17203,21 +17199,25 @@
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>offer</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Fix action 6</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>You are {c} constrained</t>
+          <t>Test the new offer on the next ten enquiries before you change anything else.</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr"/>
-      <c r="E80" s="8" t="inlineStr"/>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
@@ -17227,12 +17227,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Title, nothing failing</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>The tightest thing is {c}</t>
+          <t>You are {c} constrained</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr"/>
@@ -17246,12 +17246,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Opening</t>
+          <t>Title, nothing failing</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>You've got capacity sitting idle and not enough people asking.</t>
+          <t>The tightest thing is {c}</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr"/>
@@ -17265,24 +17265,16 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 1</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>enquiries run {q31.band}</t>
-        </is>
-      </c>
-      <c r="D83" s="7" t="inlineStr">
-        <is>
-          <t>enquiries run at about {q31.exact} a month</t>
-        </is>
-      </c>
-      <c r="E83" s="8" t="inlineStr">
-        <is>
-          <t>{q31.band}, {q31.exact}</t>
-        </is>
-      </c>
+          <t>You've got capacity sitting idle and not enough people asking.</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr"/>
+      <c r="E83" s="8" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
@@ -17292,18 +17284,22 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 2</t>
+          <t>Evidence clause 1</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>volume has {q33.band} over the last year</t>
-        </is>
-      </c>
-      <c r="D84" s="7" t="inlineStr"/>
+          <t>enquiries run {q31.band}</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>enquiries run at about {q31.exact} a month</t>
+        </is>
+      </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>{q33.band}</t>
+          <t>{q31.band}, {q31.exact}</t>
         </is>
       </c>
     </row>
@@ -17315,18 +17311,18 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 3</t>
+          <t>Evidence clause 2</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>{q35.band}</t>
+          <t>volume has {q33.band} over the last year</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr"/>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>{q35.band}</t>
+          <t>{q33.band}</t>
         </is>
       </c>
     </row>
@@ -17338,16 +17334,20 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Evidence clause 3</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>You could take on more work tomorrow, which is what separates this from a delivery problem. Nothing downstream is broken. The business just isn't being fed, and it won't start feeding itself.</t>
+          <t>{q35.band}</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr"/>
-      <c r="E86" s="8" t="inlineStr"/>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>{q35.band}</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
@@ -17357,12 +17357,12 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Fix, lead line</t>
+          <t>Closing</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Turn the tap on deliberately. One channel run properly, before you touch a second.</t>
+          <t>You could take on more work tomorrow, which is what separates this from a delivery problem. Nothing downstream is broken. The business just isn't being fed, and it won't start feeding itself.</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr"/>
@@ -17376,20 +17376,16 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Fix action 1</t>
+          <t>Fix, lead line</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>Nothing is running right now, so start with the one thing you can do every week without fail.</t>
+          <t>You need one lead source running properly and consistently before you go anywhere near a second.</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr"/>
-      <c r="E88" s="8" t="inlineStr">
-        <is>
-          <t>q35 is b/c</t>
-        </is>
-      </c>
+      <c r="E88" s="8" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
@@ -17399,18 +17395,18 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Fix action 2</t>
+          <t>Fix action 1</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Pick the channel that already brings your best customers and put real weight behind it.</t>
+          <t>Nothing is running right now, so start with the one thing you can do every week without fail.</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr"/>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>always prints</t>
+          <t>q35 is b/c</t>
         </is>
       </c>
     </row>
@@ -17422,12 +17418,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Fix action 3</t>
+          <t>Fix action 2</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>Go and ask for work. Outbound to the twenty businesses you'd most like to work with beats waiting on referrals.</t>
+          <t>Pick the channel that already brings your best customers and put real weight behind it.</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr"/>
@@ -17445,18 +17441,18 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Fix action 4</t>
+          <t>Fix action 3</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>Everything arrives through one channel. Stand up a second before that one changes.</t>
+          <t>Go and ask for work. Outbound to the twenty businesses you'd most like to work with beats waiting on referrals.</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr"/>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>q43 is c</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
@@ -17468,18 +17464,18 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Fix action 5</t>
+          <t>Fix action 4</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Ask every happy customer for one introduction.</t>
+          <t>Everything arrives through one channel. Stand up a second before that one changes.</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr"/>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>always prints</t>
+          <t>q43 is c</t>
         </is>
       </c>
     </row>
@@ -17491,12 +17487,12 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>Fix action 6</t>
+          <t>Fix action 5</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>Give a channel ninety days before you judge it. Anything shorter is guesswork.</t>
+          <t>Ask every happy customer for one introduction.</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr"/>
@@ -17509,21 +17505,25 @@
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>margin</t>
+          <t>demand</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Fix action 6</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>You are {c} constrained</t>
+          <t>Give a channel ninety days before you judge it. Anything shorter is guesswork.</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr"/>
-      <c r="E94" s="8" t="inlineStr"/>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
@@ -17533,12 +17533,12 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>Title, nothing failing</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>The tightest thing is {c}</t>
+          <t>You are {c} constrained</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr"/>
@@ -17552,12 +17552,12 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Opening</t>
+          <t>Title, nothing failing</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>You're full and busy, and there's nothing left at the end of it.</t>
+          <t>The tightest thing is {c}</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr"/>
@@ -17571,24 +17571,16 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 1</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>what's left after direct costs sits {q36.band}</t>
-        </is>
-      </c>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>what's left after direct costs sits at {q36.exact}%</t>
-        </is>
-      </c>
-      <c r="E97" s="8" t="inlineStr">
-        <is>
-          <t>{q36.band}, {q36.exact}</t>
-        </is>
-      </c>
+          <t>You're full and busy, and there's nothing left at the end of it.</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr"/>
+      <c r="E97" s="8" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
@@ -17598,22 +17590,22 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 2</t>
+          <t>Evidence clause 1</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>after everything it's {q37.band}</t>
+          <t>what's left after direct costs sits {q36.band}</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>after everything it's {q37.exact}%</t>
+          <t>what's left after direct costs sits at {q36.exact}%</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>{q37.band}, {q37.exact}</t>
+          <t>{q36.band}, {q36.exact}</t>
         </is>
       </c>
     </row>
@@ -17625,18 +17617,22 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 3</t>
+          <t>Evidence clause 2</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>{q38.band}</t>
-        </is>
-      </c>
-      <c r="D99" s="7" t="inlineStr"/>
+          <t>after everything it's {q37.band}</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>after everything it's {q37.exact}%</t>
+        </is>
+      </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>{q38.band}</t>
+          <t>{q37.band}, {q37.exact}</t>
         </is>
       </c>
     </row>
@@ -17648,18 +17644,18 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 4</t>
+          <t>Evidence clause 3</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>jobs run over what you quoted {q39.band}</t>
+          <t>{q38.band}</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr"/>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>{q39.band}</t>
+          <t>{q38.band}</t>
         </is>
       </c>
     </row>
@@ -17671,16 +17667,20 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Evidence clause 4</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>Volume won't rescue this. At the margin you're running, more work gets you more of the same result and it arrives faster.</t>
+          <t>jobs run over what you quoted {q39.band}</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr"/>
-      <c r="E101" s="8" t="inlineStr"/>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>{q39.band}</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
@@ -17690,12 +17690,12 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Fix, lead line</t>
+          <t>Closing</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>Price first, then cost. Price moves faster and costs nothing to change.</t>
+          <t>Volume won't rescue this. At the margin you're running, more work gets you more of the same result and it arrives faster.</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr"/>
@@ -17709,20 +17709,16 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Fix action 1</t>
+          <t>Fix, lead line</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>Raise prices on new work now. Ten percent across the board, and watch what actually happens.</t>
+          <t>You need to know what each job actually earns you before you change anything. A price rise can cost you customers as easily as it can fix the margin.</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr"/>
-      <c r="E103" s="8" t="inlineStr">
-        <is>
-          <t>q38 is c/d/e</t>
-        </is>
-      </c>
+      <c r="E103" s="8" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
@@ -17732,18 +17728,18 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>Fix action 2</t>
+          <t>Fix action 1</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>Work out what each job really costs, your own time included, then rank your last twenty by what was left.</t>
+          <t>Raise prices on new work now. Ten percent across the board, and watch what actually happens.</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr"/>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>always prints</t>
+          <t>q38 is c/d/e</t>
         </is>
       </c>
     </row>
@@ -17755,18 +17751,18 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Fix action 3</t>
+          <t>Fix action 2</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>Quote a contingency into the jobs that historically run over. You already know which ones they are.</t>
+          <t>Work out what each job really costs, your own time included, then rank your last twenty by what was left.</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr"/>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>q39 is c/d</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
@@ -17778,18 +17774,18 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>Fix action 4</t>
+          <t>Fix action 3</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>Find your worst three customers by margin, then reprice them or let them go.</t>
+          <t>Quote a contingency into the jobs that historically run over. You already know which ones they are.</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr"/>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>always prints</t>
+          <t>q39 is c/d</t>
         </is>
       </c>
     </row>
@@ -17801,12 +17797,12 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Fix action 5</t>
+          <t>Fix action 4</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>Stop discounting to win. A discount is the fastest way to buy work you'll resent delivering.</t>
+          <t>Find your worst three customers by margin, then reprice them or let them go.</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr"/>
@@ -17816,8 +17812,31 @@
         </is>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>margin</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>Fix action 5</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>Stop discounting to win. A discount is the fastest way to buy work you'll resent delivering.</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr"/>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:E107"/>
+  <autoFilter ref="A2:E108"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -17831,7 +17850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -17901,41 +17920,33 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>key_channel</t>
+          <t>key_asset</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Key lead source</t>
+          <t>Key asset</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Your customers arrive {q43.band}. A lead source changes without asking you first, and an algorithm shift or one referrer going quiet can halve your enquiries inside a month.</t>
+          <t>One piece of equipment or one vehicle is doing work you have no backup for. A breakdown or a long repair stops revenue you have already sold, and hire rates at short notice are set by people who know you're stuck.</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>You weren't sure where your customers actually come from, which usually means one source is doing more of the work than you think. A lead source can change without asking you first, and one referrer going quiet can halve your enquiries inside a month.</t>
-        </is>
-      </c>
+      <c r="F3" s="7" t="inlineStr"/>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>Stand up a second lead source before you need it, and give it ninety days before you judge it.</t>
+          <t>Find out today what a replacement costs at short notice, and who actually has one.</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>Write down what you'd do if the current one halved tomorrow. That plan is worth having on paper before you need it.</t>
+          <t>Put it on a service schedule and hold to it. Most failures give some warning.</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>{q43.band}</t>
-        </is>
-      </c>
+      <c r="J3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -17945,43 +17956,39 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>key_client</t>
+          <t>key_channel</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Key client</t>
+          <t>Key lead source</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>One customer carries {q41.band} of your revenue. That customer can leave, or get bought by someone who already has their own suppliers, and neither is something you get a say in.</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>One customer carries {q41.exact}% of your revenue. That customer can leave, or get bought by someone who already has their own suppliers, and neither is something you get a say in.</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr"/>
+          <t>Your customers arrive {q43.band}. A lead source changes without asking you first, and an algorithm shift or one referrer going quiet can halve your enquiries inside a month.</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>You weren't sure where your customers actually come from, which usually means one source is doing more of the work than you think. A lead source can change without asking you first, and one referrer going quiet can halve your enquiries inside a month.</t>
+        </is>
+      </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>Set a ceiling, say twenty percent of revenue from any one customer, and treat crossing it as the trigger to go and win two more.</t>
+          <t>Stand up a second lead source before you need it, and give it ninety days before you judge it.</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>Get them onto a term agreement with a notice period, so a decision to leave gives you time to react.</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>If the work is committed on a handshake, that is the first conversation to have, before the ceiling.</t>
-        </is>
-      </c>
+          <t>Write down what you'd do if the current one halved tomorrow. That plan is worth having on paper before you need it.</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>{q41.band}, {q41.exact}</t>
+          <t>{q43.band}</t>
         </is>
       </c>
     </row>
@@ -17993,33 +18000,45 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>key_licence</t>
+          <t>key_client</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Key licence</t>
+          <t>Key client</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>One licence or accreditation is the thing that lets you trade at all. Let it lapse and the business stops completely rather than slows down.</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr"/>
+          <t>One customer carries {q41.band} of your revenue. That customer can leave, or get bought by someone who already has their own suppliers, and neither is something you get a say in.</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>One customer carries {q41.exact}% of your revenue. That customer can leave, or get bought by someone who already has their own suppliers, and neither is something you get a say in.</t>
+        </is>
+      </c>
       <c r="F5" s="7" t="inlineStr"/>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Put every renewal date in a calendar with a ninety day warning on it.</t>
+          <t>Set a ceiling, say twenty percent of revenue from any one customer, and treat crossing it as the trigger to go and win two more.</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Make sure a second person can hold or renew it, so a lapse can't come down to one person's inbox.</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
+          <t>Get them onto a term agreement with a notice period, so a decision to leave gives you time to react.</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>If the work is committed on a handshake, that is the first conversation to have, before the ceiling.</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>{q41.band}, {q41.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -18029,45 +18048,33 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>key_person</t>
+          <t>key_licence</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Key person</t>
+          <t>Key licence</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>The business can't run without one person. Sold tomorrow, {q49.band}, and there's nobody who could run it if you stepped out. That caps the business at the size of one person's week.</t>
+          <t>One licence or accreditation is the thing that lets you trade at all. Let it lapse and the business stops completely rather than slows down.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>The business can't run without one person, and nobody has put a number on what that would cost. Until somebody else can run it, this is a job that owns you rather than an asset you own.</t>
-        </is>
-      </c>
+      <c r="F6" s="7" t="inlineStr"/>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Write down what that person holds, then move one piece of it to somebody else this month.</t>
+          <t>Put every renewal date in a calendar with a ninety day warning on it.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Name who would run it, tell them, and give them a budget they can act inside. A deputy who can't decide anything is a job title.</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>Book a month off twelve months out and work backwards from it. That's the deadline that makes it real.</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>{q49.band}</t>
-        </is>
-      </c>
+          <t>Make sure a second person can hold or renew it, so a lapse can't come down to one person's inbox.</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -18077,39 +18084,43 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>key_product</t>
+          <t>key_person</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Key product</t>
+          <t>Key person</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>{q42.band} of your revenue comes from one product or service line. That's fine while the market wants it, and it's a single point of failure the day the market moves or a competitor undercuts it.</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>{q42.exact}% of your revenue comes from one product or service line. That's fine while the market wants it, and it's a single point of failure the day the market moves or a competitor undercuts it.</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr"/>
+          <t>The business can't run without one person. Sold tomorrow, {q49.band}, and there's nobody who could run it if you stepped out. That caps the business at the size of one person's week.</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>The business can't run without one person, and nobody has put a number on what that would cost. Until somebody else can run it, this is a job that owns you rather than an asset you own.</t>
+        </is>
+      </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Build a second line and sell it to the customers you already have.</t>
+          <t>Write down what that person holds, then move one piece of it to somebody else this month.</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Set a target for what share of revenue it should carry in twelve months, and check it quarterly.</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr"/>
+          <t>Name who would run it, tell them, and give them a budget they can act inside. A deputy who can't decide anything is a job title.</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Book a month off twelve months out and work backwards from it. That's the deadline that makes it real.</t>
+        </is>
+      </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>{q42.band}, {q42.exact}</t>
+          <t>{q49.band}</t>
         </is>
       </c>
     </row>
@@ -18121,81 +18132,77 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>key_supplier</t>
+          <t>key_product</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Key supplier</t>
+          <t>Key product</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>There's one supplier, or one piece of gear, with no ready replacement. Their price rise is your price rise, and a breakdown or a bad year at their end stops revenue you have already sold.</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr"/>
+          <t>{q42.band} of your revenue comes from one product or service line. That's fine while the market wants it, and it's a single point of failure the day the market moves or a competitor undercuts it.</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>{q42.exact}% of your revenue comes from one product or service line. That's fine while the market wants it, and it's a single point of failure the day the market moves or a competitor undercuts it.</t>
+        </is>
+      </c>
       <c r="F8" s="7" t="inlineStr"/>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Qualify a second supplier and give them ten percent of your volume. A backup you've never bought from isn't a backup.</t>
+          <t>Build a second line and sell it to the customers you already have.</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Find out today what a replacement costs at short notice, and who actually has one.</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>Put anything you own on a service schedule and hold to it. Most failures give some warning.</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr"/>
+          <t>Set a target for what share of revenue it should carry in twelve months, and check it quarterly.</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>{q42.band}, {q42.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Concentration</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>model_misfit</t>
+          <t>key_supplier</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Model misfit</t>
+          <t>Key supplier</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>The way you spend your week is {q52.band}. It decides how long you'll keep doing this, and a business rarely outlives the owner's appetite for running it.</t>
+          <t>There's one supplier with no ready replacement. Their price rise is your price rise, and their bad year is your bad year.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>You weren't sure whether the way you spend your week matches what you wanted out of this. That question decides how long you'll keep doing it, and a business rarely outlives the owner's appetite for running it.</t>
-        </is>
-      </c>
+      <c r="F9" s="7" t="inlineStr"/>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Write down what you actually wanted out of this, then hold your week up against it.</t>
+          <t>Qualify a second supplier and give them ten percent of your volume. A backup you've never bought from isn't a backup.</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>The gap between those two is the brief for the next twelve months.</t>
+          <t>Get lead times and pricing from your current one in writing, so a change is a conversation rather than a surprise.</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>{q52.band}</t>
-        </is>
-      </c>
+      <c r="J9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -18205,39 +18212,39 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>no_succession</t>
+          <t>model_misfit</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Succession gap</t>
+          <t>Model misfit</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>There's {q50.band} for what happens if you stop or sell. Every business has an exit, planned or not. The unplanned version is the one where somebody else sets the price.</t>
+          <t>The way you spend your week is {q52.band}. It decides how long you'll keep doing this, and a business rarely outlives the owner's appetite for running it.</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr"/>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>You weren't sure what happens to the business if you stop or sell. Every business has an exit, planned or not. The unplanned version is the one where somebody else sets the price.</t>
+          <t>You weren't sure whether the way you spend your week matches what you wanted out of this. That question decides how long you'll keep doing it, and a business rarely outlives the owner's appetite for running it.</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Write the one page version. Who runs it, and what happens to the customers.</t>
+          <t>Write down what you actually wanted out of this, then hold your week up against it.</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>It doesn't need to be right, it needs to exist.</t>
+          <t>The gap between those two is the brief for the next twelve months.</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr"/>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>{q50.band}</t>
+          <t>{q52.band}</t>
         </is>
       </c>
     </row>
@@ -18249,44 +18256,88 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>personal_guarantee</t>
+          <t>no_succession</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Personal guarantee</t>
+          <t>Succession gap</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>You've personally guaranteed {q51.band} of the business's obligations. The wall between business risk and personal risk isn't up, so a bad year in the business reaches your house.</t>
+          <t>There's {q50.band} for what happens if you stop or sell. Every business has an exit, planned or not. The unplanned version is the one where somebody else sets the price.</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr"/>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>You weren't sure what you've personally guaranteed, and that's worth finding out this week. Where the wall between business risk and personal risk isn't up, a bad year in the business reaches your house.</t>
+          <t>You weren't sure what happens to the business if you stop or sell. Every business has an exit, planned or not. The unplanned version is the one where somebody else sets the price.</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>List every guarantee you've signed and put a date against each one to renegotiate or release it.</t>
+          <t>Write the one page version. Who runs it, and what happens to the customers.</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Most get renewed on autopilot, because nobody asks.</t>
+          <t>It doesn't need to be right, it needs to exist.</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr"/>
       <c r="J11" s="5" t="inlineStr">
         <is>
+          <t>{q50.band}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>personal_guarantee</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Personal guarantee</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>You've personally guaranteed {q51.band} of the business's obligations. The wall between business risk and personal risk isn't up, so a bad year in the business reaches your house.</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>You weren't sure what you've personally guaranteed, and that's worth finding out this week. Where the wall between business risk and personal risk isn't up, a bad year in the business reaches your house.</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>List every guarantee you've signed and put a date against each one to renegotiate or release it.</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Most get renewed on autopilot, because nobody asks.</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
           <t>{q51.band}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H11"/>
+  <autoFilter ref="A2:H12"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -18334,7 +18385,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>These are the things that would hurt most if they went wrong. They sit behind the constraint above in the order, not in front of it.</t>
+          <t>These are the things that would hurt most if something went wrong. They aren't capping the business the way the constraint above is, but they're major risks.</t>
         </is>
       </c>
     </row>

--- a/diagnostic/Business-Diagnostic-Spec.xlsx
+++ b/diagnostic/Business-Diagnostic-Spec.xlsx
@@ -15759,7 +15759,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Take a deposit on every job. Fifty percent thirty days out and the balance the week before, so the money is in before your costs go out.</t>
+          <t>Move to a deposit on every job. Fifty percent thirty days out and the balance the week before, so the money is in before your costs go out.</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr"/>
@@ -15805,7 +15805,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Invoice within twenty four hours of the job finishing, rather than at the end of the month.</t>
+          <t>Invoice within twenty four hours of the job finishing. Whatever the gap is between finishing and invoicing, that gap is yours to close.</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr"/>
@@ -15874,13 +15874,13 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Get a facility in place while you're still profitable. Banks lend to businesses that don't look like they need it.</t>
+          <t>Get a facility in place while the business is still profitable on paper. Banks lend to businesses that don't look like they need it.</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr"/>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>always prints</t>
+          <t>q10 is a</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Give it ninety days before you judge it, and stop being the escalation point for what you handed over.</t>
+          <t>Give it ninety days before you judge it, and don't let yourself become the escalation point for what you handed over.</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr"/>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Pull the work that doesn't need your best people off your best people.</t>
+          <t>Look at what your best people actually spent last week on. Anything that didn't need them is capacity you already have.</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr"/>
@@ -16528,7 +16528,7 @@
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Stop selling the jobs that eat the most capacity for the least return, at least until the queue clears.</t>
+          <t>Work out which jobs eat the most capacity for the least return, and stop taking those until the queue clears.</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr"/>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Add capacity last. Hiring into a broken process gets you a bigger broken process.</t>
+          <t>Add capacity last, once the steps above have been worked. Hiring multiplies whatever the process already does.</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr"/>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Look hard at the first thirty days after somebody buys. That's where most of the leaving gets decided.</t>
+          <t>Look hard at what happens in the first thirty days after somebody buys. That's the part of the experience you control most tightly.</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr"/>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Give them a reason to come back that you initiate. Waiting to be remembered isn't a retention plan.</t>
+          <t>Build one reason to come back that you initiate. A check in, or the next step offered before they go looking.</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr"/>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Measure it monthly. You can't run a business on a number you find out about once a year.</t>
+          <t>Measure retention monthly, so a drop shows up while you can still do something about it.</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr"/>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>List everything you already do for a customer that you never charge for and never mention. That is value sitting in the offer that nobody can see.</t>
+          <t>List everything you already do for a customer that isn't written into the offer. That's value nobody can see.</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr"/>
@@ -17186,7 +17186,7 @@
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Sort your last twenty losses by reason and count them. If price keeps coming up, the value isn't visible enough, it isn't too high.</t>
+          <t>Sort your last twenty losses by reason and count them. If price keeps coming up, look at the value in the offer before you look at the number.</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr"/>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Nothing is running right now, so start with the one thing you can do every week without fail.</t>
+          <t>Whatever you're doing to generate enquiries isn't running consistently. Start with the one thing you can do every week without fail.</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr"/>
@@ -17423,7 +17423,7 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>Pick the channel that already brings your best customers and put real weight behind it.</t>
+          <t>Pick the lead source that already brings your best customers and put real weight behind it.</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr"/>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Everything arrives through one channel. Stand up a second before that one changes.</t>
+          <t>Everything arrives through one lead source. Stand up a second before that one changes.</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr"/>
@@ -17515,7 +17515,7 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Give a channel ninety days before you judge it. Anything shorter is guesswork.</t>
+          <t>Give a lead source ninety days before you judge it. Anything shorter is guesswork.</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr"/>
@@ -17825,7 +17825,7 @@
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>Stop discounting to win. A discount is the fastest way to buy work you'll resent delivering.</t>
+          <t>Don't discount to win. A discount is the fastest way to buy work you'll resent delivering.</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr"/>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>Put it on a service schedule and hold to it. Most failures give some warning.</t>
+          <t>Put it on a service schedule and hold to it.</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr"/>
@@ -18198,7 +18198,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Get lead times and pricing from your current one in writing, so a change is a conversation rather than a surprise.</t>
+          <t>Get their lead times and pricing in writing, so a change becomes a conversation rather than a surprise.</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr"/>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Most get renewed on autopilot, because nobody asks.</t>
+          <t>They're easy to leave in place, because a renewal rarely asks you anything.</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr"/>

--- a/diagnostic/Business-Diagnostic-Spec.xlsx
+++ b/diagnostic/Business-Diagnostic-Spec.xlsx
@@ -24,10 +24,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Questions'!$A$2:$J$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Answer options'!$A$2:$I$305</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Constraints and order'!$A$2:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Report, constraint'!$A$2:$E$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Report, constraint'!$A$2:$E$106</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Report, risk flags'!$A$2:$H$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Report, risk section'!$A$2:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Report, don''t do yet'!$A$2:$C$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Report, don''t do yet'!$A$2:$C$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Report, open and close'!$A$2:$E$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Thresholds'!$A$2:$C$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Logic'!$A$1:$B$14</definedName>
@@ -15465,7 +15465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15935,7 +15935,7 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Talent here means a missing layer, not missing hands.</t>
+          <t>Being talent constrained means you're missing a layer in the business, not missing extra hands.</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -16088,7 +16088,7 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>You need one role hired with the authority to actually run what you hand over, rather than another pair of hands underneath you.</t>
+          <t>Hire one role that owns a layer of the business, with the authority to run it. Not another pair of hands underneath you.</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr"/>
@@ -16107,13 +16107,13 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Every layer sits with you. Hire the one that would free the most of your week first, not the one that's easiest to fill.</t>
+          <t>Write down every task you did last week.</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr"/>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>q11 is n</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>List every task you touched last week. Against each one, write the name of the person who'd do it if you were away for a month. Any task with no name against it is the hire.</t>
+          <t>Against each one, write the role that should own it. A role, not a person already in the business.</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr"/>
@@ -16153,7 +16153,7 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Hire the layer rather than the hands. Another delivery person gives you more capacity. A person who runs delivery gives you your week back.</t>
+          <t>Whichever role has the most tasks against it, or the most hours, hire that role first.</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr"/>
@@ -16176,13 +16176,13 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>You've got more direct reports than one person can run properly. The hire that fixes this sits between you and most of them.</t>
+          <t>Give them responsibility and the authority to go with it. One without the other doesn't work.</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr"/>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>q15 is d/e</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
@@ -16199,7 +16199,7 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Hand over one whole area with the decisions attached. Half a handover leaves you doing the work and them carrying the confusion.</t>
+          <t>Train them yourself, then give them ninety days to prove they're the one.</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr"/>
@@ -16212,25 +16212,21 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>talent</t>
+          <t>fulfilment</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Fix action 6</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Give it ninety days before you judge it, and don't let yourself become the escalation point for what you handed over.</t>
+          <t>You are {c} constrained</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr"/>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>always prints</t>
-        </is>
-      </c>
+      <c r="E35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -16240,12 +16236,12 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Title, nothing failing</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>You are {c} constrained</t>
+          <t>The tightest thing is {c}</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr"/>
@@ -16259,12 +16255,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Title, nothing failing</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>The tightest thing is {c}</t>
+          <t>This is capacity, not capability. You know how to do the work, but you can't do enough of it.</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr"/>
@@ -16278,16 +16274,24 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Opening</t>
+          <t>Evidence clause 1</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>This is capacity, not capability. You know how to do the work and you can't get enough hours of it out the door.</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr"/>
-      <c r="E38" s="8" t="inlineStr"/>
+          <t>you're running {q16.band}</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>you're running at {q16.exact}% booked</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>{q16.band}, {q16.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -16297,22 +16301,18 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 1</t>
+          <t>Evidence clause 2</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>you're running {q16.band}</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>you're running at {q16.exact}% booked</t>
-        </is>
-      </c>
+          <t>{q17.band}</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr"/>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>{q16.band}, {q16.exact}</t>
+          <t>{q17.band}</t>
         </is>
       </c>
     </row>
@@ -16324,18 +16324,18 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 2</t>
+          <t>Evidence clause 3</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>{q17.band}</t>
+          <t>lead times have {q18.band}</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr"/>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>{q17.band}</t>
+          <t>{q18.band}</t>
         </is>
       </c>
     </row>
@@ -16347,18 +16347,18 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 3</t>
+          <t>Evidence clause 4</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>lead times have {q18.band}</t>
+          <t>a typical job is ready {q19.band}</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr"/>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>{q18.band}</t>
+          <t>{q19.band}</t>
         </is>
       </c>
     </row>
@@ -16370,20 +16370,16 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 4</t>
+          <t>Closing</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>a typical job is ready {q19.band}</t>
+          <t>Nothing at the front of the business needs attention until the back of it can breathe. Anything you do to bring in more work right now gets paid for by the customers you already have.</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr"/>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>{q19.band}</t>
-        </is>
-      </c>
+      <c r="E42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -16393,12 +16389,12 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Fix, lead line</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Nothing at the front of the business needs attention until the back of it can breathe. Anything you do to bring in more work right now gets paid for by the customers you already have.</t>
+          <t>Make what you already have work properly, cut what isn't earning its capacity, then hire. In that order.</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr"/>
@@ -16412,16 +16408,20 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Fix, lead line</t>
+          <t>Fix action 1</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>You need more output from what you already have, or more capacity, before you go and win any more work.</t>
+          <t>Find the one step everything stalls at, and put the next day into streamlining that one step.</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr"/>
-      <c r="E44" s="8" t="inlineStr"/>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -16431,18 +16431,18 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Fix action 1</t>
+          <t>Fix action 2</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Find the one step everything queues behind, then put your next hour into that step and nothing else.</t>
+          <t>Write the five things that go wrong most often into one page checklists. Undocumented work is slow work.</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr"/>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>always prints</t>
+          <t>q46 is b/c/z</t>
         </is>
       </c>
     </row>
@@ -16454,18 +16454,18 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Fix action 2</t>
+          <t>Fix action 3</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Write the five things that go wrong most often into one page checklists. Undocumented work is slow work.</t>
+          <t>Look at what your best people actually spent last week on. Anything that didn't need them is capacity you already have.</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr"/>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>q46 is b/c/z</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
@@ -16477,12 +16477,12 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Fix action 3</t>
+          <t>Fix action 4</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Look at what your best people actually spent last week on. Anything that didn't need them is capacity you already have.</t>
+          <t>Cut the jobs that eat the most capacity for the least return.</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr"/>
@@ -16500,66 +16500,58 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Fix action 4</t>
+          <t>Fix action 5</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Quote the lead time you actually deliver rather than the one you hope for. A blown promise costs a customer you'd already won.</t>
+          <t>Then hire more capacity into the roles that need it.</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr"/>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>q19 is c/d</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>fulfilment</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Fix action 5</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Work out which jobs eat the most capacity for the least return, and stop taking those until the queue clears.</t>
+          <t>You are {c} constrained</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr"/>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>always prints</t>
-        </is>
-      </c>
+      <c r="E49" s="8" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>fulfilment</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Fix action 6</t>
+          <t>Title, nothing failing</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Add capacity last, once the steps above have been worked. Hiring multiplies whatever the process already does.</t>
+          <t>The tightest thing is {c}</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr"/>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>always prints</t>
-        </is>
-      </c>
+      <c r="E50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -16569,12 +16561,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>You are {c} constrained</t>
+          <t>Value here means what the customer perceives, and it has nothing to do with your pricing or your margin. They buy, then they either stop or start giving most of the work to somebody else.</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr"/>
@@ -16588,16 +16580,24 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Title, nothing failing</t>
+          <t>Evidence clause 1</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>The tightest thing is {c}</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr"/>
-      <c r="E52" s="8" t="inlineStr"/>
+          <t>of the customers you had a year ago, {q21.band} still buy from you</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>of the customers you had a year ago, {q21.exact}% still buy from you</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>{q21.band}, {q21.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -16607,16 +16607,24 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Opening</t>
+          <t>Evidence clause 2</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Value here means what the customer perceives, and it has nothing to do with your pricing or your margin. They buy, then they either stop or start giving most of the work to somebody else.</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr"/>
-      <c r="E53" s="8" t="inlineStr"/>
+          <t>you get {q57.band} of the work they put out</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>you get {q57.exact}% of the work they put out</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>{q57.band}, {q57.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -16626,22 +16634,18 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 1</t>
+          <t>Evidence clause 3</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>of the customers you had a year ago, {q21.band} still buy from you</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>of the customers you had a year ago, {q21.exact}% still buy from you</t>
-        </is>
-      </c>
+          <t>they come back unprompted {q22.band}</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr"/>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>{q21.band}, {q21.exact}</t>
+          <t>{q22.band}</t>
         </is>
       </c>
     </row>
@@ -16653,22 +16657,18 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 2</t>
+          <t>Evidence clause 4</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>you get {q57.band} of the work they put out</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>you get {q57.exact}% of the work they put out</t>
-        </is>
-      </c>
+          <t>referrals bring in {q23.band} of your new customers</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr"/>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>{q57.band}, {q57.exact}</t>
+          <t>{q23.band}</t>
         </is>
       </c>
     </row>
@@ -16680,20 +16680,16 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 3</t>
+          <t>Closing</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>they come back unprompted {q22.band}</t>
+          <t>You're filling a leaky bucket. Every dollar going into finding new customers is currently paying to replace the ones walking out the other side, which is why the business feels busy and stays the same size.</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr"/>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t>{q22.band}</t>
-        </is>
-      </c>
+      <c r="E56" s="8" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -16703,20 +16699,16 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 4</t>
+          <t>Fix, lead line</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>referrals bring in {q23.band} of your new customers</t>
+          <t>You need to find out why customers leave or shrink, and fix that, before you spend another dollar finding new ones.</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr"/>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t>{q23.band}</t>
-        </is>
-      </c>
+      <c r="E57" s="8" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -16726,16 +16718,20 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Fix action 1</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>You're filling a leaky bucket. Every dollar going into finding new customers is currently paying to replace the ones walking out the other side, which is why the business feels busy and stays the same size.</t>
+          <t>Ring ten customers who stopped buying or cut back, and ask them straight. Not a survey. A phone call.</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr"/>
-      <c r="E58" s="8" t="inlineStr"/>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -16745,16 +16741,20 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Fix, lead line</t>
+          <t>Fix action 2</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>You need to find out why customers leave or shrink, and fix that, before you spend another dollar finding new ones.</t>
+          <t>Ask your biggest customers what they give to somebody else, and why. That work already exists, you're just not getting it.</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr"/>
-      <c r="E59" s="8" t="inlineStr"/>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>q57 is c/d/e</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -16764,12 +16764,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Fix action 1</t>
+          <t>Fix action 3</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Ring ten customers who stopped buying or cut back, and ask them straight. Not a survey. A phone call.</t>
+          <t>Look hard at what happens in the first thirty days after somebody buys. That's the part of the experience you control most tightly.</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr"/>
@@ -16787,18 +16787,18 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Fix action 2</t>
+          <t>Fix action 4</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Ask your biggest customers what they give to somebody else, and why. That work already exists, you're just not getting it.</t>
+          <t>Build one reason to come back that you initiate. A check in, or the next step offered before they go looking.</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr"/>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>q57 is c/d/e</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
@@ -16810,12 +16810,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Fix action 3</t>
+          <t>Fix action 5</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Look hard at what happens in the first thirty days after somebody buys. That's the part of the experience you control most tightly.</t>
+          <t>Measure retention monthly, so a drop shows up while you can still do something about it.</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr"/>
@@ -16828,48 +16828,40 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>offer</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Fix action 4</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Build one reason to come back that you initiate. A check in, or the next step offered before they go looking.</t>
+          <t>You are {c} constrained</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr"/>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>always prints</t>
-        </is>
-      </c>
+      <c r="E63" s="8" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>offer</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Fix action 5</t>
+          <t>Title, nothing failing</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Measure retention monthly, so a drop shows up while you can still do something about it.</t>
+          <t>The tightest thing is {c}</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr"/>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t>always prints</t>
-        </is>
-      </c>
+      <c r="E64" s="8" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -16879,12 +16871,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Opening sentence 1</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>You are {c} constrained</t>
+          <t>Enquiries arrive and they don't convert.</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr"/>
@@ -16898,12 +16890,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Title, nothing failing</t>
+          <t>Opening sentence 2</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>The tightest thing is {c}</t>
+          <t>That isn't a sales technique problem, it's what's on the table. Either the value in the offer doesn't justify the price you're asking, or there's something in the way of somebody saying yes.</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr"/>
@@ -16917,16 +16909,24 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Opening sentence 1</t>
+          <t>Evidence clause 1</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>Enquiries arrive and they don't convert.</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr"/>
-      <c r="E67" s="8" t="inlineStr"/>
+          <t>your close rate sits {q26.band}</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>your close rate sits at {q26.exact}%</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>{q26.band}, {q26.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -16936,16 +16936,20 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Opening sentence 2</t>
+          <t>Evidence clause 2</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>That isn't a sales technique problem, it's what's on the table. Either the value in the offer doesn't justify the price you're asking, or there's something in the way of somebody saying yes.</t>
+          <t>the most common reason you lose is {q27.band}</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr"/>
-      <c r="E68" s="8" t="inlineStr"/>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>{q27.band}</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -16955,22 +16959,18 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 1</t>
+          <t>Evidence clause 3</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>your close rate sits {q26.band}</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>your close rate sits at {q26.exact}%</t>
-        </is>
-      </c>
+          <t>prospects come back on your quote asking what's included {q28.band}</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr"/>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>{q26.band}, {q26.exact}</t>
+          <t>{q28.band}</t>
         </is>
       </c>
     </row>
@@ -16982,18 +16982,18 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 2</t>
+          <t>Evidence clause 4</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>the most common reason you lose is {q27.band}</t>
+          <t>they find out what you charge {q30.band}</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr"/>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>{q27.band}</t>
+          <t>{q30.band}</t>
         </is>
       </c>
     </row>
@@ -17005,20 +17005,16 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 3</t>
+          <t>Closing</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>prospects come back on your quote asking what's included {q28.band}</t>
+          <t>You don't fix this by dropping the price. You fix it by putting things into the offer that cost you very little and are worth real money to the buyer, and by removing whatever a prospect has to get over before they can say yes.</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr"/>
-      <c r="E71" s="8" t="inlineStr">
-        <is>
-          <t>{q28.band}</t>
-        </is>
-      </c>
+      <c r="E71" s="8" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -17028,20 +17024,16 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 4</t>
+          <t>Fix, lead line</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>they find out what you charge {q30.band}</t>
+          <t>You need more value in the offer than the price is asking for, and the hurdles taken out of the way of somebody saying yes.</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr"/>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t>{q30.band}</t>
-        </is>
-      </c>
+      <c r="E72" s="8" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
@@ -17051,16 +17043,20 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Fix action 1</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>You don't fix this by dropping the price. You fix it by putting things into the offer that cost you very little and are worth real money to the buyer, and by removing whatever a prospect has to get over before they can say yes.</t>
+          <t>List everything you already do for a customer that isn't written into the offer. That's value nobody can see.</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr"/>
-      <c r="E73" s="8" t="inlineStr"/>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
@@ -17070,16 +17066,20 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Fix, lead line</t>
+          <t>Fix action 2</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>You need more value in the offer than the price is asking for, and the hurdles taken out of the way of somebody saying yes.</t>
+          <t>Add two things that cost you close to nothing and are worth real money to the buyer. A guarantee, or something they would otherwise have to go and source themselves.</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr"/>
-      <c r="E74" s="8" t="inlineStr"/>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -17089,18 +17089,18 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Fix action 1</t>
+          <t>Fix action 3</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>List everything you already do for a customer that isn't written into the offer. That's value nobody can see.</t>
+          <t>Write down every question a prospect asks after they get the quote, then answer all of them inside the quote itself.</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr"/>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>always prints</t>
+          <t>q28 is c/d</t>
         </is>
       </c>
     </row>
@@ -17112,18 +17112,18 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Fix action 2</t>
+          <t>Fix action 4</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>Add two things that cost you close to nothing and are worth real money to the buyer. A guarantee, or something they would otherwise have to go and source themselves.</t>
+          <t>Put a price or a range where they can see it. Making somebody wait for a number is a hurdle before they have even decided.</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr"/>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>always prints</t>
+          <t>q30 is c/d</t>
         </is>
       </c>
     </row>
@@ -17135,18 +17135,18 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>Fix action 3</t>
+          <t>Fix action 5</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>Write down every question a prospect asks after they get the quote, then answer all of them inside the quote itself.</t>
+          <t>Sort your last twenty losses by reason and count them. If price keeps coming up, look at the value in the offer before you look at the number.</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr"/>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>q28 is c/d</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
@@ -17158,66 +17158,58 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Fix action 4</t>
+          <t>Fix action 6</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>Put a price or a range where they can see it. Making somebody wait for a number is a hurdle before they have even decided.</t>
+          <t>Test the new offer on the next ten enquiries before you change anything else.</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr"/>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>q30 is c/d</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>demand</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Fix action 5</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Sort your last twenty losses by reason and count them. If price keeps coming up, look at the value in the offer before you look at the number.</t>
+          <t>You are {c} constrained</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr"/>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t>always prints</t>
-        </is>
-      </c>
+      <c r="E79" s="8" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>demand</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Fix action 6</t>
+          <t>Title, nothing failing</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>Test the new offer on the next ten enquiries before you change anything else.</t>
+          <t>The tightest thing is {c}</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr"/>
-      <c r="E80" s="8" t="inlineStr">
-        <is>
-          <t>always prints</t>
-        </is>
-      </c>
+      <c r="E80" s="8" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
@@ -17227,12 +17219,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>You are {c} constrained</t>
+          <t>You've got capacity sitting idle and not enough people asking.</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr"/>
@@ -17246,16 +17238,24 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Title, nothing failing</t>
+          <t>Evidence clause 1</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>The tightest thing is {c}</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="inlineStr"/>
-      <c r="E82" s="8" t="inlineStr"/>
+          <t>enquiries run {q31.band}</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>enquiries run at about {q31.exact} a month</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>{q31.band}, {q31.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
@@ -17265,16 +17265,20 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Opening</t>
+          <t>Evidence clause 2</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>You've got capacity sitting idle and not enough people asking.</t>
+          <t>volume has {q33.band} over the last year</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr"/>
-      <c r="E83" s="8" t="inlineStr"/>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>{q33.band}</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
@@ -17284,22 +17288,18 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 1</t>
+          <t>Evidence clause 3</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>enquiries run {q31.band}</t>
-        </is>
-      </c>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>enquiries run at about {q31.exact} a month</t>
-        </is>
-      </c>
+          <t>{q35.band}</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr"/>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>{q31.band}, {q31.exact}</t>
+          <t>{q35.band}</t>
         </is>
       </c>
     </row>
@@ -17311,20 +17311,16 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 2</t>
+          <t>Closing</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>volume has {q33.band} over the last year</t>
+          <t>You could take on more work tomorrow, which is what separates this from a delivery problem. Nothing downstream is broken. The business just isn't being fed, and it won't start feeding itself.</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr"/>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t>{q33.band}</t>
-        </is>
-      </c>
+      <c r="E85" s="8" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
@@ -17334,20 +17330,16 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 3</t>
+          <t>Fix, lead line</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>{q35.band}</t>
+          <t>You need one lead source running properly and consistently before you go anywhere near a second.</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr"/>
-      <c r="E86" s="8" t="inlineStr">
-        <is>
-          <t>{q35.band}</t>
-        </is>
-      </c>
+      <c r="E86" s="8" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
@@ -17357,16 +17349,20 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Fix action 1</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>You could take on more work tomorrow, which is what separates this from a delivery problem. Nothing downstream is broken. The business just isn't being fed, and it won't start feeding itself.</t>
+          <t>Whatever you're doing to generate enquiries isn't running consistently. Start with the one thing you can do every week without fail.</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr"/>
-      <c r="E87" s="8" t="inlineStr"/>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>q35 is b/c</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
@@ -17376,16 +17372,20 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Fix, lead line</t>
+          <t>Fix action 2</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>You need one lead source running properly and consistently before you go anywhere near a second.</t>
+          <t>Pick the lead source that already brings your best customers and put real weight behind it.</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr"/>
-      <c r="E88" s="8" t="inlineStr"/>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
@@ -17395,18 +17395,18 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Fix action 1</t>
+          <t>Fix action 3</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Whatever you're doing to generate enquiries isn't running consistently. Start with the one thing you can do every week without fail.</t>
+          <t>Go and ask for work. Outbound to the twenty businesses you'd most like to work with beats waiting on referrals.</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr"/>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>q35 is b/c</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
@@ -17418,18 +17418,18 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Fix action 2</t>
+          <t>Fix action 4</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>Pick the lead source that already brings your best customers and put real weight behind it.</t>
+          <t>Everything arrives through one lead source. Stand up a second before that one changes.</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr"/>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>always prints</t>
+          <t>q43 is c</t>
         </is>
       </c>
     </row>
@@ -17441,12 +17441,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Fix action 3</t>
+          <t>Fix action 5</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>Go and ask for work. Outbound to the twenty businesses you'd most like to work with beats waiting on referrals.</t>
+          <t>Ask every happy customer for one introduction.</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr"/>
@@ -17464,66 +17464,58 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Fix action 4</t>
+          <t>Fix action 6</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Everything arrives through one lead source. Stand up a second before that one changes.</t>
+          <t>Give a lead source ninety days before you judge it. Anything shorter is guesswork.</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr"/>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>q43 is c</t>
+          <t>always prints</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>margin</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>Fix action 5</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>Ask every happy customer for one introduction.</t>
+          <t>You are {c} constrained</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr"/>
-      <c r="E93" s="8" t="inlineStr">
-        <is>
-          <t>always prints</t>
-        </is>
-      </c>
+      <c r="E93" s="8" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>margin</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Fix action 6</t>
+          <t>Title, nothing failing</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Give a lead source ninety days before you judge it. Anything shorter is guesswork.</t>
+          <t>The tightest thing is {c}</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr"/>
-      <c r="E94" s="8" t="inlineStr">
-        <is>
-          <t>always prints</t>
-        </is>
-      </c>
+      <c r="E94" s="8" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
@@ -17533,12 +17525,12 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>You are {c} constrained</t>
+          <t>You're full and busy, and there's nothing left at the end of it.</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr"/>
@@ -17552,16 +17544,24 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Title, nothing failing</t>
+          <t>Evidence clause 1</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>The tightest thing is {c}</t>
-        </is>
-      </c>
-      <c r="D96" s="7" t="inlineStr"/>
-      <c r="E96" s="8" t="inlineStr"/>
+          <t>what's left after direct costs sits {q36.band}</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>what's left after direct costs sits at {q36.exact}%</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>{q36.band}, {q36.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
@@ -17571,16 +17571,24 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Opening</t>
+          <t>Evidence clause 2</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>You're full and busy, and there's nothing left at the end of it.</t>
-        </is>
-      </c>
-      <c r="D97" s="7" t="inlineStr"/>
-      <c r="E97" s="8" t="inlineStr"/>
+          <t>after everything it's {q37.band}</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>after everything it's {q37.exact}%</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>{q37.band}, {q37.exact}</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
@@ -17590,22 +17598,18 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 1</t>
+          <t>Evidence clause 3</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>what's left after direct costs sits {q36.band}</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>what's left after direct costs sits at {q36.exact}%</t>
-        </is>
-      </c>
+          <t>{q38.band}</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr"/>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>{q36.band}, {q36.exact}</t>
+          <t>{q38.band}</t>
         </is>
       </c>
     </row>
@@ -17617,22 +17621,18 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 2</t>
+          <t>Evidence clause 4</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>after everything it's {q37.band}</t>
-        </is>
-      </c>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>after everything it's {q37.exact}%</t>
-        </is>
-      </c>
+          <t>jobs run over what you quoted {q39.band}</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr"/>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>{q37.band}, {q37.exact}</t>
+          <t>{q39.band}</t>
         </is>
       </c>
     </row>
@@ -17644,20 +17644,16 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 3</t>
+          <t>Closing</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>{q38.band}</t>
+          <t>Volume won't rescue this. At the margin you're running, more work gets you more of the same result and it arrives faster.</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr"/>
-      <c r="E100" s="8" t="inlineStr">
-        <is>
-          <t>{q38.band}</t>
-        </is>
-      </c>
+      <c r="E100" s="8" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
@@ -17667,20 +17663,16 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Evidence clause 4</t>
+          <t>Fix, lead line</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>jobs run over what you quoted {q39.band}</t>
+          <t>You need to know what each job actually earns you before you change anything. A price rise can cost you customers as easily as it can fix the margin.</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr"/>
-      <c r="E101" s="8" t="inlineStr">
-        <is>
-          <t>{q39.band}</t>
-        </is>
-      </c>
+      <c r="E101" s="8" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
@@ -17690,16 +17682,20 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Closing</t>
+          <t>Fix action 1</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>Volume won't rescue this. At the margin you're running, more work gets you more of the same result and it arrives faster.</t>
+          <t>Raise prices on new work now. Ten percent across the board, and watch what actually happens.</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr"/>
-      <c r="E102" s="8" t="inlineStr"/>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>q38 is c/d/e</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
@@ -17709,16 +17705,20 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Fix, lead line</t>
+          <t>Fix action 2</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>You need to know what each job actually earns you before you change anything. A price rise can cost you customers as easily as it can fix the margin.</t>
+          <t>Work out what each job really costs, your own time included, then rank your last twenty by what was left.</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr"/>
-      <c r="E103" s="8" t="inlineStr"/>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>always prints</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
@@ -17728,18 +17728,18 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>Fix action 1</t>
+          <t>Fix action 3</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>Raise prices on new work now. Ten percent across the board, and watch what actually happens.</t>
+          <t>Quote a contingency into the jobs that historically run over. You already know which ones they are.</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr"/>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>q38 is c/d/e</t>
+          <t>q39 is c/d</t>
         </is>
       </c>
     </row>
@@ -17751,12 +17751,12 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Fix action 2</t>
+          <t>Fix action 4</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>Work out what each job really costs, your own time included, then rank your last twenty by what was left.</t>
+          <t>Find your worst three customers by margin, then reprice them or let them go.</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr"/>
@@ -17774,69 +17774,23 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>Fix action 3</t>
+          <t>Fix action 5</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>Quote a contingency into the jobs that historically run over. You already know which ones they are.</t>
+          <t>Don't discount to win. A discount is the fastest way to buy work you'll resent delivering.</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr"/>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>q39 is c/d</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>margin</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>Fix action 4</t>
-        </is>
-      </c>
-      <c r="C107" s="7" t="inlineStr">
-        <is>
-          <t>Find your worst three customers by margin, then reprice them or let them go.</t>
-        </is>
-      </c>
-      <c r="D107" s="7" t="inlineStr"/>
-      <c r="E107" s="8" t="inlineStr">
-        <is>
           <t>always prints</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>margin</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
-        <is>
-          <t>Fix action 5</t>
-        </is>
-      </c>
-      <c r="C108" s="7" t="inlineStr">
-        <is>
-          <t>Don't discount to win. A discount is the fastest way to buy work you'll resent delivering.</t>
-        </is>
-      </c>
-      <c r="D108" s="7" t="inlineStr"/>
-      <c r="E108" s="8" t="inlineStr">
-        <is>
-          <t>always prints</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:E108"/>
+  <autoFilter ref="A2:E106"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -18404,7 +18358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18626,17 +18580,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>talent</t>
+          <t>fulfilment</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Item 5</t>
+          <t>Lead line</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Don't redraw the org chart. What's missing is a person who doesn't exist, not a diagram.</t>
+          <t>Until you've done the above, leave these alone.</t>
         </is>
       </c>
     </row>
@@ -18648,12 +18602,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Lead line</t>
+          <t>Item 1</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Until you can deliver what you've already sold, leave these alone.</t>
+          <t>Don't take on new customers until you've done the above.</t>
         </is>
       </c>
     </row>
@@ -18665,12 +18619,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Item 1</t>
+          <t>Item 2</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Don't chase new customers. You'd be damaging the ones you have to serve the ones you win.</t>
+          <t>Don't start something new.</t>
         </is>
       </c>
     </row>
@@ -18682,12 +18636,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Item 2</t>
+          <t>Item 3</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Don't increase marketing spend. Adding demand to a full pipeline is the classic accelerant.</t>
+          <t>Don't drop your prices.</t>
         </is>
       </c>
     </row>
@@ -18699,46 +18653,46 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Item 3</t>
+          <t>Item 4</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Don't launch a new service line. New work is slow work while the process is still being learned.</t>
+          <t>Don't promise a shorter lead time to win a job.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>fulfilment</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Item 4</t>
+          <t>Lead line</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Don't drop your prices. You've got more demand than capacity, which is the one time raising them is easy.</t>
+          <t>Until customers stay, leave these alone.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>fulfilment</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Item 5</t>
+          <t>Item 1</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Don't promise a shorter lead time to win a job. That's where the quality problem starts.</t>
+          <t>Don't spend more on acquisition. You'd be paying to fill a bucket with a hole in it.</t>
         </is>
       </c>
     </row>
@@ -18750,12 +18704,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Lead line</t>
+          <t>Item 2</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Until customers stay, leave these alone.</t>
+          <t>Don't raise prices. Value perception is already the problem.</t>
         </is>
       </c>
     </row>
@@ -18767,12 +18721,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Item 1</t>
+          <t>Item 3</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Don't spend more on acquisition. You'd be paying to fill a bucket with a hole in it.</t>
+          <t>Don't add a new product for existing customers who aren't buying the current one.</t>
         </is>
       </c>
     </row>
@@ -18784,12 +18738,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Item 2</t>
+          <t>Item 4</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Don't raise prices. Value perception is already the problem.</t>
+          <t>Don't expand into a new market. You'd take the retention problem with you.</t>
         </is>
       </c>
     </row>
@@ -18801,46 +18755,46 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Item 3</t>
+          <t>Item 5</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Don't add a new product for existing customers who aren't buying the current one.</t>
+          <t>Don't run a loyalty programme. A discount doesn't fix a value gap, it confirms one.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>offer</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Item 4</t>
+          <t>Lead line</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Don't expand into a new market. You'd take the retention problem with you.</t>
+          <t>Until the offer lands, leave these alone.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>offer</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Item 5</t>
+          <t>Item 1</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Don't run a loyalty programme. A discount doesn't fix a value gap, it confirms one.</t>
+          <t>Don't buy more leads. You'd pay more money for the same conversion rate.</t>
         </is>
       </c>
     </row>
@@ -18852,12 +18806,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Lead line</t>
+          <t>Item 2</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Until the offer lands, leave these alone.</t>
+          <t>Don't hire a salesperson. They'd fail against the same offer you're failing against.</t>
         </is>
       </c>
     </row>
@@ -18869,12 +18823,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Item 1</t>
+          <t>Item 3</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Don't buy more leads. You'd pay more money for the same conversion rate.</t>
+          <t>Don't cut your price. Price is rarely the real reason, and you can't test it while the offer is unclear.</t>
         </is>
       </c>
     </row>
@@ -18886,12 +18840,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Item 2</t>
+          <t>Item 4</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Don't hire a salesperson. They'd fail against the same offer you're failing against.</t>
+          <t>Don't add more options. More choice is part of why these deals are stalling.</t>
         </is>
       </c>
     </row>
@@ -18903,46 +18857,46 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Item 3</t>
+          <t>Item 5</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Don't cut your price. Price is rarely the real reason, and you can't test it while the offer is unclear.</t>
+          <t>Don't rebrand. The words are the problem, not the logo.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>demand</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Item 4</t>
+          <t>Lead line</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Don't add more options. More choice is part of why these deals are stalling.</t>
+          <t>Until enquiries lift, leave these alone.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>demand</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Item 5</t>
+          <t>Item 1</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Don't rebrand. The words are the problem, not the logo.</t>
+          <t>Don't hire. You'd be adding capacity to capacity you already can't fill.</t>
         </is>
       </c>
     </row>
@@ -18954,12 +18908,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Lead line</t>
+          <t>Item 2</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Until enquiries lift, leave these alone.</t>
+          <t>Don't build a new product. The one you have hasn't been shown to enough people.</t>
         </is>
       </c>
     </row>
@@ -18971,12 +18925,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Item 1</t>
+          <t>Item 3</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Don't hire. You'd be adding capacity to capacity you already can't fill.</t>
+          <t>Don't cut prices to stimulate demand. It rarely moves volume, and it permanently resets what customers expect to pay.</t>
         </is>
       </c>
     </row>
@@ -18988,12 +18942,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Item 2</t>
+          <t>Item 4</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Don't build a new product. The one you have hasn't been shown to enough people.</t>
+          <t>Don't spread across five channels at once. One channel run properly beats five run badly.</t>
         </is>
       </c>
     </row>
@@ -19005,46 +18959,46 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Item 3</t>
+          <t>Item 5</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Don't cut prices to stimulate demand. It rarely moves volume, and it permanently resets what customers expect to pay.</t>
+          <t>Don't wait for referrals to pick back up. Referral volume follows the number of customers you have, and that's the number that's short.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>margin</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Item 4</t>
+          <t>Lead line</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Don't spread across five channels at once. One channel run properly beats five run badly.</t>
+          <t>Until the margin moves, leave these alone.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>demand</t>
+          <t>margin</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Item 5</t>
+          <t>Item 1</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Don't wait for referrals to pick back up. Referral volume follows the number of customers you have, and that's the number that's short.</t>
+          <t>Don't chase volume. More work at this margin is more risk for the same money.</t>
         </is>
       </c>
     </row>
@@ -19056,12 +19010,12 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Lead line</t>
+          <t>Item 2</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Until the margin moves, leave these alone.</t>
+          <t>Don't hire. Every head you add at this margin needs a lot of revenue standing behind it.</t>
         </is>
       </c>
     </row>
@@ -19073,12 +19027,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Item 1</t>
+          <t>Item 3</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Don't chase volume. More work at this margin is more risk for the same money.</t>
+          <t>Don't take the big thin job because it's good for the brand. Reputation doesn't pay wages.</t>
         </is>
       </c>
     </row>
@@ -19090,12 +19044,12 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Item 2</t>
+          <t>Item 4</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Don't hire. Every head you add at this margin needs a lot of revenue standing behind it.</t>
+          <t>Don't discount anything. There's nothing left to give away.</t>
         </is>
       </c>
     </row>
@@ -19107,51 +19061,17 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Item 3</t>
+          <t>Item 5</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Don't take the big thin job because it's good for the brand. Reputation doesn't pay wages.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>margin</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>Item 4</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>Don't discount anything. There's nothing left to give away.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>margin</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>Item 5</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
           <t>Don't invest in growth. Growing an unprofitable model makes it unprofitable faster.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C44"/>
+  <autoFilter ref="A2:C42"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
